--- a/Data Files/Backoffce/IndexacaoFG/Arquivos/Relatório de Recusas  08.09.2025 a 14.09.2025.xlsx
+++ b/Data Files/Backoffce/IndexacaoFG/Arquivos/Relatório de Recusas  08.09.2025 a 14.09.2025.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://allianzms.sharepoint.com/teams/BR0010-4356589/Shared Documents/BACK-OFFICE SME/Santander/2025/Relatório de Recusas/05. Maio/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{0DE4BEDC-03F2-469C-BF9E-7D3AD3DA4426}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{31977251-4844-4E1E-9117-76B9027D71CD}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="19530" windowHeight="9780" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="19530" windowHeight="9780" firstSheet="1" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="08.09" sheetId="2" r:id="rId1"/>
@@ -42,7 +42,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="293" uniqueCount="59">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="360" uniqueCount="91">
   <si>
     <t>SEGURADORA</t>
   </si>
@@ -219,6 +219,108 @@
   </si>
   <si>
     <t xml:space="preserve">LILIAN JUCELI SOARES KELLER                  </t>
+  </si>
+  <si>
+    <t>PAULO RODRIGO MARTIM KARSBURG CPF- 01175391042</t>
+  </si>
+  <si>
+    <t>EDUARDO RIBEIRO RAGAZZI CPF- 42254439812</t>
+  </si>
+  <si>
+    <t>ADRIANA APARECIDA DE ALMEIDA CPF- 09364077601</t>
+  </si>
+  <si>
+    <t>A marca informada não corresponde ao chassi do veículo.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">JEFFERSON BRAZ FONSECA ROSA                  </t>
+  </si>
+  <si>
+    <t>Falta de vistoria</t>
+  </si>
+  <si>
+    <t xml:space="preserve">LARISSA DOS SANTOS FRIGOTTO                  </t>
+  </si>
+  <si>
+    <t>Fotos que tiveram repique: Documento do veículo, Frente e lateral do passageiro, Chassi</t>
+  </si>
+  <si>
+    <t xml:space="preserve">ARCEU SANTOS CORDEIRO DE CAMPOS              </t>
+  </si>
+  <si>
+    <t>Bônus;</t>
+  </si>
+  <si>
+    <t>Conforme consulta na central de bônus, identificamos que não
+há possibilidade efetuar a transferência de bônus para o(a) senhor
+(a) ARCEU SANTOS CORDEIRO DE CAMPOS, pois este não consta como con
+dutor na apólice anterior.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">EDGAR ALVES NETO                             </t>
+  </si>
+  <si>
+    <t xml:space="preserve">a pedido segurado </t>
+  </si>
+  <si>
+    <t xml:space="preserve">JOSE RICARDO PEDROSA DE MORAES               </t>
+  </si>
+  <si>
+    <t>Informamos que a proposta em questão se encontra em duplicidade co
+m a proposta 134174713 e a apólice de renovação 517720245131208773
+8 ainda consta vigente até 25/10/25, para prosseguirmos com a emis
+são se faz necessário realizar o cancelamento de ambas</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10 338 070 ROSMEN DOS SANTOS LOPES ME        </t>
+  </si>
+  <si>
+    <t>Santander - Veículo em duplicidade com proposta</t>
+  </si>
+  <si>
+    <t xml:space="preserve">WILKELENE DA COSTA NASCIMENTO                </t>
+  </si>
+  <si>
+    <t>SEGURADO NÃO CORRIGIU AS FOTOS / PRAZO INSPIRADO Fotos: Frente e lateral do passageiro, Frente e lateral do motorista, Traseira e lateral do motorista, Traseira e lateral do passageiro, Chassi</t>
+  </si>
+  <si>
+    <t xml:space="preserve">FRANCISCO EDIVAN DE ARAUJO                   </t>
+  </si>
+  <si>
+    <t xml:space="preserve">Fotos que tiveram repique: Frente e lateral do passageiro, Frente e lateral do motorista, Traseira e lateral do motorista, Motor e placa </t>
+  </si>
+  <si>
+    <t xml:space="preserve">ANA DE FATIMA RIBEIRO RAMOS                  </t>
+  </si>
+  <si>
+    <t>FRUSTRADO, PRAZO PARA REENVIO EXPIRADO. FOTOS NÃO CORRIGIDAS: Documento da moto, Lateral esquerda, Número do Chassi, Painel com a motocicleta ligada</t>
+  </si>
+  <si>
+    <t xml:space="preserve">WELLINGTON VICENTE DA SILVA                  </t>
+  </si>
+  <si>
+    <t xml:space="preserve">TLBM RENTAL CONSTRUCOES LTDA ME              </t>
+  </si>
+  <si>
+    <t xml:space="preserve">MALHARIA AURORA LTDA EPP                     </t>
+  </si>
+  <si>
+    <t xml:space="preserve">TEMPO REAL PROMOCOES E EVENTOS LTDA ME       </t>
+  </si>
+  <si>
+    <t xml:space="preserve">ANDRIELI KOBREN                              </t>
+  </si>
+  <si>
+    <t xml:space="preserve">FRUSTRADO, PRAZO PARA REENVIO EXPIRADO. FOTOS NÃO CORRIGIDAS: CHASSI </t>
+  </si>
+  <si>
+    <t xml:space="preserve">MANUEL DE OLIVEIRA SILVA                     </t>
+  </si>
+  <si>
+    <t xml:space="preserve">MARIA DO CARMO ALVES RIBEIRO                 </t>
+  </si>
+  <si>
+    <t xml:space="preserve">POLEN LTDA EPP                               </t>
   </si>
 </sst>
 </file>
@@ -270,7 +372,7 @@
       <charset val="1"/>
     </font>
   </fonts>
-  <fills count="3">
+  <fills count="4">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -283,8 +385,14 @@
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="0"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
   </fills>
-  <borders count="14">
+  <borders count="15">
     <border>
       <left/>
       <right/>
@@ -457,12 +565,27 @@
       </bottom>
       <diagonal/>
     </border>
+    <border>
+      <left style="thin">
+        <color rgb="FF000000"/>
+      </left>
+      <right style="thin">
+        <color rgb="FF000000"/>
+      </right>
+      <top style="thin">
+        <color rgb="FF000000"/>
+      </top>
+      <bottom style="thin">
+        <color theme="4" tint="0.39997558519241921"/>
+      </bottom>
+      <diagonal/>
+    </border>
   </borders>
   <cellStyleXfs count="2">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="56">
+  <cellXfs count="78">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="2" borderId="1" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
@@ -541,9 +664,6 @@
       <alignment horizontal="center" vertical="top"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="3" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment wrapText="1"/>
-    </xf>
     <xf numFmtId="14" fontId="2" fillId="2" borderId="2" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
@@ -576,29 +696,119 @@
     <xf numFmtId="0" fontId="5" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1"/>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="13" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1"/>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="12" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="3" xfId="0" applyBorder="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="5" fillId="3" borderId="14" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="3" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="12" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="12" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="14" fontId="5" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="14" fontId="5" fillId="0" borderId="5" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="12" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="1" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
   </cellXfs>
   <cellStyles count="2">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
     <cellStyle name="Normal_Plan2_1" xfId="1" xr:uid="{69F13A52-20D9-46CA-8619-BC7A1BA09FD8}"/>
   </cellStyles>
-  <dxfs count="0"/>
+  <dxfs count="3">
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+  </dxfs>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleMedium9"/>
   <extLst>
     <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{EB79DEF2-80B8-43e5-95BD-54CBDDF9020C}">
@@ -983,7 +1193,7 @@
       <c r="D2" s="21" t="s">
         <v>10</v>
       </c>
-      <c r="E2" s="49">
+      <c r="E2" s="46">
         <v>3450074298</v>
       </c>
       <c r="F2" s="22" t="s">
@@ -1007,13 +1217,13 @@
       <c r="C3" s="7">
         <v>45908</v>
       </c>
-      <c r="D3" s="51" t="s">
+      <c r="D3" s="47" t="s">
         <v>10</v>
       </c>
-      <c r="E3" s="49">
+      <c r="E3" s="46">
         <v>3450074265</v>
       </c>
-      <c r="F3" s="50" t="s">
+      <c r="F3" s="31" t="s">
         <v>14</v>
       </c>
       <c r="G3" s="20" t="s">
@@ -1034,13 +1244,13 @@
       <c r="C4" s="28">
         <v>45908</v>
       </c>
-      <c r="D4" s="53">
+      <c r="D4" s="25">
         <v>134188990</v>
       </c>
-      <c r="E4" s="49">
+      <c r="E4" s="46">
         <v>3450067764</v>
       </c>
-      <c r="F4" s="48" t="s">
+      <c r="F4" s="12" t="s">
         <v>15</v>
       </c>
       <c r="G4" s="20" t="s">
@@ -1063,13 +1273,13 @@
       <c r="C5" s="28">
         <v>45908</v>
       </c>
-      <c r="D5" s="53">
+      <c r="D5" s="25">
         <v>134191040</v>
       </c>
-      <c r="E5" s="49">
+      <c r="E5" s="46">
         <v>3450067820</v>
       </c>
-      <c r="F5" s="48" t="s">
+      <c r="F5" s="12" t="s">
         <v>18</v>
       </c>
       <c r="G5" s="20" t="s">
@@ -1092,13 +1302,13 @@
       <c r="C6" s="28">
         <v>45908</v>
       </c>
-      <c r="D6" s="53">
+      <c r="D6" s="25">
         <v>134189799</v>
       </c>
-      <c r="E6" s="49">
+      <c r="E6" s="46">
         <v>3450066763</v>
       </c>
-      <c r="F6" s="48" t="s">
+      <c r="F6" s="12" t="s">
         <v>19</v>
       </c>
       <c r="G6" s="20" t="s">
@@ -1121,19 +1331,19 @@
       <c r="C7" s="28">
         <v>45908</v>
       </c>
-      <c r="D7" s="53">
+      <c r="D7" s="25">
         <v>134190893</v>
       </c>
-      <c r="E7" s="49">
+      <c r="E7" s="46">
         <v>3450067819</v>
       </c>
-      <c r="F7" s="48" t="s">
+      <c r="F7" s="12" t="s">
         <v>20</v>
       </c>
       <c r="G7" s="26" t="s">
         <v>21</v>
       </c>
-      <c r="H7" s="47" t="s">
+      <c r="H7" s="12" t="s">
         <v>22</v>
       </c>
       <c r="I7" s="27">
@@ -1150,13 +1360,13 @@
       <c r="C8" s="28">
         <v>45908</v>
       </c>
-      <c r="D8" s="53">
+      <c r="D8" s="25">
         <v>134222045</v>
       </c>
-      <c r="E8" s="49">
+      <c r="E8" s="46">
         <v>3450069601</v>
       </c>
-      <c r="F8" s="48" t="s">
+      <c r="F8" s="12" t="s">
         <v>23</v>
       </c>
       <c r="G8" s="26" t="s">
@@ -1179,13 +1389,13 @@
       <c r="C9" s="28">
         <v>45908</v>
       </c>
-      <c r="D9" s="53">
+      <c r="D9" s="25">
         <v>134248576</v>
       </c>
-      <c r="E9" s="49">
+      <c r="E9" s="46">
         <v>3450070921</v>
       </c>
-      <c r="F9" s="48" t="s">
+      <c r="F9" s="12" t="s">
         <v>26</v>
       </c>
       <c r="G9" s="20" t="s">
@@ -1208,13 +1418,13 @@
       <c r="C10" s="28">
         <v>45908</v>
       </c>
-      <c r="D10" s="53">
+      <c r="D10" s="25">
         <v>134242792</v>
       </c>
-      <c r="E10" s="49">
+      <c r="E10" s="46">
         <v>3450070679</v>
       </c>
-      <c r="F10" s="48" t="s">
+      <c r="F10" s="12" t="s">
         <v>27</v>
       </c>
       <c r="G10" s="20" t="s">
@@ -1237,19 +1447,19 @@
       <c r="C11" s="28">
         <v>45908</v>
       </c>
-      <c r="D11" s="53">
+      <c r="D11" s="25">
         <v>134283389</v>
       </c>
-      <c r="E11" s="49">
+      <c r="E11" s="46">
         <v>3450072769</v>
       </c>
-      <c r="F11" s="48" t="s">
+      <c r="F11" s="12" t="s">
         <v>28</v>
       </c>
       <c r="G11" s="20" t="s">
         <v>24</v>
       </c>
-      <c r="H11" s="54" t="s">
+      <c r="H11" s="49" t="s">
         <v>29</v>
       </c>
       <c r="I11" s="27">
@@ -1266,19 +1476,19 @@
       <c r="C12" s="28">
         <v>45908</v>
       </c>
-      <c r="D12" s="53">
+      <c r="D12" s="25">
         <v>134313099</v>
       </c>
-      <c r="E12" s="49">
+      <c r="E12" s="46">
         <v>3450074529</v>
       </c>
-      <c r="F12" s="48" t="s">
+      <c r="F12" s="12" t="s">
         <v>30</v>
       </c>
       <c r="G12" s="20" t="s">
         <v>31</v>
       </c>
-      <c r="H12" s="55" t="s">
+      <c r="H12" s="9" t="s">
         <v>32</v>
       </c>
       <c r="I12" s="27">
@@ -1295,19 +1505,19 @@
       <c r="C13" s="28">
         <v>45908</v>
       </c>
-      <c r="D13" s="53">
+      <c r="D13" s="25">
         <v>134303403</v>
       </c>
-      <c r="E13" s="49">
+      <c r="E13" s="46">
         <v>3450073781</v>
       </c>
-      <c r="F13" s="48" t="s">
+      <c r="F13" s="12" t="s">
         <v>33</v>
       </c>
       <c r="G13" s="20" t="s">
         <v>31</v>
       </c>
-      <c r="H13" s="55" t="s">
+      <c r="H13" s="9" t="s">
         <v>32</v>
       </c>
       <c r="I13" s="27">
@@ -1324,19 +1534,19 @@
       <c r="C14" s="28">
         <v>45908</v>
       </c>
-      <c r="D14" s="53">
+      <c r="D14" s="25">
         <v>134197036</v>
       </c>
-      <c r="E14" s="49">
+      <c r="E14" s="46">
         <v>3450068281</v>
       </c>
-      <c r="F14" s="48" t="s">
+      <c r="F14" s="12" t="s">
         <v>34</v>
       </c>
       <c r="G14" s="20" t="s">
         <v>21</v>
       </c>
-      <c r="H14" s="55" t="s">
+      <c r="H14" s="9" t="s">
         <v>35</v>
       </c>
       <c r="I14" s="27">
@@ -1353,19 +1563,19 @@
       <c r="C15" s="28">
         <v>45908</v>
       </c>
-      <c r="D15" s="53">
+      <c r="D15" s="25">
         <v>134196299</v>
       </c>
-      <c r="E15" s="49">
+      <c r="E15" s="46">
         <v>3450068226</v>
       </c>
-      <c r="F15" s="48" t="s">
+      <c r="F15" s="12" t="s">
         <v>36</v>
       </c>
       <c r="G15" s="20" t="s">
         <v>31</v>
       </c>
-      <c r="H15" s="55" t="s">
+      <c r="H15" s="9" t="s">
         <v>32</v>
       </c>
       <c r="I15" s="27">
@@ -1382,19 +1592,19 @@
       <c r="C16" s="28">
         <v>45908</v>
       </c>
-      <c r="D16" s="53">
+      <c r="D16" s="25">
         <v>134192439</v>
       </c>
-      <c r="E16" s="49">
+      <c r="E16" s="46">
         <v>3450066400</v>
       </c>
-      <c r="F16" s="48" t="s">
+      <c r="F16" s="12" t="s">
         <v>37</v>
       </c>
       <c r="G16" s="20" t="s">
         <v>31</v>
       </c>
-      <c r="H16" s="55" t="s">
+      <c r="H16" s="9" t="s">
         <v>32</v>
       </c>
       <c r="I16" s="27">
@@ -1411,13 +1621,13 @@
       <c r="C17" s="28">
         <v>45908</v>
       </c>
-      <c r="D17" s="53">
+      <c r="D17" s="25">
         <v>134172329</v>
       </c>
-      <c r="E17" s="49">
+      <c r="E17" s="46">
         <v>3450066895</v>
       </c>
-      <c r="F17" s="48" t="s">
+      <c r="F17" s="12" t="s">
         <v>38</v>
       </c>
       <c r="G17" s="20" t="s">
@@ -1440,19 +1650,19 @@
       <c r="C18" s="28">
         <v>45908</v>
       </c>
-      <c r="D18" s="53">
+      <c r="D18" s="25">
         <v>134200564</v>
       </c>
-      <c r="E18" s="49">
+      <c r="E18" s="46">
         <v>3450068424</v>
       </c>
-      <c r="F18" s="48" t="s">
+      <c r="F18" s="12" t="s">
         <v>39</v>
       </c>
       <c r="G18" s="20" t="s">
         <v>21</v>
       </c>
-      <c r="H18" s="55" t="s">
+      <c r="H18" s="9" t="s">
         <v>40</v>
       </c>
       <c r="I18" s="27">
@@ -1469,13 +1679,13 @@
       <c r="C19" s="28">
         <v>45908</v>
       </c>
-      <c r="D19" s="53">
+      <c r="D19" s="25">
         <v>134185921</v>
       </c>
-      <c r="E19" s="49">
+      <c r="E19" s="46">
         <v>3450067665</v>
       </c>
-      <c r="F19" s="48" t="s">
+      <c r="F19" s="12" t="s">
         <v>41</v>
       </c>
       <c r="G19" s="20" t="s">
@@ -1498,13 +1708,13 @@
       <c r="C20" s="28">
         <v>45908</v>
       </c>
-      <c r="D20" s="53">
+      <c r="D20" s="25">
         <v>134186694</v>
       </c>
-      <c r="E20" s="49">
+      <c r="E20" s="46">
         <v>3450067049</v>
       </c>
-      <c r="F20" s="48" t="s">
+      <c r="F20" s="12" t="s">
         <v>42</v>
       </c>
       <c r="G20" s="20" t="s">
@@ -1527,13 +1737,13 @@
       <c r="C21" s="28">
         <v>45908</v>
       </c>
-      <c r="D21" s="53">
+      <c r="D21" s="25">
         <v>134188321</v>
       </c>
-      <c r="E21" s="49">
+      <c r="E21" s="46">
         <v>3450067720</v>
       </c>
-      <c r="F21" s="48" t="s">
+      <c r="F21" s="12" t="s">
         <v>43</v>
       </c>
       <c r="G21" s="20" t="s">
@@ -1556,13 +1766,13 @@
       <c r="C22" s="28">
         <v>45908</v>
       </c>
-      <c r="D22" s="53">
+      <c r="D22" s="25">
         <v>134190841</v>
       </c>
-      <c r="E22" s="49">
+      <c r="E22" s="46">
         <v>3450067808</v>
       </c>
-      <c r="F22" s="48" t="s">
+      <c r="F22" s="12" t="s">
         <v>44</v>
       </c>
       <c r="G22" s="20" t="s">
@@ -1585,13 +1795,13 @@
       <c r="C23" s="28">
         <v>45908</v>
       </c>
-      <c r="D23" s="53">
+      <c r="D23" s="25">
         <v>134191494</v>
       </c>
-      <c r="E23" s="49">
+      <c r="E23" s="46">
         <v>3450067852</v>
       </c>
-      <c r="F23" s="48" t="s">
+      <c r="F23" s="12" t="s">
         <v>45</v>
       </c>
       <c r="G23" s="20" t="s">
@@ -1614,13 +1824,13 @@
       <c r="C24" s="28">
         <v>45908</v>
       </c>
-      <c r="D24" s="53">
+      <c r="D24" s="25">
         <v>134191741</v>
       </c>
-      <c r="E24" s="49">
+      <c r="E24" s="46">
         <v>3450067874</v>
       </c>
-      <c r="F24" s="48" t="s">
+      <c r="F24" s="12" t="s">
         <v>46</v>
       </c>
       <c r="G24" s="20" t="s">
@@ -1643,13 +1853,13 @@
       <c r="C25" s="28">
         <v>45908</v>
       </c>
-      <c r="D25" s="53">
+      <c r="D25" s="25">
         <v>134192757</v>
       </c>
-      <c r="E25" s="49">
+      <c r="E25" s="46">
         <v>3450066378</v>
       </c>
-      <c r="F25" s="48" t="s">
+      <c r="F25" s="12" t="s">
         <v>47</v>
       </c>
       <c r="G25" s="20" t="s">
@@ -1672,13 +1882,13 @@
       <c r="C26" s="28">
         <v>45908</v>
       </c>
-      <c r="D26" s="53">
+      <c r="D26" s="25">
         <v>134195357</v>
       </c>
-      <c r="E26" s="49">
+      <c r="E26" s="46">
         <v>3450068083</v>
       </c>
-      <c r="F26" s="48" t="s">
+      <c r="F26" s="12" t="s">
         <v>48</v>
       </c>
       <c r="G26" s="20" t="s">
@@ -1701,13 +1911,13 @@
       <c r="C27" s="28">
         <v>45908</v>
       </c>
-      <c r="D27" s="53">
+      <c r="D27" s="25">
         <v>134197529</v>
       </c>
-      <c r="E27" s="49">
+      <c r="E27" s="46">
         <v>3450068303</v>
       </c>
-      <c r="F27" s="48" t="s">
+      <c r="F27" s="12" t="s">
         <v>49</v>
       </c>
       <c r="G27" s="20" t="s">
@@ -1730,13 +1940,13 @@
       <c r="C28" s="28">
         <v>45908</v>
       </c>
-      <c r="D28" s="53">
+      <c r="D28" s="25">
         <v>134197979</v>
       </c>
-      <c r="E28" s="49">
+      <c r="E28" s="46">
         <v>3450068325</v>
       </c>
-      <c r="F28" s="48" t="s">
+      <c r="F28" s="12" t="s">
         <v>50</v>
       </c>
       <c r="G28" s="20" t="s">
@@ -1759,13 +1969,13 @@
       <c r="C29" s="28">
         <v>45908</v>
       </c>
-      <c r="D29" s="53">
+      <c r="D29" s="25">
         <v>134199689</v>
       </c>
-      <c r="E29" s="49">
+      <c r="E29" s="46">
         <v>3450068380</v>
       </c>
-      <c r="F29" s="48" t="s">
+      <c r="F29" s="12" t="s">
         <v>51</v>
       </c>
       <c r="G29" s="20" t="s">
@@ -1788,13 +1998,13 @@
       <c r="C30" s="28">
         <v>45908</v>
       </c>
-      <c r="D30" s="53">
+      <c r="D30" s="25">
         <v>134199896</v>
       </c>
-      <c r="E30" s="49">
+      <c r="E30" s="46">
         <v>3450068402</v>
       </c>
-      <c r="F30" s="48" t="s">
+      <c r="F30" s="12" t="s">
         <v>52</v>
       </c>
       <c r="G30" s="20" t="s">
@@ -1817,13 +2027,13 @@
       <c r="C31" s="28">
         <v>45908</v>
       </c>
-      <c r="D31" s="53">
+      <c r="D31" s="25">
         <v>134200360</v>
       </c>
-      <c r="E31" s="49">
+      <c r="E31" s="46">
         <v>3450068413</v>
       </c>
-      <c r="F31" s="48" t="s">
+      <c r="F31" s="12" t="s">
         <v>53</v>
       </c>
       <c r="G31" s="20" t="s">
@@ -1846,13 +2056,13 @@
       <c r="C32" s="28">
         <v>45908</v>
       </c>
-      <c r="D32" s="53">
+      <c r="D32" s="25">
         <v>134201161</v>
       </c>
-      <c r="E32" s="49">
+      <c r="E32" s="46">
         <v>3450068468</v>
       </c>
-      <c r="F32" s="48" t="s">
+      <c r="F32" s="12" t="s">
         <v>54</v>
       </c>
       <c r="G32" s="20" t="s">
@@ -1875,13 +2085,13 @@
       <c r="C33" s="28">
         <v>45908</v>
       </c>
-      <c r="D33" s="53">
+      <c r="D33" s="25">
         <v>134201314</v>
       </c>
-      <c r="E33" s="49">
+      <c r="E33" s="46">
         <v>3450068490</v>
       </c>
-      <c r="F33" s="48" t="s">
+      <c r="F33" s="12" t="s">
         <v>55</v>
       </c>
       <c r="G33" s="20" t="s">
@@ -1904,13 +2114,13 @@
       <c r="C34" s="28">
         <v>45908</v>
       </c>
-      <c r="D34" s="53">
+      <c r="D34" s="25">
         <v>134201496</v>
       </c>
-      <c r="E34" s="49">
+      <c r="E34" s="46">
         <v>3450068534</v>
       </c>
-      <c r="F34" s="48" t="s">
+      <c r="F34" s="12" t="s">
         <v>54</v>
       </c>
       <c r="G34" s="20" t="s">
@@ -1933,13 +2143,13 @@
       <c r="C35" s="28">
         <v>45908</v>
       </c>
-      <c r="D35" s="53">
+      <c r="D35" s="25">
         <v>134204824</v>
       </c>
-      <c r="E35" s="49">
+      <c r="E35" s="46">
         <v>3450068699</v>
       </c>
-      <c r="F35" s="48" t="s">
+      <c r="F35" s="12" t="s">
         <v>56</v>
       </c>
       <c r="G35" s="20" t="s">
@@ -1962,13 +2172,13 @@
       <c r="C36" s="28">
         <v>45908</v>
       </c>
-      <c r="D36" s="53">
+      <c r="D36" s="25">
         <v>134208669</v>
       </c>
-      <c r="E36" s="49">
+      <c r="E36" s="46">
         <v>3450069029</v>
       </c>
-      <c r="F36" s="48" t="s">
+      <c r="F36" s="12" t="s">
         <v>57</v>
       </c>
       <c r="G36" s="20" t="s">
@@ -1991,13 +2201,13 @@
       <c r="C37" s="28">
         <v>45908</v>
       </c>
-      <c r="D37" s="53">
+      <c r="D37" s="25">
         <v>134209125</v>
       </c>
-      <c r="E37" s="49">
+      <c r="E37" s="46">
         <v>3450069051</v>
       </c>
-      <c r="F37" s="48" t="s">
+      <c r="F37" s="12" t="s">
         <v>58</v>
       </c>
       <c r="G37" s="20" t="s">
@@ -2014,9 +2224,9 @@
       <c r="A38" s="6"/>
       <c r="B38" s="7"/>
       <c r="C38" s="7"/>
-      <c r="D38" s="52"/>
+      <c r="D38" s="48"/>
       <c r="E38" s="18"/>
-      <c r="F38" s="36"/>
+      <c r="F38" s="35"/>
       <c r="G38" s="24"/>
       <c r="H38" s="9"/>
       <c r="I38" s="27"/>
@@ -2224,16 +2434,16 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{FFA17127-7620-4DD9-9061-6C654E2EC5C2}">
-  <dimension ref="A1:I55"/>
+  <dimension ref="A1:I53"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
-    <col min="1" max="1" width="16" customWidth="1"/>
+    <col min="1" max="1" width="9.5703125" customWidth="1"/>
     <col min="2" max="2" width="16.5703125" customWidth="1"/>
     <col min="3" max="3" width="21.5703125" customWidth="1"/>
-    <col min="4" max="4" width="27.7109375" style="17" customWidth="1"/>
+    <col min="4" max="4" width="13.28515625" style="17" customWidth="1"/>
     <col min="5" max="5" width="18.5703125" customWidth="1"/>
     <col min="6" max="6" width="31.5703125" customWidth="1"/>
-    <col min="7" max="7" width="19.7109375" customWidth="1"/>
+    <col min="7" max="7" width="19.7109375" style="76" customWidth="1"/>
     <col min="8" max="8" width="24" customWidth="1"/>
     <col min="9" max="9" width="22.7109375" style="16" customWidth="1"/>
   </cols>
@@ -2257,7 +2467,7 @@
       <c r="F1" s="1" t="s">
         <v>5</v>
       </c>
-      <c r="G1" s="1" t="s">
+      <c r="G1" s="74" t="s">
         <v>6</v>
       </c>
       <c r="H1" s="4" t="s">
@@ -2268,421 +2478,743 @@
       </c>
     </row>
     <row r="2" spans="1:9">
-      <c r="A2" s="6" t="s">
-        <v>9</v>
-      </c>
-      <c r="B2" s="7"/>
-      <c r="C2" s="28"/>
-      <c r="D2" s="25"/>
-      <c r="E2" s="18"/>
-      <c r="F2" s="12"/>
-      <c r="G2" s="20"/>
-      <c r="H2" s="12"/>
+      <c r="A2" s="61" t="s">
+        <v>9</v>
+      </c>
+      <c r="B2" s="62">
+        <v>45908</v>
+      </c>
+      <c r="C2" s="63">
+        <v>45909</v>
+      </c>
+      <c r="D2" s="50" t="s">
+        <v>10</v>
+      </c>
+      <c r="E2" s="51">
+        <v>3450075486</v>
+      </c>
+      <c r="F2" s="52" t="s">
+        <v>59</v>
+      </c>
+      <c r="G2" s="45" t="s">
+        <v>12</v>
+      </c>
+      <c r="H2" s="38" t="s">
+        <v>13</v>
+      </c>
       <c r="I2" s="27"/>
     </row>
     <row r="3" spans="1:9">
-      <c r="A3" s="6" t="s">
-        <v>9</v>
-      </c>
-      <c r="B3" s="7"/>
-      <c r="C3" s="28"/>
-      <c r="D3" s="25"/>
-      <c r="E3" s="18"/>
-      <c r="F3" s="12"/>
-      <c r="G3" s="20"/>
-      <c r="H3" s="9"/>
+      <c r="A3" s="61" t="s">
+        <v>9</v>
+      </c>
+      <c r="B3" s="62">
+        <v>45908</v>
+      </c>
+      <c r="C3" s="63">
+        <v>45909</v>
+      </c>
+      <c r="D3" s="50" t="s">
+        <v>10</v>
+      </c>
+      <c r="E3" s="51">
+        <v>3450075190</v>
+      </c>
+      <c r="F3" s="40" t="s">
+        <v>60</v>
+      </c>
+      <c r="G3" s="45" t="s">
+        <v>12</v>
+      </c>
+      <c r="H3" s="38" t="s">
+        <v>13</v>
+      </c>
       <c r="I3" s="27"/>
     </row>
     <row r="4" spans="1:9">
-      <c r="A4" s="6" t="s">
-        <v>9</v>
-      </c>
-      <c r="B4" s="7"/>
-      <c r="C4" s="28"/>
-      <c r="D4" s="25"/>
-      <c r="E4" s="18"/>
-      <c r="F4" s="12"/>
-      <c r="G4" s="20"/>
-      <c r="H4" s="9"/>
-      <c r="I4" s="27"/>
+      <c r="A4" s="61" t="s">
+        <v>9</v>
+      </c>
+      <c r="B4" s="62">
+        <v>45905</v>
+      </c>
+      <c r="C4" s="63">
+        <v>45909</v>
+      </c>
+      <c r="D4" s="53" t="s">
+        <v>10</v>
+      </c>
+      <c r="E4" s="54">
+        <v>3450074430</v>
+      </c>
+      <c r="F4" s="55" t="s">
+        <v>61</v>
+      </c>
+      <c r="G4" s="45" t="s">
+        <v>12</v>
+      </c>
+      <c r="H4" s="38" t="s">
+        <v>62</v>
+      </c>
+      <c r="I4" s="9"/>
     </row>
     <row r="5" spans="1:9">
-      <c r="A5" s="6" t="s">
-        <v>9</v>
-      </c>
-      <c r="B5" s="7"/>
-      <c r="C5" s="28"/>
-      <c r="D5" s="25"/>
-      <c r="E5" s="18"/>
-      <c r="F5" s="12"/>
-      <c r="G5" s="20"/>
-      <c r="H5" s="9"/>
-      <c r="I5" s="27"/>
+      <c r="A5" s="64" t="s">
+        <v>9</v>
+      </c>
+      <c r="B5" s="62">
+        <v>45898</v>
+      </c>
+      <c r="C5" s="63">
+        <v>45909</v>
+      </c>
+      <c r="D5" s="56">
+        <v>134216123</v>
+      </c>
+      <c r="E5" s="65">
+        <v>3450069040</v>
+      </c>
+      <c r="F5" s="57" t="s">
+        <v>63</v>
+      </c>
+      <c r="G5" s="45" t="s">
+        <v>16</v>
+      </c>
+      <c r="H5" s="38" t="s">
+        <v>64</v>
+      </c>
+      <c r="I5" s="27">
+        <v>45898</v>
+      </c>
     </row>
     <row r="6" spans="1:9">
-      <c r="A6" s="6" t="s">
-        <v>9</v>
-      </c>
-      <c r="B6" s="7"/>
-      <c r="C6" s="28"/>
-      <c r="D6" s="25"/>
-      <c r="E6" s="18"/>
-      <c r="F6" s="12"/>
-      <c r="G6" s="20"/>
-      <c r="H6" s="22"/>
-      <c r="I6" s="27"/>
+      <c r="A6" s="64" t="s">
+        <v>9</v>
+      </c>
+      <c r="B6" s="62">
+        <v>45898</v>
+      </c>
+      <c r="C6" s="63">
+        <v>45909</v>
+      </c>
+      <c r="D6" s="56">
+        <v>134216628</v>
+      </c>
+      <c r="E6" s="65">
+        <v>3450068831</v>
+      </c>
+      <c r="F6" s="57" t="s">
+        <v>65</v>
+      </c>
+      <c r="G6" s="45" t="s">
+        <v>21</v>
+      </c>
+      <c r="H6" s="72" t="s">
+        <v>66</v>
+      </c>
+      <c r="I6" s="27">
+        <v>45898</v>
+      </c>
     </row>
     <row r="7" spans="1:9">
-      <c r="A7" s="6" t="s">
-        <v>9</v>
-      </c>
-      <c r="B7" s="7"/>
-      <c r="C7" s="28"/>
-      <c r="D7" s="25"/>
-      <c r="E7" s="18"/>
-      <c r="F7" s="12"/>
-      <c r="G7" s="26"/>
-      <c r="H7" s="31"/>
-      <c r="I7" s="27"/>
+      <c r="A7" s="64" t="s">
+        <v>9</v>
+      </c>
+      <c r="B7" s="62">
+        <v>45929</v>
+      </c>
+      <c r="C7" s="63">
+        <v>45909</v>
+      </c>
+      <c r="D7" s="56">
+        <v>134230678</v>
+      </c>
+      <c r="E7" s="65">
+        <v>3450070118</v>
+      </c>
+      <c r="F7" s="57" t="s">
+        <v>67</v>
+      </c>
+      <c r="G7" s="44" t="s">
+        <v>68</v>
+      </c>
+      <c r="H7" s="73" t="s">
+        <v>69</v>
+      </c>
+      <c r="I7" s="27">
+        <v>45903</v>
+      </c>
     </row>
     <row r="8" spans="1:9">
-      <c r="A8" s="6" t="s">
-        <v>9</v>
-      </c>
-      <c r="B8" s="7"/>
-      <c r="C8" s="28"/>
-      <c r="D8" s="25"/>
-      <c r="E8" s="18"/>
-      <c r="F8" s="12"/>
-      <c r="G8" s="26"/>
-      <c r="H8" s="12"/>
-      <c r="I8" s="27"/>
+      <c r="A8" s="64" t="s">
+        <v>9</v>
+      </c>
+      <c r="B8" s="62">
+        <v>45903</v>
+      </c>
+      <c r="C8" s="63">
+        <v>45909</v>
+      </c>
+      <c r="D8" s="56">
+        <v>134267077</v>
+      </c>
+      <c r="E8" s="65">
+        <v>3450072000</v>
+      </c>
+      <c r="F8" s="77" t="s">
+        <v>70</v>
+      </c>
+      <c r="G8" s="44" t="s">
+        <v>24</v>
+      </c>
+      <c r="H8" s="58" t="s">
+        <v>71</v>
+      </c>
+      <c r="I8" s="27">
+        <v>45905</v>
+      </c>
     </row>
     <row r="9" spans="1:9">
-      <c r="A9" s="6" t="s">
-        <v>9</v>
-      </c>
-      <c r="B9" s="7"/>
-      <c r="C9" s="28"/>
-      <c r="D9" s="25"/>
-      <c r="E9" s="18"/>
-      <c r="F9" s="12"/>
-      <c r="G9" s="20"/>
-      <c r="H9" s="15"/>
-      <c r="I9" s="27"/>
+      <c r="A9" s="64" t="s">
+        <v>9</v>
+      </c>
+      <c r="B9" s="62">
+        <v>45926</v>
+      </c>
+      <c r="C9" s="63">
+        <v>45909</v>
+      </c>
+      <c r="D9" s="56">
+        <v>134150028</v>
+      </c>
+      <c r="E9" s="65">
+        <v>3450065707</v>
+      </c>
+      <c r="F9" s="57" t="s">
+        <v>72</v>
+      </c>
+      <c r="G9" s="45" t="s">
+        <v>68</v>
+      </c>
+      <c r="H9" s="71" t="s">
+        <v>73</v>
+      </c>
+      <c r="I9" s="27">
+        <v>45901</v>
+      </c>
     </row>
     <row r="10" spans="1:9">
-      <c r="A10" s="6" t="s">
-        <v>9</v>
-      </c>
-      <c r="B10" s="7"/>
-      <c r="C10" s="28"/>
-      <c r="D10" s="25"/>
-      <c r="E10" s="18"/>
-      <c r="F10" s="12"/>
-      <c r="G10" s="20"/>
-      <c r="H10" s="9"/>
-      <c r="I10" s="27"/>
+      <c r="A10" s="64" t="s">
+        <v>9</v>
+      </c>
+      <c r="B10" s="62">
+        <v>45896</v>
+      </c>
+      <c r="C10" s="63">
+        <v>45909</v>
+      </c>
+      <c r="D10" s="56">
+        <v>134142970</v>
+      </c>
+      <c r="E10" s="65">
+        <v>3450065190</v>
+      </c>
+      <c r="F10" s="57" t="s">
+        <v>74</v>
+      </c>
+      <c r="G10" s="45" t="s">
+        <v>68</v>
+      </c>
+      <c r="H10" s="71" t="s">
+        <v>75</v>
+      </c>
+      <c r="I10" s="27">
+        <v>45896</v>
+      </c>
     </row>
     <row r="11" spans="1:9">
-      <c r="A11" s="6" t="s">
-        <v>9</v>
-      </c>
-      <c r="B11" s="7"/>
-      <c r="C11" s="28"/>
-      <c r="D11" s="25"/>
-      <c r="E11" s="18"/>
-      <c r="F11" s="12"/>
-      <c r="G11" s="20"/>
-      <c r="H11" s="9"/>
-      <c r="I11" s="27"/>
+      <c r="A11" s="64" t="s">
+        <v>9</v>
+      </c>
+      <c r="B11" s="62">
+        <v>45901</v>
+      </c>
+      <c r="C11" s="63">
+        <v>45909</v>
+      </c>
+      <c r="D11" s="56">
+        <v>134218656</v>
+      </c>
+      <c r="E11" s="65">
+        <v>3450069282</v>
+      </c>
+      <c r="F11" s="57" t="s">
+        <v>76</v>
+      </c>
+      <c r="G11" s="45" t="s">
+        <v>21</v>
+      </c>
+      <c r="H11" s="71" t="s">
+        <v>77</v>
+      </c>
+      <c r="I11" s="27">
+        <v>45901</v>
+      </c>
     </row>
     <row r="12" spans="1:9">
-      <c r="A12" s="6" t="s">
-        <v>9</v>
-      </c>
-      <c r="B12" s="7"/>
-      <c r="C12" s="28"/>
-      <c r="D12" s="25"/>
-      <c r="E12" s="18"/>
-      <c r="F12" s="12"/>
-      <c r="G12" s="20"/>
-      <c r="H12" s="9"/>
-      <c r="I12" s="27"/>
+      <c r="A12" s="64" t="s">
+        <v>9</v>
+      </c>
+      <c r="B12" s="62">
+        <v>45901</v>
+      </c>
+      <c r="C12" s="63">
+        <v>45909</v>
+      </c>
+      <c r="D12" s="56">
+        <v>134217366</v>
+      </c>
+      <c r="E12" s="65">
+        <v>3450069249</v>
+      </c>
+      <c r="F12" s="57" t="s">
+        <v>78</v>
+      </c>
+      <c r="G12" s="45" t="s">
+        <v>21</v>
+      </c>
+      <c r="H12" s="71" t="s">
+        <v>79</v>
+      </c>
+      <c r="I12" s="27">
+        <v>45901</v>
+      </c>
     </row>
     <row r="13" spans="1:9">
-      <c r="A13" s="6" t="s">
-        <v>9</v>
-      </c>
-      <c r="B13" s="7"/>
-      <c r="C13" s="28"/>
-      <c r="D13" s="25"/>
-      <c r="E13" s="18"/>
-      <c r="F13" s="12"/>
-      <c r="G13" s="20"/>
-      <c r="H13" s="9"/>
-      <c r="I13" s="27"/>
+      <c r="A13" s="64" t="s">
+        <v>9</v>
+      </c>
+      <c r="B13" s="62">
+        <v>45898</v>
+      </c>
+      <c r="C13" s="63">
+        <v>45909</v>
+      </c>
+      <c r="D13" s="56">
+        <v>134221682</v>
+      </c>
+      <c r="E13" s="65">
+        <v>3450067962</v>
+      </c>
+      <c r="F13" s="57" t="s">
+        <v>80</v>
+      </c>
+      <c r="G13" s="45" t="s">
+        <v>21</v>
+      </c>
+      <c r="H13" s="71" t="s">
+        <v>81</v>
+      </c>
+      <c r="I13" s="27">
+        <v>45898</v>
+      </c>
     </row>
     <row r="14" spans="1:9">
-      <c r="A14" s="6" t="s">
-        <v>9</v>
-      </c>
-      <c r="B14" s="7"/>
-      <c r="C14" s="28"/>
-      <c r="D14" s="25"/>
-      <c r="E14" s="18"/>
-      <c r="F14" s="12"/>
-      <c r="G14" s="20"/>
-      <c r="H14" s="9"/>
-      <c r="I14" s="27"/>
+      <c r="A14" s="64" t="s">
+        <v>9</v>
+      </c>
+      <c r="B14" s="62">
+        <v>45903</v>
+      </c>
+      <c r="C14" s="63">
+        <v>45909</v>
+      </c>
+      <c r="D14" s="56">
+        <v>134259586</v>
+      </c>
+      <c r="E14" s="65">
+        <v>3450071460</v>
+      </c>
+      <c r="F14" s="57" t="s">
+        <v>82</v>
+      </c>
+      <c r="G14" s="45" t="s">
+        <v>31</v>
+      </c>
+      <c r="H14" s="71" t="s">
+        <v>32</v>
+      </c>
+      <c r="I14" s="27">
+        <v>45903</v>
+      </c>
     </row>
     <row r="15" spans="1:9">
-      <c r="A15" s="6" t="s">
-        <v>9</v>
-      </c>
-      <c r="B15" s="7"/>
-      <c r="C15" s="28"/>
-      <c r="D15" s="25"/>
-      <c r="E15" s="18"/>
-      <c r="F15" s="12"/>
-      <c r="G15" s="20"/>
-      <c r="H15" s="9"/>
-      <c r="I15" s="27"/>
+      <c r="A15" s="64" t="s">
+        <v>9</v>
+      </c>
+      <c r="B15" s="62">
+        <v>45901</v>
+      </c>
+      <c r="C15" s="63">
+        <v>45909</v>
+      </c>
+      <c r="D15" s="56">
+        <v>134220631</v>
+      </c>
+      <c r="E15" s="65">
+        <v>3450069436</v>
+      </c>
+      <c r="F15" s="57" t="s">
+        <v>83</v>
+      </c>
+      <c r="G15" s="45" t="s">
+        <v>16</v>
+      </c>
+      <c r="H15" s="38" t="s">
+        <v>64</v>
+      </c>
+      <c r="I15" s="27">
+        <v>45901</v>
+      </c>
     </row>
     <row r="16" spans="1:9">
-      <c r="A16" s="6" t="s">
-        <v>9</v>
-      </c>
-      <c r="B16" s="7"/>
-      <c r="C16" s="28"/>
-      <c r="D16" s="25"/>
-      <c r="E16" s="18"/>
-      <c r="F16" s="12"/>
-      <c r="G16" s="20"/>
-      <c r="H16" s="9"/>
-      <c r="I16" s="27"/>
+      <c r="A16" s="64" t="s">
+        <v>9</v>
+      </c>
+      <c r="B16" s="62">
+        <v>45898</v>
+      </c>
+      <c r="C16" s="63">
+        <v>45909</v>
+      </c>
+      <c r="D16" s="56">
+        <v>134217300</v>
+      </c>
+      <c r="E16" s="65">
+        <v>3450068820</v>
+      </c>
+      <c r="F16" s="57" t="s">
+        <v>84</v>
+      </c>
+      <c r="G16" s="45" t="s">
+        <v>16</v>
+      </c>
+      <c r="H16" s="38" t="s">
+        <v>64</v>
+      </c>
+      <c r="I16" s="27">
+        <v>45898</v>
+      </c>
     </row>
     <row r="17" spans="1:9">
-      <c r="A17" s="6" t="s">
-        <v>9</v>
-      </c>
-      <c r="B17" s="7"/>
-      <c r="C17" s="28"/>
-      <c r="D17" s="25"/>
-      <c r="E17" s="18"/>
-      <c r="F17" s="12"/>
-      <c r="G17" s="20"/>
-      <c r="H17" s="9"/>
-      <c r="I17" s="27"/>
+      <c r="A17" s="64" t="s">
+        <v>9</v>
+      </c>
+      <c r="B17" s="62">
+        <v>45898</v>
+      </c>
+      <c r="C17" s="63">
+        <v>45909</v>
+      </c>
+      <c r="D17" s="56">
+        <v>134221526</v>
+      </c>
+      <c r="E17" s="65">
+        <v>3450068017</v>
+      </c>
+      <c r="F17" s="57" t="s">
+        <v>85</v>
+      </c>
+      <c r="G17" s="45" t="s">
+        <v>16</v>
+      </c>
+      <c r="H17" s="38" t="s">
+        <v>64</v>
+      </c>
+      <c r="I17" s="27">
+        <v>45898</v>
+      </c>
     </row>
     <row r="18" spans="1:9">
-      <c r="A18" s="6"/>
-      <c r="B18" s="7"/>
-      <c r="C18" s="28"/>
-      <c r="D18" s="25"/>
-      <c r="E18" s="18"/>
-      <c r="F18" s="12"/>
-      <c r="G18" s="20"/>
-      <c r="H18" s="9"/>
-      <c r="I18" s="27"/>
+      <c r="A18" s="64" t="s">
+        <v>9</v>
+      </c>
+      <c r="B18" s="62">
+        <v>45903</v>
+      </c>
+      <c r="C18" s="63">
+        <v>45909</v>
+      </c>
+      <c r="D18" s="56">
+        <v>134275478</v>
+      </c>
+      <c r="E18" s="65">
+        <v>3450072615</v>
+      </c>
+      <c r="F18" s="57" t="s">
+        <v>86</v>
+      </c>
+      <c r="G18" s="45" t="s">
+        <v>21</v>
+      </c>
+      <c r="H18" s="71" t="s">
+        <v>87</v>
+      </c>
+      <c r="I18" s="27">
+        <v>45903</v>
+      </c>
     </row>
     <row r="19" spans="1:9">
-      <c r="A19" s="6"/>
-      <c r="B19" s="7"/>
-      <c r="C19" s="28"/>
-      <c r="D19" s="25"/>
-      <c r="E19" s="18"/>
-      <c r="F19" s="12"/>
-      <c r="G19" s="20"/>
-      <c r="H19" s="9"/>
-      <c r="I19" s="27"/>
+      <c r="A19" s="64" t="s">
+        <v>9</v>
+      </c>
+      <c r="B19" s="62">
+        <v>45901</v>
+      </c>
+      <c r="C19" s="63">
+        <v>45909</v>
+      </c>
+      <c r="D19" s="56">
+        <v>134224096</v>
+      </c>
+      <c r="E19" s="65">
+        <v>3450069722</v>
+      </c>
+      <c r="F19" s="57" t="s">
+        <v>88</v>
+      </c>
+      <c r="G19" s="45" t="s">
+        <v>16</v>
+      </c>
+      <c r="H19" s="38" t="s">
+        <v>64</v>
+      </c>
+      <c r="I19" s="27">
+        <v>45901</v>
+      </c>
     </row>
     <row r="20" spans="1:9">
-      <c r="A20" s="6"/>
-      <c r="B20" s="7"/>
-      <c r="C20" s="28"/>
-      <c r="D20" s="25"/>
-      <c r="E20" s="18"/>
-      <c r="F20" s="12"/>
-      <c r="G20" s="20"/>
-      <c r="H20" s="9"/>
-      <c r="I20" s="27"/>
+      <c r="A20" s="64" t="s">
+        <v>9</v>
+      </c>
+      <c r="B20" s="62">
+        <v>45901</v>
+      </c>
+      <c r="C20" s="63">
+        <v>45909</v>
+      </c>
+      <c r="D20" s="56">
+        <v>134227978</v>
+      </c>
+      <c r="E20" s="65">
+        <v>3450069986</v>
+      </c>
+      <c r="F20" s="57" t="s">
+        <v>89</v>
+      </c>
+      <c r="G20" s="45" t="s">
+        <v>16</v>
+      </c>
+      <c r="H20" s="38" t="s">
+        <v>64</v>
+      </c>
+      <c r="I20" s="27">
+        <v>45901</v>
+      </c>
     </row>
     <row r="21" spans="1:9">
-      <c r="A21" s="6"/>
-      <c r="B21" s="7"/>
-      <c r="C21" s="28"/>
-      <c r="D21" s="25"/>
-      <c r="E21" s="18"/>
-      <c r="F21" s="12"/>
-      <c r="G21" s="20"/>
-      <c r="H21" s="9"/>
-      <c r="I21" s="27"/>
+      <c r="A21" s="64" t="s">
+        <v>9</v>
+      </c>
+      <c r="B21" s="62">
+        <v>45901</v>
+      </c>
+      <c r="C21" s="63">
+        <v>45909</v>
+      </c>
+      <c r="D21" s="56">
+        <v>134231864</v>
+      </c>
+      <c r="E21" s="65">
+        <v>3450070173</v>
+      </c>
+      <c r="F21" s="57" t="s">
+        <v>90</v>
+      </c>
+      <c r="G21" s="45" t="s">
+        <v>16</v>
+      </c>
+      <c r="H21" s="38" t="s">
+        <v>64</v>
+      </c>
+      <c r="I21" s="27">
+        <v>45901</v>
+      </c>
     </row>
     <row r="22" spans="1:9">
-      <c r="A22" s="6"/>
-      <c r="B22" s="7"/>
-      <c r="C22" s="28"/>
-      <c r="D22" s="25"/>
-      <c r="E22" s="18"/>
-      <c r="F22" s="12"/>
-      <c r="G22" s="20"/>
-      <c r="H22" s="9"/>
+      <c r="A22" s="64"/>
+      <c r="B22" s="62"/>
+      <c r="C22" s="63"/>
+      <c r="D22" s="50"/>
+      <c r="E22" s="65"/>
+      <c r="F22" s="58"/>
+      <c r="G22" s="45"/>
+      <c r="H22" s="38"/>
       <c r="I22" s="27"/>
     </row>
     <row r="23" spans="1:9">
-      <c r="A23" s="6"/>
-      <c r="B23" s="7"/>
-      <c r="C23" s="28"/>
-      <c r="D23" s="25"/>
-      <c r="E23" s="18"/>
-      <c r="F23" s="12"/>
-      <c r="G23" s="20"/>
-      <c r="H23" s="9"/>
+      <c r="A23" s="64"/>
+      <c r="B23" s="62"/>
+      <c r="C23" s="63"/>
+      <c r="D23" s="50"/>
+      <c r="E23" s="65"/>
+      <c r="F23" s="58"/>
+      <c r="G23" s="45"/>
+      <c r="H23" s="38"/>
       <c r="I23" s="27"/>
     </row>
     <row r="24" spans="1:9">
-      <c r="A24" s="6"/>
-      <c r="B24" s="7"/>
-      <c r="C24" s="28"/>
-      <c r="D24" s="25"/>
-      <c r="E24" s="18"/>
-      <c r="F24" s="12"/>
-      <c r="G24" s="20"/>
-      <c r="H24" s="9"/>
+      <c r="A24" s="64"/>
+      <c r="B24" s="62"/>
+      <c r="C24" s="63"/>
+      <c r="D24" s="50"/>
+      <c r="E24" s="65"/>
+      <c r="F24" s="58"/>
+      <c r="G24" s="45"/>
+      <c r="H24" s="66"/>
       <c r="I24" s="27"/>
     </row>
     <row r="25" spans="1:9">
-      <c r="A25" s="6"/>
-      <c r="B25" s="7"/>
-      <c r="C25" s="28"/>
-      <c r="D25" s="25"/>
-      <c r="E25" s="18"/>
-      <c r="F25" s="12"/>
-      <c r="G25" s="20"/>
-      <c r="H25" s="9"/>
+      <c r="A25" s="64"/>
+      <c r="B25" s="62"/>
+      <c r="C25" s="63"/>
+      <c r="D25" s="50"/>
+      <c r="E25" s="65"/>
+      <c r="F25" s="58"/>
+      <c r="G25" s="45"/>
+      <c r="H25" s="38"/>
       <c r="I25" s="27"/>
     </row>
     <row r="26" spans="1:9">
-      <c r="A26" s="6"/>
-      <c r="B26" s="7"/>
-      <c r="C26" s="28"/>
-      <c r="D26" s="25"/>
-      <c r="E26" s="18"/>
-      <c r="F26" s="12"/>
-      <c r="G26" s="20"/>
-      <c r="H26" s="32"/>
+      <c r="A26" s="64"/>
+      <c r="B26" s="62"/>
+      <c r="C26" s="63"/>
+      <c r="D26" s="50"/>
+      <c r="E26" s="65"/>
+      <c r="F26" s="58"/>
+      <c r="G26" s="45"/>
+      <c r="H26" s="38"/>
       <c r="I26" s="27"/>
     </row>
     <row r="27" spans="1:9">
-      <c r="A27" s="6"/>
-      <c r="B27" s="7"/>
-      <c r="C27" s="28"/>
-      <c r="D27" s="25"/>
-      <c r="E27" s="18"/>
-      <c r="F27" s="12"/>
-      <c r="G27" s="20"/>
-      <c r="H27" s="9"/>
+      <c r="A27" s="64"/>
+      <c r="B27" s="62"/>
+      <c r="C27" s="63"/>
+      <c r="D27" s="50"/>
+      <c r="E27" s="65"/>
+      <c r="F27" s="58"/>
+      <c r="G27" s="45"/>
+      <c r="H27" s="38"/>
       <c r="I27" s="27"/>
     </row>
     <row r="28" spans="1:9">
-      <c r="A28" s="6"/>
-      <c r="B28" s="7"/>
-      <c r="C28" s="28"/>
-      <c r="D28" s="25"/>
-      <c r="E28" s="18"/>
-      <c r="F28" s="12"/>
-      <c r="G28" s="20"/>
-      <c r="H28" s="9"/>
+      <c r="A28" s="64"/>
+      <c r="B28" s="62"/>
+      <c r="C28" s="63"/>
+      <c r="D28" s="50"/>
+      <c r="E28" s="65"/>
+      <c r="F28" s="58"/>
+      <c r="G28" s="45"/>
+      <c r="H28" s="38"/>
       <c r="I28" s="27"/>
     </row>
     <row r="29" spans="1:9">
-      <c r="A29" s="6"/>
-      <c r="B29" s="7"/>
-      <c r="C29" s="28"/>
-      <c r="D29" s="25"/>
-      <c r="E29" s="18"/>
-      <c r="F29" s="12"/>
-      <c r="G29" s="20"/>
-      <c r="H29" s="9"/>
+      <c r="A29" s="64"/>
+      <c r="B29" s="62"/>
+      <c r="C29" s="63"/>
+      <c r="D29" s="50"/>
+      <c r="E29" s="65"/>
+      <c r="F29" s="58"/>
+      <c r="G29" s="45"/>
+      <c r="H29" s="38"/>
       <c r="I29" s="27"/>
     </row>
     <row r="30" spans="1:9">
-      <c r="A30" s="6"/>
-      <c r="B30" s="7"/>
-      <c r="C30" s="28"/>
-      <c r="D30" s="25"/>
-      <c r="E30" s="18"/>
-      <c r="F30" s="12"/>
-      <c r="G30" s="20"/>
-      <c r="H30" s="9"/>
+      <c r="A30" s="64"/>
+      <c r="B30" s="62"/>
+      <c r="C30" s="63"/>
+      <c r="D30" s="50"/>
+      <c r="E30" s="65"/>
+      <c r="F30" s="58"/>
+      <c r="G30" s="45"/>
+      <c r="H30" s="38"/>
       <c r="I30" s="27"/>
     </row>
     <row r="31" spans="1:9">
-      <c r="A31" s="6"/>
-      <c r="B31" s="7"/>
-      <c r="C31" s="28"/>
-      <c r="D31" s="25"/>
-      <c r="E31" s="18"/>
-      <c r="F31" s="12"/>
-      <c r="G31" s="20"/>
-      <c r="H31" s="9"/>
+      <c r="A31" s="64"/>
+      <c r="B31" s="62"/>
+      <c r="C31" s="63"/>
+      <c r="D31" s="59"/>
+      <c r="E31" s="67"/>
+      <c r="F31" s="60"/>
+      <c r="G31" s="45"/>
+      <c r="H31" s="38"/>
       <c r="I31" s="27"/>
     </row>
     <row r="32" spans="1:9">
-      <c r="A32" s="6"/>
-      <c r="B32" s="7"/>
-      <c r="C32" s="28"/>
-      <c r="D32" s="25"/>
-      <c r="E32" s="18"/>
-      <c r="F32" s="12"/>
-      <c r="G32" s="20"/>
-      <c r="H32" s="9"/>
+      <c r="A32" s="64"/>
+      <c r="B32" s="68"/>
+      <c r="C32" s="62"/>
+      <c r="D32" s="69"/>
+      <c r="E32" s="69"/>
+      <c r="F32" s="70"/>
+      <c r="G32" s="75"/>
+      <c r="H32" s="38"/>
       <c r="I32" s="27"/>
     </row>
     <row r="33" spans="1:9">
-      <c r="A33" s="6"/>
-      <c r="B33" s="7"/>
-      <c r="C33" s="28"/>
-      <c r="D33" s="25"/>
-      <c r="E33" s="18"/>
-      <c r="F33" s="12"/>
-      <c r="G33" s="20"/>
-      <c r="H33" s="9"/>
+      <c r="A33" s="64"/>
+      <c r="B33" s="68"/>
+      <c r="C33" s="62"/>
+      <c r="D33" s="68"/>
+      <c r="E33" s="68"/>
+      <c r="F33" s="71"/>
+      <c r="G33" s="75"/>
+      <c r="H33" s="38"/>
       <c r="I33" s="27"/>
     </row>
     <row r="34" spans="1:9">
-      <c r="A34" s="6"/>
-      <c r="B34" s="8"/>
-      <c r="C34" s="7"/>
-      <c r="D34" s="23"/>
-      <c r="E34" s="23"/>
-      <c r="F34" s="15"/>
-      <c r="G34" s="6"/>
-      <c r="H34" s="9"/>
+      <c r="A34" s="61"/>
+      <c r="B34" s="68"/>
+      <c r="C34" s="62"/>
+      <c r="D34" s="68"/>
+      <c r="E34" s="68"/>
+      <c r="F34" s="38"/>
+      <c r="G34" s="75"/>
+      <c r="H34" s="38"/>
       <c r="I34" s="27"/>
     </row>
     <row r="35" spans="1:9">
-      <c r="A35" s="6"/>
-      <c r="B35" s="8"/>
-      <c r="C35" s="7"/>
-      <c r="D35" s="8"/>
-      <c r="E35" s="8"/>
-      <c r="F35" s="9"/>
-      <c r="G35" s="6"/>
-      <c r="H35" s="9"/>
-      <c r="I35" s="27"/>
+      <c r="A35" s="61"/>
+      <c r="B35" s="68"/>
+      <c r="C35" s="62"/>
+      <c r="D35" s="68"/>
+      <c r="E35" s="68"/>
+      <c r="F35" s="38"/>
+      <c r="G35" s="75"/>
+      <c r="H35" s="38"/>
+      <c r="I35"/>
     </row>
     <row r="36" spans="1:9">
-      <c r="A36" s="6"/>
-      <c r="B36" s="8"/>
-      <c r="C36" s="7"/>
-      <c r="D36" s="8"/>
-      <c r="E36" s="8"/>
-      <c r="F36" s="9"/>
-      <c r="G36" s="6"/>
-      <c r="H36" s="9"/>
-      <c r="I36" s="27"/>
+      <c r="A36" s="61"/>
+      <c r="B36" s="68"/>
+      <c r="C36" s="62"/>
+      <c r="D36" s="68"/>
+      <c r="E36" s="68"/>
+      <c r="F36" s="38"/>
+      <c r="G36" s="75"/>
+      <c r="H36" s="38"/>
+      <c r="I36"/>
     </row>
     <row r="37" spans="1:9">
       <c r="A37" s="6"/>
@@ -2691,7 +3223,7 @@
       <c r="D37" s="8"/>
       <c r="E37" s="8"/>
       <c r="F37" s="9"/>
-      <c r="G37" s="6"/>
+      <c r="G37" s="33"/>
       <c r="H37" s="9"/>
       <c r="I37"/>
     </row>
@@ -2702,7 +3234,7 @@
       <c r="D38" s="8"/>
       <c r="E38" s="8"/>
       <c r="F38" s="9"/>
-      <c r="G38" s="6"/>
+      <c r="G38" s="33"/>
       <c r="H38" s="9"/>
       <c r="I38"/>
     </row>
@@ -2713,7 +3245,7 @@
       <c r="D39" s="8"/>
       <c r="E39" s="8"/>
       <c r="F39" s="9"/>
-      <c r="G39" s="6"/>
+      <c r="G39" s="33"/>
       <c r="H39" s="9"/>
       <c r="I39"/>
     </row>
@@ -2724,7 +3256,7 @@
       <c r="D40" s="8"/>
       <c r="E40" s="8"/>
       <c r="F40" s="9"/>
-      <c r="G40" s="6"/>
+      <c r="G40" s="33"/>
       <c r="H40" s="9"/>
       <c r="I40"/>
     </row>
@@ -2735,7 +3267,7 @@
       <c r="D41" s="8"/>
       <c r="E41" s="8"/>
       <c r="F41" s="9"/>
-      <c r="G41" s="6"/>
+      <c r="G41" s="33"/>
       <c r="H41" s="9"/>
       <c r="I41"/>
     </row>
@@ -2746,7 +3278,7 @@
       <c r="D42" s="8"/>
       <c r="E42" s="8"/>
       <c r="F42" s="9"/>
-      <c r="G42" s="6"/>
+      <c r="G42" s="33"/>
       <c r="H42" s="9"/>
       <c r="I42"/>
     </row>
@@ -2757,7 +3289,7 @@
       <c r="D43" s="8"/>
       <c r="E43" s="8"/>
       <c r="F43" s="9"/>
-      <c r="G43" s="6"/>
+      <c r="G43" s="33"/>
       <c r="H43" s="9"/>
       <c r="I43"/>
     </row>
@@ -2768,7 +3300,7 @@
       <c r="D44" s="8"/>
       <c r="E44" s="8"/>
       <c r="F44" s="9"/>
-      <c r="G44" s="6"/>
+      <c r="G44" s="33"/>
       <c r="H44" s="9"/>
       <c r="I44"/>
     </row>
@@ -2779,7 +3311,7 @@
       <c r="D45" s="8"/>
       <c r="E45" s="8"/>
       <c r="F45" s="9"/>
-      <c r="G45" s="6"/>
+      <c r="G45" s="33"/>
       <c r="H45" s="9"/>
       <c r="I45"/>
     </row>
@@ -2790,7 +3322,7 @@
       <c r="D46" s="8"/>
       <c r="E46" s="8"/>
       <c r="F46" s="9"/>
-      <c r="G46" s="6"/>
+      <c r="G46" s="33"/>
       <c r="H46" s="9"/>
       <c r="I46"/>
     </row>
@@ -2801,7 +3333,7 @@
       <c r="D47" s="8"/>
       <c r="E47" s="8"/>
       <c r="F47" s="9"/>
-      <c r="G47" s="6"/>
+      <c r="G47" s="33"/>
       <c r="H47" s="9"/>
       <c r="I47"/>
     </row>
@@ -2812,7 +3344,7 @@
       <c r="D48" s="8"/>
       <c r="E48" s="8"/>
       <c r="F48" s="9"/>
-      <c r="G48" s="6"/>
+      <c r="G48" s="33"/>
       <c r="H48" s="9"/>
       <c r="I48"/>
     </row>
@@ -2823,7 +3355,7 @@
       <c r="D49" s="8"/>
       <c r="E49" s="8"/>
       <c r="F49" s="9"/>
-      <c r="G49" s="6"/>
+      <c r="G49" s="33"/>
       <c r="H49" s="9"/>
       <c r="I49"/>
     </row>
@@ -2834,7 +3366,7 @@
       <c r="D50" s="8"/>
       <c r="E50" s="8"/>
       <c r="F50" s="9"/>
-      <c r="G50" s="6"/>
+      <c r="G50" s="33"/>
       <c r="H50" s="9"/>
       <c r="I50"/>
     </row>
@@ -2845,7 +3377,7 @@
       <c r="D51" s="8"/>
       <c r="E51" s="8"/>
       <c r="F51" s="9"/>
-      <c r="G51" s="6"/>
+      <c r="G51" s="33"/>
       <c r="H51" s="9"/>
       <c r="I51"/>
     </row>
@@ -2856,7 +3388,7 @@
       <c r="D52" s="8"/>
       <c r="E52" s="8"/>
       <c r="F52" s="9"/>
-      <c r="G52" s="6"/>
+      <c r="G52" s="33"/>
       <c r="H52" s="9"/>
       <c r="I52"/>
     </row>
@@ -2867,43 +3399,30 @@
       <c r="D53" s="8"/>
       <c r="E53" s="8"/>
       <c r="F53" s="9"/>
-      <c r="G53" s="6"/>
+      <c r="G53" s="33"/>
       <c r="H53" s="9"/>
       <c r="I53"/>
     </row>
-    <row r="54" spans="1:9">
-      <c r="A54" s="6"/>
-      <c r="B54" s="8"/>
-      <c r="C54" s="7"/>
-      <c r="D54" s="8"/>
-      <c r="E54" s="8"/>
-      <c r="F54" s="9"/>
-      <c r="G54" s="6"/>
-      <c r="H54" s="9"/>
-      <c r="I54"/>
-    </row>
-    <row r="55" spans="1:9">
-      <c r="A55" s="6"/>
-      <c r="B55" s="8"/>
-      <c r="C55" s="7"/>
-      <c r="D55" s="8"/>
-      <c r="E55" s="8"/>
-      <c r="F55" s="9"/>
-      <c r="G55" s="6"/>
-      <c r="H55" s="9"/>
-      <c r="I55"/>
-    </row>
   </sheetData>
   <conditionalFormatting sqref="B1:C1">
-    <cfRule type="notContainsBlanks" priority="2">
+    <cfRule type="notContainsBlanks" priority="6">
       <formula>LEN(TRIM(B1))&gt;0</formula>
     </cfRule>
   </conditionalFormatting>
+  <conditionalFormatting sqref="E2">
+    <cfRule type="duplicateValues" dxfId="2" priority="4"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="E3">
+    <cfRule type="duplicateValues" dxfId="1" priority="3"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="E4">
+    <cfRule type="duplicateValues" dxfId="0" priority="2"/>
+  </conditionalFormatting>
   <dataValidations count="2">
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="A2:A33" xr:uid="{4D257AA8-3FDB-42B7-A450-B3788B0ABB12}">
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="A2:A31" xr:uid="{4D257AA8-3FDB-42B7-A450-B3788B0ABB12}">
       <formula1>$J$2</formula1>
     </dataValidation>
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="G2:G41" xr:uid="{5FAA0C61-6912-46B8-8149-B719594B77CB}">
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="G2:G39" xr:uid="{5FAA0C61-6912-46B8-8149-B719594B77CB}">
       <formula1>"Vistoria Frustrada;,Vistoria Recusada,Bônus;,Desistência;,Inadimplência;,Política de Aceitação;,Duplicidade;,Demais Motivos,Falta de Vistoria;,"</formula1>
     </dataValidation>
   </dataValidations>
@@ -2951,7 +3470,7 @@
       <c r="H1" s="4" t="s">
         <v>7</v>
       </c>
-      <c r="I1" s="33" t="s">
+      <c r="I1" s="32" t="s">
         <v>8</v>
       </c>
     </row>
@@ -4114,7 +4633,7 @@
       <c r="G1" s="1" t="s">
         <v>6</v>
       </c>
-      <c r="H1" s="44" t="s">
+      <c r="H1" s="43" t="s">
         <v>7</v>
       </c>
       <c r="I1" s="5" t="s">
@@ -4130,8 +4649,8 @@
       <c r="D2" s="25"/>
       <c r="E2" s="18"/>
       <c r="F2" s="19"/>
-      <c r="G2" s="42"/>
-      <c r="H2" s="39"/>
+      <c r="G2" s="41"/>
+      <c r="H2" s="38"/>
       <c r="I2" s="27"/>
     </row>
     <row r="3" spans="1:9">
@@ -4143,8 +4662,8 @@
       <c r="D3" s="25"/>
       <c r="E3" s="18"/>
       <c r="F3" s="19"/>
-      <c r="G3" s="42"/>
-      <c r="H3" s="39"/>
+      <c r="G3" s="41"/>
+      <c r="H3" s="38"/>
       <c r="I3" s="27"/>
     </row>
     <row r="4" spans="1:9">
@@ -4156,8 +4675,8 @@
       <c r="D4" s="25"/>
       <c r="E4" s="18"/>
       <c r="F4" s="19"/>
-      <c r="G4" s="42"/>
-      <c r="H4" s="39"/>
+      <c r="G4" s="41"/>
+      <c r="H4" s="38"/>
       <c r="I4" s="27"/>
     </row>
     <row r="5" spans="1:9">
@@ -4169,8 +4688,8 @@
       <c r="D5" s="25"/>
       <c r="E5" s="18"/>
       <c r="F5" s="19"/>
-      <c r="G5" s="42"/>
-      <c r="H5" s="40"/>
+      <c r="G5" s="41"/>
+      <c r="H5" s="39"/>
       <c r="I5" s="27"/>
     </row>
     <row r="6" spans="1:9">
@@ -4182,8 +4701,8 @@
       <c r="D6" s="25"/>
       <c r="E6" s="18"/>
       <c r="F6" s="19"/>
-      <c r="G6" s="43"/>
-      <c r="H6" s="41"/>
+      <c r="G6" s="42"/>
+      <c r="H6" s="40"/>
       <c r="I6" s="27"/>
     </row>
     <row r="7" spans="1:9">
@@ -4195,8 +4714,8 @@
       <c r="D7" s="25"/>
       <c r="E7" s="18"/>
       <c r="F7" s="19"/>
-      <c r="G7" s="45"/>
-      <c r="H7" s="41"/>
+      <c r="G7" s="44"/>
+      <c r="H7" s="40"/>
       <c r="I7" s="27"/>
     </row>
     <row r="8" spans="1:9">
@@ -4208,8 +4727,8 @@
       <c r="D8" s="25"/>
       <c r="E8" s="18"/>
       <c r="F8" s="19"/>
-      <c r="G8" s="46"/>
-      <c r="H8" s="41"/>
+      <c r="G8" s="45"/>
+      <c r="H8" s="40"/>
       <c r="I8" s="27"/>
     </row>
     <row r="9" spans="1:9">
@@ -4221,8 +4740,8 @@
       <c r="D9" s="25"/>
       <c r="E9" s="18"/>
       <c r="F9" s="19"/>
-      <c r="G9" s="46"/>
-      <c r="H9" s="39"/>
+      <c r="G9" s="45"/>
+      <c r="H9" s="38"/>
       <c r="I9" s="27"/>
     </row>
     <row r="10" spans="1:9">
@@ -4234,8 +4753,8 @@
       <c r="D10" s="25"/>
       <c r="E10" s="18"/>
       <c r="F10" s="19"/>
-      <c r="G10" s="46"/>
-      <c r="H10" s="39"/>
+      <c r="G10" s="45"/>
+      <c r="H10" s="38"/>
       <c r="I10" s="27"/>
     </row>
     <row r="11" spans="1:9">
@@ -4247,8 +4766,8 @@
       <c r="D11" s="25"/>
       <c r="E11" s="18"/>
       <c r="F11" s="19"/>
-      <c r="G11" s="46"/>
-      <c r="H11" s="39"/>
+      <c r="G11" s="45"/>
+      <c r="H11" s="38"/>
       <c r="I11" s="27"/>
     </row>
     <row r="12" spans="1:9">
@@ -4260,8 +4779,8 @@
       <c r="D12" s="25"/>
       <c r="E12" s="18"/>
       <c r="F12" s="19"/>
-      <c r="G12" s="46"/>
-      <c r="H12" s="39"/>
+      <c r="G12" s="45"/>
+      <c r="H12" s="38"/>
       <c r="I12" s="27"/>
     </row>
     <row r="13" spans="1:9">
@@ -4273,8 +4792,8 @@
       <c r="D13" s="25"/>
       <c r="E13" s="18"/>
       <c r="F13" s="19"/>
-      <c r="G13" s="46"/>
-      <c r="H13" s="39"/>
+      <c r="G13" s="45"/>
+      <c r="H13" s="38"/>
       <c r="I13" s="27"/>
     </row>
     <row r="14" spans="1:9">
@@ -4286,8 +4805,8 @@
       <c r="D14" s="25"/>
       <c r="E14" s="18"/>
       <c r="F14" s="19"/>
-      <c r="G14" s="46"/>
-      <c r="H14" s="39"/>
+      <c r="G14" s="45"/>
+      <c r="H14" s="38"/>
       <c r="I14" s="27"/>
     </row>
     <row r="15" spans="1:9">
@@ -4299,8 +4818,8 @@
       <c r="D15" s="25"/>
       <c r="E15" s="18"/>
       <c r="F15" s="19"/>
-      <c r="G15" s="46"/>
-      <c r="H15" s="39"/>
+      <c r="G15" s="45"/>
+      <c r="H15" s="38"/>
       <c r="I15" s="27"/>
     </row>
     <row r="16" spans="1:9">
@@ -4312,8 +4831,8 @@
       <c r="D16" s="25"/>
       <c r="E16" s="18"/>
       <c r="F16" s="12"/>
-      <c r="G16" s="46"/>
-      <c r="H16" s="39"/>
+      <c r="G16" s="45"/>
+      <c r="H16" s="38"/>
       <c r="I16" s="27"/>
     </row>
     <row r="17" spans="1:9" ht="15" customHeight="1">
@@ -4325,8 +4844,8 @@
       <c r="D17" s="25"/>
       <c r="E17" s="18"/>
       <c r="F17" s="12"/>
-      <c r="G17" s="42"/>
-      <c r="H17" s="39"/>
+      <c r="G17" s="41"/>
+      <c r="H17" s="38"/>
       <c r="I17" s="27"/>
     </row>
     <row r="18" spans="1:9">
@@ -4338,8 +4857,8 @@
       <c r="D18" s="25"/>
       <c r="E18" s="18"/>
       <c r="F18" s="12"/>
-      <c r="G18" s="46"/>
-      <c r="H18" s="39"/>
+      <c r="G18" s="45"/>
+      <c r="H18" s="38"/>
       <c r="I18" s="27"/>
     </row>
     <row r="19" spans="1:9">
@@ -4347,9 +4866,9 @@
       <c r="B19" s="8"/>
       <c r="C19" s="7"/>
       <c r="D19" s="23"/>
-      <c r="E19" s="35"/>
-      <c r="F19" s="37"/>
-      <c r="G19" s="34"/>
+      <c r="E19" s="34"/>
+      <c r="F19" s="36"/>
+      <c r="G19" s="33"/>
       <c r="H19" s="9"/>
       <c r="I19" s="27"/>
     </row>
@@ -4360,7 +4879,7 @@
       <c r="D20" s="8"/>
       <c r="E20" s="8"/>
       <c r="F20" s="15"/>
-      <c r="G20" s="34"/>
+      <c r="G20" s="33"/>
       <c r="H20" s="9"/>
       <c r="I20" s="27"/>
     </row>
@@ -4371,7 +4890,7 @@
       <c r="D21" s="8"/>
       <c r="E21" s="8"/>
       <c r="F21" s="9"/>
-      <c r="G21" s="34"/>
+      <c r="G21" s="33"/>
       <c r="H21" s="9"/>
       <c r="I21" s="27"/>
     </row>
@@ -4382,7 +4901,7 @@
       <c r="D22" s="8"/>
       <c r="E22" s="8"/>
       <c r="F22" s="9"/>
-      <c r="G22" s="34"/>
+      <c r="G22" s="33"/>
       <c r="H22" s="9"/>
       <c r="I22" s="27"/>
     </row>
@@ -4393,7 +4912,7 @@
       <c r="D23" s="8"/>
       <c r="E23" s="8"/>
       <c r="F23" s="9"/>
-      <c r="G23" s="34"/>
+      <c r="G23" s="33"/>
       <c r="H23" s="9"/>
       <c r="I23" s="27"/>
     </row>
@@ -4404,7 +4923,7 @@
       <c r="D24" s="8"/>
       <c r="E24" s="8"/>
       <c r="F24" s="9"/>
-      <c r="G24" s="34"/>
+      <c r="G24" s="33"/>
       <c r="H24" s="9"/>
       <c r="I24" s="27"/>
     </row>
@@ -4835,7 +5354,7 @@
       <c r="F3" s="12"/>
       <c r="G3" s="20"/>
       <c r="H3" s="9"/>
-      <c r="I3" s="38"/>
+      <c r="I3" s="37"/>
     </row>
     <row r="4" spans="1:9">
       <c r="A4" s="6" t="s">
@@ -4868,8 +5387,8 @@
       <c r="B6" s="7"/>
       <c r="C6" s="7"/>
       <c r="D6" s="23"/>
-      <c r="E6" s="35"/>
-      <c r="F6" s="36"/>
+      <c r="E6" s="34"/>
+      <c r="F6" s="35"/>
       <c r="G6" s="6"/>
       <c r="H6" s="9"/>
       <c r="I6" s="27"/>
@@ -6026,6 +6545,49 @@
 </file>
 
 <file path=customXml/item1.xml><?xml version="1.0" encoding="utf-8"?>
+<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
+  <documentManagement>
+    <_dlc_DocId xmlns="01f4fd7c-51c3-4ad2-ae58-e5034556b4ea">QAFFA7D2F2TC-2102087286-496578</_dlc_DocId>
+    <_dlc_DocIdUrl xmlns="01f4fd7c-51c3-4ad2-ae58-e5034556b4ea">
+      <Url>https://allianzms.sharepoint.com/teams/BR0010-4356589/_layouts/15/DocIdRedir.aspx?ID=QAFFA7D2F2TC-2102087286-496578</Url>
+      <Description>QAFFA7D2F2TC-2102087286-496578</Description>
+    </_dlc_DocIdUrl>
+    <DossierOwner xmlns="01f4fd7c-51c3-4ad2-ae58-e5034556b4ea">
+      <UserInfo>
+        <DisplayName/>
+        <AccountId xsi:nil="true"/>
+        <AccountType/>
+      </UserInfo>
+    </DossierOwner>
+    <_ip_UnifiedCompliancePolicyUIAction xmlns="http://schemas.microsoft.com/sharepoint/v3" xsi:nil="true"/>
+    <ccca9d190a3c43e89f73773ee806c8b5 xmlns="01f4fd7c-51c3-4ad2-ae58-e5034556b4ea">
+      <Terms xmlns="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    </ccca9d190a3c43e89f73773ee806c8b5>
+    <lcf76f155ced4ddcb4097134ff3c332f xmlns="ea6c6725-5210-4d6a-93cc-4cf85111ac5e">
+      <Terms xmlns="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    </lcf76f155ced4ddcb4097134ff3c332f>
+    <ContractDate xmlns="01f4fd7c-51c3-4ad2-ae58-e5034556b4ea" xsi:nil="true"/>
+    <MailPreviewData xmlns="01f4fd7c-51c3-4ad2-ae58-e5034556b4ea" xsi:nil="true"/>
+    <_Flow_SignoffStatus xmlns="ea6c6725-5210-4d6a-93cc-4cf85111ac5e" xsi:nil="true"/>
+    <_ip_UnifiedCompliancePolicyProperties xmlns="http://schemas.microsoft.com/sharepoint/v3" xsi:nil="true"/>
+    <ContractExpirationDate xmlns="01f4fd7c-51c3-4ad2-ae58-e5034556b4ea" xsi:nil="true"/>
+    <DossierStatus xmlns="01f4fd7c-51c3-4ad2-ae58-e5034556b4ea" xsi:nil="true"/>
+    <ia4b831ccad64069ad2e0cbd870e9b8a xmlns="01f4fd7c-51c3-4ad2-ae58-e5034556b4ea">
+      <Terms xmlns="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    </ia4b831ccad64069ad2e0cbd870e9b8a>
+    <TaxCatchAll xmlns="01f4fd7c-51c3-4ad2-ae58-e5034556b4ea" xsi:nil="true"/>
+    <alteradopor xmlns="ea6c6725-5210-4d6a-93cc-4cf85111ac5e">
+      <UserInfo>
+        <DisplayName/>
+        <AccountId xsi:nil="true"/>
+        <AccountType/>
+      </UserInfo>
+    </alteradopor>
+  </documentManagement>
+</p:properties>
+</file>
+
+<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
 <ct:contentTypeSchema xmlns:ct="http://schemas.microsoft.com/office/2006/metadata/contentType" xmlns:ma="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes" ct:_="" ma:_="" ma:contentTypeName="Document" ma:contentTypeID="0x01010006E7B04763359F4AAB0FC84D5027BFC8" ma:contentTypeVersion="44" ma:contentTypeDescription="Create a new document." ma:contentTypeScope="" ma:versionID="ac14f8cb44178d381f4c0afb30680a90">
   <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:ns1="http://schemas.microsoft.com/sharepoint/v3" xmlns:ns2="01f4fd7c-51c3-4ad2-ae58-e5034556b4ea" xmlns:ns3="ea6c6725-5210-4d6a-93cc-4cf85111ac5e" targetNamespace="http://schemas.microsoft.com/office/2006/metadata/properties" ma:root="true" ma:fieldsID="5e58414b065c9b590c40efa77cd84bb6" ns1:_="" ns2:_="" ns3:_="">
     <xsd:import namespace="http://schemas.microsoft.com/sharepoint/v3"/>
@@ -6403,59 +6965,7 @@
 </ct:contentTypeSchema>
 </file>
 
-<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
-<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
-  <documentManagement>
-    <_dlc_DocId xmlns="01f4fd7c-51c3-4ad2-ae58-e5034556b4ea">QAFFA7D2F2TC-2102087286-496578</_dlc_DocId>
-    <_dlc_DocIdUrl xmlns="01f4fd7c-51c3-4ad2-ae58-e5034556b4ea">
-      <Url>https://allianzms.sharepoint.com/teams/BR0010-4356589/_layouts/15/DocIdRedir.aspx?ID=QAFFA7D2F2TC-2102087286-496578</Url>
-      <Description>QAFFA7D2F2TC-2102087286-496578</Description>
-    </_dlc_DocIdUrl>
-    <DossierOwner xmlns="01f4fd7c-51c3-4ad2-ae58-e5034556b4ea">
-      <UserInfo>
-        <DisplayName/>
-        <AccountId xsi:nil="true"/>
-        <AccountType/>
-      </UserInfo>
-    </DossierOwner>
-    <_ip_UnifiedCompliancePolicyUIAction xmlns="http://schemas.microsoft.com/sharepoint/v3" xsi:nil="true"/>
-    <ccca9d190a3c43e89f73773ee806c8b5 xmlns="01f4fd7c-51c3-4ad2-ae58-e5034556b4ea">
-      <Terms xmlns="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
-    </ccca9d190a3c43e89f73773ee806c8b5>
-    <lcf76f155ced4ddcb4097134ff3c332f xmlns="ea6c6725-5210-4d6a-93cc-4cf85111ac5e">
-      <Terms xmlns="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
-    </lcf76f155ced4ddcb4097134ff3c332f>
-    <ContractDate xmlns="01f4fd7c-51c3-4ad2-ae58-e5034556b4ea" xsi:nil="true"/>
-    <MailPreviewData xmlns="01f4fd7c-51c3-4ad2-ae58-e5034556b4ea" xsi:nil="true"/>
-    <_Flow_SignoffStatus xmlns="ea6c6725-5210-4d6a-93cc-4cf85111ac5e" xsi:nil="true"/>
-    <_ip_UnifiedCompliancePolicyProperties xmlns="http://schemas.microsoft.com/sharepoint/v3" xsi:nil="true"/>
-    <ContractExpirationDate xmlns="01f4fd7c-51c3-4ad2-ae58-e5034556b4ea" xsi:nil="true"/>
-    <DossierStatus xmlns="01f4fd7c-51c3-4ad2-ae58-e5034556b4ea" xsi:nil="true"/>
-    <ia4b831ccad64069ad2e0cbd870e9b8a xmlns="01f4fd7c-51c3-4ad2-ae58-e5034556b4ea">
-      <Terms xmlns="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
-    </ia4b831ccad64069ad2e0cbd870e9b8a>
-    <TaxCatchAll xmlns="01f4fd7c-51c3-4ad2-ae58-e5034556b4ea" xsi:nil="true"/>
-    <alteradopor xmlns="ea6c6725-5210-4d6a-93cc-4cf85111ac5e">
-      <UserInfo>
-        <DisplayName/>
-        <AccountId xsi:nil="true"/>
-        <AccountType/>
-      </UserInfo>
-    </alteradopor>
-  </documentManagement>
-</p:properties>
-</file>
-
 <file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
-<?mso-contentType ?>
-<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
-  <Display>DocumentLibraryForm</Display>
-  <Edit>DocumentLibraryForm</Edit>
-  <New>DocumentLibraryForm</New>
-</FormTemplates>
-</file>
-
-<file path=customXml/item4.xml><?xml version="1.0" encoding="utf-8"?>
 <?mso-contentType ?>
 <spe:Receivers xmlns:spe="http://schemas.microsoft.com/sharepoint/events">
   <Receiver>
@@ -6505,18 +7015,27 @@
 </spe:Receivers>
 </file>
 
+<file path=customXml/item4.xml><?xml version="1.0" encoding="utf-8"?>
+<?mso-contentType ?>
+<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
+  <Display>DocumentLibraryForm</Display>
+  <Edit>DocumentLibraryForm</Edit>
+  <New>DocumentLibraryForm</New>
+</FormTemplates>
+</file>
+
 <file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{C48653D8-7562-408C-9B57-D83FFA71DB43}"/>
+</file>
+
+<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
 <ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{E4D3A833-2B0B-418C-BE4E-5DFB58A9B857}"/>
 </file>
 
-<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{C48653D8-7562-408C-9B57-D83FFA71DB43}"/>
-</file>
-
 <file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{BC9CB02D-0F63-4CE2-B316-61A87327416C}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{13279B2D-D76C-4CA7-B517-83259B9C0FB4}"/>
 </file>
 
 <file path=customXml/itemProps4.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{13279B2D-D76C-4CA7-B517-83259B9C0FB4}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{BC9CB02D-0F63-4CE2-B316-61A87327416C}"/>
 </file>
--- a/Data Files/Backoffce/IndexacaoFG/Arquivos/Relatório de Recusas  08.09.2025 a 14.09.2025.xlsx
+++ b/Data Files/Backoffce/IndexacaoFG/Arquivos/Relatório de Recusas  08.09.2025 a 14.09.2025.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="4" rupBuild="29301"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="4" rupBuild="28526"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://allianzms.sharepoint.com/teams/BR0010-4356589/Shared Documents/BACK-OFFICE SME/Santander/2025/Relatório de Recusas/05. Maio/"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\APZelizi\Desktop\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{31977251-4844-4E1E-9117-76B9027D71CD}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{5BABB57C-32F2-4206-813C-D4637768572A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="19530" windowHeight="9780" firstSheet="1" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10420" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="08.09" sheetId="2" r:id="rId1"/>
@@ -42,7 +42,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="360" uniqueCount="91">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="403" uniqueCount="114">
   <si>
     <t>SEGURADORA</t>
   </si>
@@ -321,13 +321,82 @@
   </si>
   <si>
     <t xml:space="preserve">POLEN LTDA EPP                               </t>
+  </si>
+  <si>
+    <t>MARIA APARECIDA RODRIGUES CPF 03275565877</t>
+  </si>
+  <si>
+    <t> Chassi irregular</t>
+  </si>
+  <si>
+    <t xml:space="preserve">HENRIQUETA BARBOSA SANTOS                    </t>
+  </si>
+  <si>
+    <t>FRUSTRADO, PRAZO PARA REENVIO EXPIRADO</t>
+  </si>
+  <si>
+    <t>22/09/2025</t>
+  </si>
+  <si>
+    <t xml:space="preserve">NEY FAUSTO GUERIM                            </t>
+  </si>
+  <si>
+    <t>NUP Cancelamento 09.09.2025</t>
+  </si>
+  <si>
+    <t xml:space="preserve">PAULO FERREIRA DE ARAUJO                     </t>
+  </si>
+  <si>
+    <t>28/08/2025</t>
+  </si>
+  <si>
+    <t xml:space="preserve">TMC LOL TRANSPORTES LTDA EPP                 </t>
+  </si>
+  <si>
+    <t>Veículo informado é diferente do calculado.</t>
+  </si>
+  <si>
+    <t>será necessário a apresentação do endosso de cancelamento emitido, a atualização junto a Central de Bônus.</t>
+  </si>
+  <si>
+    <t>01/09 e 09/09/2025</t>
+  </si>
+  <si>
+    <t xml:space="preserve">MARCUS TOSELLI                               </t>
+  </si>
+  <si>
+    <t xml:space="preserve"> Veículo informado é diferente do calculado.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">RAFAEL LOPES VIEIRA                          </t>
+  </si>
+  <si>
+    <t>30/08/2025</t>
+  </si>
+  <si>
+    <t xml:space="preserve">LAURA MARIA DE LACERDA CHAVES                </t>
+  </si>
+  <si>
+    <t xml:space="preserve">ADMILSON FERNANDES                           </t>
+  </si>
+  <si>
+    <t xml:space="preserve"> Auto Compara, solicita recusa da proposta 134383118</t>
+  </si>
+  <si>
+    <t>17/09/2025</t>
+  </si>
+  <si>
+    <t xml:space="preserve">DILSON RODRIGUES SOUTO                       </t>
+  </si>
+  <si>
+    <t xml:space="preserve">Favor enviar cópia completa da apólice anterior 2024/2025 (atual) através desse e-mail. </t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="7">
+  <fonts count="9">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -369,6 +438,18 @@
       <color rgb="FF414141"/>
       <name val="Allianz Neo"/>
       <family val="2"/>
+      <charset val="1"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF000000"/>
+      <name val="Aptos Narrow"/>
+      <family val="2"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF242424"/>
+      <name val="Aptos Narrow"/>
       <charset val="1"/>
     </font>
   </fonts>
@@ -585,7 +666,7 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="78">
+  <cellXfs count="88">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="2" borderId="1" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
@@ -722,15 +803,10 @@
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1"/>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1"/>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="12" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="12" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="12" xfId="0" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top" wrapText="1"/>
     </xf>
@@ -758,26 +834,89 @@
     <xf numFmtId="0" fontId="5" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1"/>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1"/>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1"/>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="2" fillId="2" borderId="1" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1"/>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="14" fontId="0" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="4" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="14" fontId="0" fillId="0" borderId="4" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="4" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="6" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="14" fontId="0" fillId="0" borderId="6" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="4" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="4" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="4" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="14" fontId="0" fillId="0" borderId="4" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="4" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment vertical="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="2">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
     <cellStyle name="Normal_Plan2_1" xfId="1" xr:uid="{69F13A52-20D9-46CA-8619-BC7A1BA09FD8}"/>
   </cellStyles>
-  <dxfs count="3">
+  <dxfs count="5">
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
     <dxf>
       <font>
         <color rgb="FF9C0006"/>
@@ -1139,16 +1278,16 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{A2FDCF22-758E-4370-8390-755171A8B113}">
   <dimension ref="A1:I56"/>
-  <sheetFormatPr defaultRowHeight="15"/>
+  <sheetFormatPr defaultRowHeight="14.5"/>
   <cols>
-    <col min="2" max="2" width="14.140625" customWidth="1"/>
-    <col min="3" max="3" width="18.140625" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="16.140625" customWidth="1"/>
-    <col min="5" max="5" width="18.85546875" customWidth="1"/>
+    <col min="2" max="2" width="14.1796875" customWidth="1"/>
+    <col min="3" max="3" width="18.1796875" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="16.1796875" customWidth="1"/>
+    <col min="5" max="5" width="18.81640625" customWidth="1"/>
     <col min="6" max="6" width="40" customWidth="1"/>
-    <col min="7" max="7" width="20.28515625" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="23.7109375" customWidth="1"/>
-    <col min="9" max="9" width="17.5703125" customWidth="1"/>
+    <col min="7" max="7" width="20.26953125" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="23.7265625" customWidth="1"/>
+    <col min="9" max="9" width="17.54296875" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:9">
@@ -2435,17 +2574,17 @@
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{FFA17127-7620-4DD9-9061-6C654E2EC5C2}">
   <dimension ref="A1:I53"/>
-  <sheetFormatPr defaultRowHeight="15"/>
+  <sheetFormatPr defaultRowHeight="14.5"/>
   <cols>
-    <col min="1" max="1" width="9.5703125" customWidth="1"/>
-    <col min="2" max="2" width="16.5703125" customWidth="1"/>
-    <col min="3" max="3" width="21.5703125" customWidth="1"/>
-    <col min="4" max="4" width="13.28515625" style="17" customWidth="1"/>
-    <col min="5" max="5" width="18.5703125" customWidth="1"/>
-    <col min="6" max="6" width="31.5703125" customWidth="1"/>
-    <col min="7" max="7" width="19.7109375" style="76" customWidth="1"/>
+    <col min="1" max="1" width="9.54296875" customWidth="1"/>
+    <col min="2" max="2" width="16.54296875" customWidth="1"/>
+    <col min="3" max="3" width="21.54296875" customWidth="1"/>
+    <col min="4" max="4" width="13.26953125" style="17" customWidth="1"/>
+    <col min="5" max="5" width="18.54296875" customWidth="1"/>
+    <col min="6" max="6" width="31.54296875" customWidth="1"/>
+    <col min="7" max="7" width="19.7265625" customWidth="1"/>
     <col min="8" max="8" width="24" customWidth="1"/>
-    <col min="9" max="9" width="22.7109375" style="16" customWidth="1"/>
+    <col min="9" max="9" width="22.7265625" style="16" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:9">
@@ -2467,7 +2606,7 @@
       <c r="F1" s="1" t="s">
         <v>5</v>
       </c>
-      <c r="G1" s="74" t="s">
+      <c r="G1" s="68" t="s">
         <v>6</v>
       </c>
       <c r="H1" s="4" t="s">
@@ -2478,13 +2617,13 @@
       </c>
     </row>
     <row r="2" spans="1:9">
-      <c r="A2" s="61" t="s">
-        <v>9</v>
-      </c>
-      <c r="B2" s="62">
+      <c r="A2" s="58" t="s">
+        <v>9</v>
+      </c>
+      <c r="B2" s="59">
         <v>45908</v>
       </c>
-      <c r="C2" s="63">
+      <c r="C2" s="60">
         <v>45909</v>
       </c>
       <c r="D2" s="50" t="s">
@@ -2505,13 +2644,13 @@
       <c r="I2" s="27"/>
     </row>
     <row r="3" spans="1:9">
-      <c r="A3" s="61" t="s">
-        <v>9</v>
-      </c>
-      <c r="B3" s="62">
+      <c r="A3" s="58" t="s">
+        <v>9</v>
+      </c>
+      <c r="B3" s="59">
         <v>45908</v>
       </c>
-      <c r="C3" s="63">
+      <c r="C3" s="60">
         <v>45909</v>
       </c>
       <c r="D3" s="50" t="s">
@@ -2532,13 +2671,13 @@
       <c r="I3" s="27"/>
     </row>
     <row r="4" spans="1:9">
-      <c r="A4" s="61" t="s">
-        <v>9</v>
-      </c>
-      <c r="B4" s="62">
+      <c r="A4" s="58" t="s">
+        <v>9</v>
+      </c>
+      <c r="B4" s="59">
         <v>45905</v>
       </c>
-      <c r="C4" s="63">
+      <c r="C4" s="60">
         <v>45909</v>
       </c>
       <c r="D4" s="53" t="s">
@@ -2559,22 +2698,22 @@
       <c r="I4" s="9"/>
     </row>
     <row r="5" spans="1:9">
-      <c r="A5" s="64" t="s">
-        <v>9</v>
-      </c>
-      <c r="B5" s="62">
+      <c r="A5" s="61" t="s">
+        <v>9</v>
+      </c>
+      <c r="B5" s="59">
         <v>45898</v>
       </c>
-      <c r="C5" s="63">
+      <c r="C5" s="60">
         <v>45909</v>
       </c>
-      <c r="D5" s="56">
+      <c r="D5" s="50">
         <v>134216123</v>
       </c>
-      <c r="E5" s="65">
+      <c r="E5" s="62">
         <v>3450069040</v>
       </c>
-      <c r="F5" s="57" t="s">
+      <c r="F5" s="40" t="s">
         <v>63</v>
       </c>
       <c r="G5" s="45" t="s">
@@ -2588,28 +2727,28 @@
       </c>
     </row>
     <row r="6" spans="1:9">
-      <c r="A6" s="64" t="s">
-        <v>9</v>
-      </c>
-      <c r="B6" s="62">
+      <c r="A6" s="61" t="s">
+        <v>9</v>
+      </c>
+      <c r="B6" s="59">
         <v>45898</v>
       </c>
-      <c r="C6" s="63">
+      <c r="C6" s="60">
         <v>45909</v>
       </c>
-      <c r="D6" s="56">
+      <c r="D6" s="50">
         <v>134216628</v>
       </c>
-      <c r="E6" s="65">
+      <c r="E6" s="62">
         <v>3450068831</v>
       </c>
-      <c r="F6" s="57" t="s">
+      <c r="F6" s="40" t="s">
         <v>65</v>
       </c>
       <c r="G6" s="45" t="s">
         <v>21</v>
       </c>
-      <c r="H6" s="72" t="s">
+      <c r="H6" s="39" t="s">
         <v>66</v>
       </c>
       <c r="I6" s="27">
@@ -2617,28 +2756,28 @@
       </c>
     </row>
     <row r="7" spans="1:9">
-      <c r="A7" s="64" t="s">
-        <v>9</v>
-      </c>
-      <c r="B7" s="62">
+      <c r="A7" s="61" t="s">
+        <v>9</v>
+      </c>
+      <c r="B7" s="59">
         <v>45929</v>
       </c>
-      <c r="C7" s="63">
+      <c r="C7" s="60">
         <v>45909</v>
       </c>
-      <c r="D7" s="56">
+      <c r="D7" s="50">
         <v>134230678</v>
       </c>
-      <c r="E7" s="65">
+      <c r="E7" s="62">
         <v>3450070118</v>
       </c>
-      <c r="F7" s="57" t="s">
+      <c r="F7" s="40" t="s">
         <v>67</v>
       </c>
       <c r="G7" s="44" t="s">
         <v>68</v>
       </c>
-      <c r="H7" s="73" t="s">
+      <c r="H7" s="55" t="s">
         <v>69</v>
       </c>
       <c r="I7" s="27">
@@ -2646,28 +2785,28 @@
       </c>
     </row>
     <row r="8" spans="1:9">
-      <c r="A8" s="64" t="s">
-        <v>9</v>
-      </c>
-      <c r="B8" s="62">
+      <c r="A8" s="61" t="s">
+        <v>9</v>
+      </c>
+      <c r="B8" s="59">
         <v>45903</v>
       </c>
-      <c r="C8" s="63">
+      <c r="C8" s="60">
         <v>45909</v>
       </c>
-      <c r="D8" s="56">
+      <c r="D8" s="50">
         <v>134267077</v>
       </c>
-      <c r="E8" s="65">
+      <c r="E8" s="62">
         <v>3450072000</v>
       </c>
-      <c r="F8" s="77" t="s">
+      <c r="F8" s="70" t="s">
         <v>70</v>
       </c>
       <c r="G8" s="44" t="s">
         <v>24</v>
       </c>
-      <c r="H8" s="58" t="s">
+      <c r="H8" s="40" t="s">
         <v>71</v>
       </c>
       <c r="I8" s="27">
@@ -2675,28 +2814,28 @@
       </c>
     </row>
     <row r="9" spans="1:9">
-      <c r="A9" s="64" t="s">
-        <v>9</v>
-      </c>
-      <c r="B9" s="62">
+      <c r="A9" s="61" t="s">
+        <v>9</v>
+      </c>
+      <c r="B9" s="59">
         <v>45926</v>
       </c>
-      <c r="C9" s="63">
+      <c r="C9" s="60">
         <v>45909</v>
       </c>
-      <c r="D9" s="56">
+      <c r="D9" s="50">
         <v>134150028</v>
       </c>
-      <c r="E9" s="65">
+      <c r="E9" s="62">
         <v>3450065707</v>
       </c>
-      <c r="F9" s="57" t="s">
+      <c r="F9" s="40" t="s">
         <v>72</v>
       </c>
       <c r="G9" s="45" t="s">
         <v>68</v>
       </c>
-      <c r="H9" s="71" t="s">
+      <c r="H9" s="38" t="s">
         <v>73</v>
       </c>
       <c r="I9" s="27">
@@ -2704,28 +2843,28 @@
       </c>
     </row>
     <row r="10" spans="1:9">
-      <c r="A10" s="64" t="s">
-        <v>9</v>
-      </c>
-      <c r="B10" s="62">
+      <c r="A10" s="61" t="s">
+        <v>9</v>
+      </c>
+      <c r="B10" s="59">
         <v>45896</v>
       </c>
-      <c r="C10" s="63">
+      <c r="C10" s="60">
         <v>45909</v>
       </c>
-      <c r="D10" s="56">
+      <c r="D10" s="50">
         <v>134142970</v>
       </c>
-      <c r="E10" s="65">
+      <c r="E10" s="62">
         <v>3450065190</v>
       </c>
-      <c r="F10" s="57" t="s">
+      <c r="F10" s="40" t="s">
         <v>74</v>
       </c>
       <c r="G10" s="45" t="s">
         <v>68</v>
       </c>
-      <c r="H10" s="71" t="s">
+      <c r="H10" s="38" t="s">
         <v>75</v>
       </c>
       <c r="I10" s="27">
@@ -2733,28 +2872,28 @@
       </c>
     </row>
     <row r="11" spans="1:9">
-      <c r="A11" s="64" t="s">
-        <v>9</v>
-      </c>
-      <c r="B11" s="62">
+      <c r="A11" s="61" t="s">
+        <v>9</v>
+      </c>
+      <c r="B11" s="59">
         <v>45901</v>
       </c>
-      <c r="C11" s="63">
+      <c r="C11" s="60">
         <v>45909</v>
       </c>
-      <c r="D11" s="56">
+      <c r="D11" s="50">
         <v>134218656</v>
       </c>
-      <c r="E11" s="65">
+      <c r="E11" s="62">
         <v>3450069282</v>
       </c>
-      <c r="F11" s="57" t="s">
+      <c r="F11" s="40" t="s">
         <v>76</v>
       </c>
       <c r="G11" s="45" t="s">
         <v>21</v>
       </c>
-      <c r="H11" s="71" t="s">
+      <c r="H11" s="38" t="s">
         <v>77</v>
       </c>
       <c r="I11" s="27">
@@ -2762,28 +2901,28 @@
       </c>
     </row>
     <row r="12" spans="1:9">
-      <c r="A12" s="64" t="s">
-        <v>9</v>
-      </c>
-      <c r="B12" s="62">
+      <c r="A12" s="61" t="s">
+        <v>9</v>
+      </c>
+      <c r="B12" s="59">
         <v>45901</v>
       </c>
-      <c r="C12" s="63">
+      <c r="C12" s="60">
         <v>45909</v>
       </c>
-      <c r="D12" s="56">
+      <c r="D12" s="50">
         <v>134217366</v>
       </c>
-      <c r="E12" s="65">
+      <c r="E12" s="62">
         <v>3450069249</v>
       </c>
-      <c r="F12" s="57" t="s">
+      <c r="F12" s="40" t="s">
         <v>78</v>
       </c>
       <c r="G12" s="45" t="s">
         <v>21</v>
       </c>
-      <c r="H12" s="71" t="s">
+      <c r="H12" s="38" t="s">
         <v>79</v>
       </c>
       <c r="I12" s="27">
@@ -2791,28 +2930,28 @@
       </c>
     </row>
     <row r="13" spans="1:9">
-      <c r="A13" s="64" t="s">
-        <v>9</v>
-      </c>
-      <c r="B13" s="62">
+      <c r="A13" s="61" t="s">
+        <v>9</v>
+      </c>
+      <c r="B13" s="59">
         <v>45898</v>
       </c>
-      <c r="C13" s="63">
+      <c r="C13" s="60">
         <v>45909</v>
       </c>
-      <c r="D13" s="56">
+      <c r="D13" s="50">
         <v>134221682</v>
       </c>
-      <c r="E13" s="65">
+      <c r="E13" s="62">
         <v>3450067962</v>
       </c>
-      <c r="F13" s="57" t="s">
+      <c r="F13" s="40" t="s">
         <v>80</v>
       </c>
       <c r="G13" s="45" t="s">
         <v>21</v>
       </c>
-      <c r="H13" s="71" t="s">
+      <c r="H13" s="38" t="s">
         <v>81</v>
       </c>
       <c r="I13" s="27">
@@ -2820,28 +2959,28 @@
       </c>
     </row>
     <row r="14" spans="1:9">
-      <c r="A14" s="64" t="s">
-        <v>9</v>
-      </c>
-      <c r="B14" s="62">
+      <c r="A14" s="61" t="s">
+        <v>9</v>
+      </c>
+      <c r="B14" s="59">
         <v>45903</v>
       </c>
-      <c r="C14" s="63">
+      <c r="C14" s="60">
         <v>45909</v>
       </c>
-      <c r="D14" s="56">
+      <c r="D14" s="50">
         <v>134259586</v>
       </c>
-      <c r="E14" s="65">
+      <c r="E14" s="62">
         <v>3450071460</v>
       </c>
-      <c r="F14" s="57" t="s">
+      <c r="F14" s="40" t="s">
         <v>82</v>
       </c>
       <c r="G14" s="45" t="s">
         <v>31</v>
       </c>
-      <c r="H14" s="71" t="s">
+      <c r="H14" s="38" t="s">
         <v>32</v>
       </c>
       <c r="I14" s="27">
@@ -2849,22 +2988,22 @@
       </c>
     </row>
     <row r="15" spans="1:9">
-      <c r="A15" s="64" t="s">
-        <v>9</v>
-      </c>
-      <c r="B15" s="62">
+      <c r="A15" s="61" t="s">
+        <v>9</v>
+      </c>
+      <c r="B15" s="59">
         <v>45901</v>
       </c>
-      <c r="C15" s="63">
+      <c r="C15" s="60">
         <v>45909</v>
       </c>
-      <c r="D15" s="56">
+      <c r="D15" s="50">
         <v>134220631</v>
       </c>
-      <c r="E15" s="65">
+      <c r="E15" s="62">
         <v>3450069436</v>
       </c>
-      <c r="F15" s="57" t="s">
+      <c r="F15" s="40" t="s">
         <v>83</v>
       </c>
       <c r="G15" s="45" t="s">
@@ -2878,22 +3017,22 @@
       </c>
     </row>
     <row r="16" spans="1:9">
-      <c r="A16" s="64" t="s">
-        <v>9</v>
-      </c>
-      <c r="B16" s="62">
+      <c r="A16" s="61" t="s">
+        <v>9</v>
+      </c>
+      <c r="B16" s="59">
         <v>45898</v>
       </c>
-      <c r="C16" s="63">
+      <c r="C16" s="60">
         <v>45909</v>
       </c>
-      <c r="D16" s="56">
+      <c r="D16" s="50">
         <v>134217300</v>
       </c>
-      <c r="E16" s="65">
+      <c r="E16" s="62">
         <v>3450068820</v>
       </c>
-      <c r="F16" s="57" t="s">
+      <c r="F16" s="40" t="s">
         <v>84</v>
       </c>
       <c r="G16" s="45" t="s">
@@ -2907,22 +3046,22 @@
       </c>
     </row>
     <row r="17" spans="1:9">
-      <c r="A17" s="64" t="s">
-        <v>9</v>
-      </c>
-      <c r="B17" s="62">
+      <c r="A17" s="61" t="s">
+        <v>9</v>
+      </c>
+      <c r="B17" s="59">
         <v>45898</v>
       </c>
-      <c r="C17" s="63">
+      <c r="C17" s="60">
         <v>45909</v>
       </c>
-      <c r="D17" s="56">
+      <c r="D17" s="50">
         <v>134221526</v>
       </c>
-      <c r="E17" s="65">
+      <c r="E17" s="62">
         <v>3450068017</v>
       </c>
-      <c r="F17" s="57" t="s">
+      <c r="F17" s="40" t="s">
         <v>85</v>
       </c>
       <c r="G17" s="45" t="s">
@@ -2936,28 +3075,28 @@
       </c>
     </row>
     <row r="18" spans="1:9">
-      <c r="A18" s="64" t="s">
-        <v>9</v>
-      </c>
-      <c r="B18" s="62">
+      <c r="A18" s="61" t="s">
+        <v>9</v>
+      </c>
+      <c r="B18" s="59">
         <v>45903</v>
       </c>
-      <c r="C18" s="63">
+      <c r="C18" s="60">
         <v>45909</v>
       </c>
-      <c r="D18" s="56">
+      <c r="D18" s="50">
         <v>134275478</v>
       </c>
-      <c r="E18" s="65">
+      <c r="E18" s="62">
         <v>3450072615</v>
       </c>
-      <c r="F18" s="57" t="s">
+      <c r="F18" s="40" t="s">
         <v>86</v>
       </c>
       <c r="G18" s="45" t="s">
         <v>21</v>
       </c>
-      <c r="H18" s="71" t="s">
+      <c r="H18" s="38" t="s">
         <v>87</v>
       </c>
       <c r="I18" s="27">
@@ -2965,22 +3104,22 @@
       </c>
     </row>
     <row r="19" spans="1:9">
-      <c r="A19" s="64" t="s">
-        <v>9</v>
-      </c>
-      <c r="B19" s="62">
+      <c r="A19" s="61" t="s">
+        <v>9</v>
+      </c>
+      <c r="B19" s="59">
         <v>45901</v>
       </c>
-      <c r="C19" s="63">
+      <c r="C19" s="60">
         <v>45909</v>
       </c>
-      <c r="D19" s="56">
+      <c r="D19" s="50">
         <v>134224096</v>
       </c>
-      <c r="E19" s="65">
+      <c r="E19" s="62">
         <v>3450069722</v>
       </c>
-      <c r="F19" s="57" t="s">
+      <c r="F19" s="40" t="s">
         <v>88</v>
       </c>
       <c r="G19" s="45" t="s">
@@ -2994,22 +3133,22 @@
       </c>
     </row>
     <row r="20" spans="1:9">
-      <c r="A20" s="64" t="s">
-        <v>9</v>
-      </c>
-      <c r="B20" s="62">
+      <c r="A20" s="61" t="s">
+        <v>9</v>
+      </c>
+      <c r="B20" s="59">
         <v>45901</v>
       </c>
-      <c r="C20" s="63">
+      <c r="C20" s="60">
         <v>45909</v>
       </c>
-      <c r="D20" s="56">
+      <c r="D20" s="50">
         <v>134227978</v>
       </c>
-      <c r="E20" s="65">
+      <c r="E20" s="62">
         <v>3450069986</v>
       </c>
-      <c r="F20" s="57" t="s">
+      <c r="F20" s="40" t="s">
         <v>89</v>
       </c>
       <c r="G20" s="45" t="s">
@@ -3023,22 +3162,22 @@
       </c>
     </row>
     <row r="21" spans="1:9">
-      <c r="A21" s="64" t="s">
-        <v>9</v>
-      </c>
-      <c r="B21" s="62">
+      <c r="A21" s="61" t="s">
+        <v>9</v>
+      </c>
+      <c r="B21" s="59">
         <v>45901</v>
       </c>
-      <c r="C21" s="63">
+      <c r="C21" s="60">
         <v>45909</v>
       </c>
-      <c r="D21" s="56">
+      <c r="D21" s="50">
         <v>134231864</v>
       </c>
-      <c r="E21" s="65">
+      <c r="E21" s="62">
         <v>3450070173</v>
       </c>
-      <c r="F21" s="57" t="s">
+      <c r="F21" s="40" t="s">
         <v>90</v>
       </c>
       <c r="G21" s="45" t="s">
@@ -3052,167 +3191,167 @@
       </c>
     </row>
     <row r="22" spans="1:9">
-      <c r="A22" s="64"/>
-      <c r="B22" s="62"/>
-      <c r="C22" s="63"/>
+      <c r="A22" s="61"/>
+      <c r="B22" s="59"/>
+      <c r="C22" s="60"/>
       <c r="D22" s="50"/>
-      <c r="E22" s="65"/>
-      <c r="F22" s="58"/>
+      <c r="E22" s="62"/>
+      <c r="F22" s="40"/>
       <c r="G22" s="45"/>
       <c r="H22" s="38"/>
       <c r="I22" s="27"/>
     </row>
     <row r="23" spans="1:9">
-      <c r="A23" s="64"/>
-      <c r="B23" s="62"/>
-      <c r="C23" s="63"/>
+      <c r="A23" s="61"/>
+      <c r="B23" s="59"/>
+      <c r="C23" s="60"/>
       <c r="D23" s="50"/>
-      <c r="E23" s="65"/>
-      <c r="F23" s="58"/>
+      <c r="E23" s="62"/>
+      <c r="F23" s="40"/>
       <c r="G23" s="45"/>
       <c r="H23" s="38"/>
       <c r="I23" s="27"/>
     </row>
     <row r="24" spans="1:9">
-      <c r="A24" s="64"/>
-      <c r="B24" s="62"/>
-      <c r="C24" s="63"/>
+      <c r="A24" s="61"/>
+      <c r="B24" s="59"/>
+      <c r="C24" s="60"/>
       <c r="D24" s="50"/>
-      <c r="E24" s="65"/>
-      <c r="F24" s="58"/>
+      <c r="E24" s="62"/>
+      <c r="F24" s="40"/>
       <c r="G24" s="45"/>
-      <c r="H24" s="66"/>
+      <c r="H24" s="63"/>
       <c r="I24" s="27"/>
     </row>
     <row r="25" spans="1:9">
-      <c r="A25" s="64"/>
-      <c r="B25" s="62"/>
-      <c r="C25" s="63"/>
+      <c r="A25" s="61"/>
+      <c r="B25" s="59"/>
+      <c r="C25" s="60"/>
       <c r="D25" s="50"/>
-      <c r="E25" s="65"/>
-      <c r="F25" s="58"/>
+      <c r="E25" s="62"/>
+      <c r="F25" s="40"/>
       <c r="G25" s="45"/>
       <c r="H25" s="38"/>
       <c r="I25" s="27"/>
     </row>
     <row r="26" spans="1:9">
-      <c r="A26" s="64"/>
-      <c r="B26" s="62"/>
-      <c r="C26" s="63"/>
+      <c r="A26" s="61"/>
+      <c r="B26" s="59"/>
+      <c r="C26" s="60"/>
       <c r="D26" s="50"/>
-      <c r="E26" s="65"/>
-      <c r="F26" s="58"/>
+      <c r="E26" s="62"/>
+      <c r="F26" s="40"/>
       <c r="G26" s="45"/>
       <c r="H26" s="38"/>
       <c r="I26" s="27"/>
     </row>
     <row r="27" spans="1:9">
-      <c r="A27" s="64"/>
-      <c r="B27" s="62"/>
-      <c r="C27" s="63"/>
+      <c r="A27" s="61"/>
+      <c r="B27" s="59"/>
+      <c r="C27" s="60"/>
       <c r="D27" s="50"/>
-      <c r="E27" s="65"/>
-      <c r="F27" s="58"/>
+      <c r="E27" s="62"/>
+      <c r="F27" s="40"/>
       <c r="G27" s="45"/>
       <c r="H27" s="38"/>
       <c r="I27" s="27"/>
     </row>
     <row r="28" spans="1:9">
-      <c r="A28" s="64"/>
-      <c r="B28" s="62"/>
-      <c r="C28" s="63"/>
+      <c r="A28" s="61"/>
+      <c r="B28" s="59"/>
+      <c r="C28" s="60"/>
       <c r="D28" s="50"/>
-      <c r="E28" s="65"/>
-      <c r="F28" s="58"/>
+      <c r="E28" s="62"/>
+      <c r="F28" s="40"/>
       <c r="G28" s="45"/>
       <c r="H28" s="38"/>
       <c r="I28" s="27"/>
     </row>
     <row r="29" spans="1:9">
-      <c r="A29" s="64"/>
-      <c r="B29" s="62"/>
-      <c r="C29" s="63"/>
+      <c r="A29" s="61"/>
+      <c r="B29" s="59"/>
+      <c r="C29" s="60"/>
       <c r="D29" s="50"/>
-      <c r="E29" s="65"/>
-      <c r="F29" s="58"/>
+      <c r="E29" s="62"/>
+      <c r="F29" s="40"/>
       <c r="G29" s="45"/>
       <c r="H29" s="38"/>
       <c r="I29" s="27"/>
     </row>
     <row r="30" spans="1:9">
-      <c r="A30" s="64"/>
-      <c r="B30" s="62"/>
-      <c r="C30" s="63"/>
+      <c r="A30" s="61"/>
+      <c r="B30" s="59"/>
+      <c r="C30" s="60"/>
       <c r="D30" s="50"/>
-      <c r="E30" s="65"/>
-      <c r="F30" s="58"/>
+      <c r="E30" s="62"/>
+      <c r="F30" s="40"/>
       <c r="G30" s="45"/>
       <c r="H30" s="38"/>
       <c r="I30" s="27"/>
     </row>
     <row r="31" spans="1:9">
-      <c r="A31" s="64"/>
-      <c r="B31" s="62"/>
-      <c r="C31" s="63"/>
-      <c r="D31" s="59"/>
-      <c r="E31" s="67"/>
-      <c r="F31" s="60"/>
+      <c r="A31" s="61"/>
+      <c r="B31" s="59"/>
+      <c r="C31" s="60"/>
+      <c r="D31" s="56"/>
+      <c r="E31" s="64"/>
+      <c r="F31" s="57"/>
       <c r="G31" s="45"/>
       <c r="H31" s="38"/>
       <c r="I31" s="27"/>
     </row>
     <row r="32" spans="1:9">
-      <c r="A32" s="64"/>
-      <c r="B32" s="68"/>
-      <c r="C32" s="62"/>
-      <c r="D32" s="69"/>
-      <c r="E32" s="69"/>
-      <c r="F32" s="70"/>
-      <c r="G32" s="75"/>
+      <c r="A32" s="61"/>
+      <c r="B32" s="65"/>
+      <c r="C32" s="59"/>
+      <c r="D32" s="66"/>
+      <c r="E32" s="66"/>
+      <c r="F32" s="67"/>
+      <c r="G32" s="69"/>
       <c r="H32" s="38"/>
       <c r="I32" s="27"/>
     </row>
     <row r="33" spans="1:9">
-      <c r="A33" s="64"/>
-      <c r="B33" s="68"/>
-      <c r="C33" s="62"/>
-      <c r="D33" s="68"/>
-      <c r="E33" s="68"/>
-      <c r="F33" s="71"/>
-      <c r="G33" s="75"/>
+      <c r="A33" s="61"/>
+      <c r="B33" s="65"/>
+      <c r="C33" s="59"/>
+      <c r="D33" s="65"/>
+      <c r="E33" s="65"/>
+      <c r="F33" s="38"/>
+      <c r="G33" s="69"/>
       <c r="H33" s="38"/>
       <c r="I33" s="27"/>
     </row>
     <row r="34" spans="1:9">
-      <c r="A34" s="61"/>
-      <c r="B34" s="68"/>
-      <c r="C34" s="62"/>
-      <c r="D34" s="68"/>
-      <c r="E34" s="68"/>
+      <c r="A34" s="58"/>
+      <c r="B34" s="65"/>
+      <c r="C34" s="59"/>
+      <c r="D34" s="65"/>
+      <c r="E34" s="65"/>
       <c r="F34" s="38"/>
-      <c r="G34" s="75"/>
+      <c r="G34" s="69"/>
       <c r="H34" s="38"/>
       <c r="I34" s="27"/>
     </row>
     <row r="35" spans="1:9">
-      <c r="A35" s="61"/>
-      <c r="B35" s="68"/>
-      <c r="C35" s="62"/>
-      <c r="D35" s="68"/>
-      <c r="E35" s="68"/>
+      <c r="A35" s="58"/>
+      <c r="B35" s="65"/>
+      <c r="C35" s="59"/>
+      <c r="D35" s="65"/>
+      <c r="E35" s="65"/>
       <c r="F35" s="38"/>
-      <c r="G35" s="75"/>
+      <c r="G35" s="69"/>
       <c r="H35" s="38"/>
       <c r="I35"/>
     </row>
     <row r="36" spans="1:9">
-      <c r="A36" s="61"/>
-      <c r="B36" s="68"/>
-      <c r="C36" s="62"/>
-      <c r="D36" s="68"/>
-      <c r="E36" s="68"/>
+      <c r="A36" s="58"/>
+      <c r="B36" s="65"/>
+      <c r="C36" s="59"/>
+      <c r="D36" s="65"/>
+      <c r="E36" s="65"/>
       <c r="F36" s="38"/>
-      <c r="G36" s="75"/>
+      <c r="G36" s="69"/>
       <c r="H36" s="38"/>
       <c r="I36"/>
     </row>
@@ -3410,13 +3549,13 @@
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="E2">
-    <cfRule type="duplicateValues" dxfId="2" priority="4"/>
+    <cfRule type="duplicateValues" dxfId="4" priority="4"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="E3">
-    <cfRule type="duplicateValues" dxfId="1" priority="3"/>
+    <cfRule type="duplicateValues" dxfId="3" priority="3"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="E4">
-    <cfRule type="duplicateValues" dxfId="0" priority="2"/>
+    <cfRule type="duplicateValues" dxfId="2" priority="2"/>
   </conditionalFormatting>
   <dataValidations count="2">
     <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="A2:A31" xr:uid="{4D257AA8-3FDB-42B7-A450-B3788B0ABB12}">
@@ -3433,15 +3572,15 @@
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{5BD26F43-5C8A-4C67-93F6-3B4E17ED8491}">
   <dimension ref="A1:I43"/>
-  <sheetFormatPr defaultRowHeight="15"/>
+  <sheetFormatPr defaultRowHeight="14.5"/>
   <cols>
-    <col min="2" max="2" width="15.85546875" style="17" customWidth="1"/>
-    <col min="3" max="3" width="18.140625" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="17.5703125" style="17" customWidth="1"/>
-    <col min="5" max="5" width="17.85546875" style="17" customWidth="1"/>
+    <col min="2" max="2" width="15.81640625" style="17" customWidth="1"/>
+    <col min="3" max="3" width="18.1796875" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="17.54296875" style="17" customWidth="1"/>
+    <col min="5" max="5" width="17.81640625" style="17" customWidth="1"/>
     <col min="6" max="6" width="27" customWidth="1"/>
-    <col min="7" max="7" width="20.28515625" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="31.5703125" customWidth="1"/>
+    <col min="7" max="7" width="20.26953125" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="47.26953125" customWidth="1"/>
     <col min="9" max="9" width="21" style="27" customWidth="1"/>
   </cols>
   <sheetData>
@@ -3478,162 +3617,378 @@
       <c r="A2" s="6" t="s">
         <v>9</v>
       </c>
-      <c r="B2" s="6"/>
-      <c r="C2" s="28"/>
-      <c r="D2" s="29"/>
-      <c r="E2" s="18"/>
-      <c r="F2" s="12"/>
-      <c r="G2" s="20"/>
-      <c r="H2" s="22"/>
+      <c r="B2" s="71">
+        <v>45909</v>
+      </c>
+      <c r="C2" s="28">
+        <v>45910</v>
+      </c>
+      <c r="D2" s="29" t="s">
+        <v>10</v>
+      </c>
+      <c r="E2" s="18">
+        <v>3450076927</v>
+      </c>
+      <c r="F2" s="12" t="s">
+        <v>91</v>
+      </c>
+      <c r="G2" s="20" t="s">
+        <v>12</v>
+      </c>
+      <c r="H2" s="15" t="s">
+        <v>92</v>
+      </c>
     </row>
     <row r="3" spans="1:9">
-      <c r="A3" s="6" t="s">
-        <v>9</v>
-      </c>
-      <c r="B3" s="6"/>
-      <c r="C3" s="28"/>
-      <c r="D3" s="29"/>
-      <c r="E3" s="18"/>
-      <c r="F3" s="12"/>
-      <c r="G3" s="26"/>
-      <c r="H3" s="12"/>
+      <c r="A3" s="72" t="s">
+        <v>9</v>
+      </c>
+      <c r="B3" s="73">
+        <v>45905</v>
+      </c>
+      <c r="C3" s="28">
+        <v>45910</v>
+      </c>
+      <c r="D3" s="74">
+        <v>134313690</v>
+      </c>
+      <c r="E3" s="18">
+        <v>3450074530</v>
+      </c>
+      <c r="F3" s="75" t="s">
+        <v>93</v>
+      </c>
+      <c r="G3" s="76" t="s">
+        <v>21</v>
+      </c>
+      <c r="H3" s="79" t="s">
+        <v>94</v>
+      </c>
+      <c r="I3" s="83">
+        <v>45905</v>
+      </c>
     </row>
     <row r="4" spans="1:9">
-      <c r="A4" s="6" t="s">
-        <v>9</v>
-      </c>
-      <c r="B4" s="6"/>
-      <c r="C4" s="28"/>
-      <c r="D4" s="29"/>
-      <c r="E4" s="18"/>
-      <c r="F4" s="12"/>
-      <c r="G4" s="26"/>
-      <c r="H4" s="12"/>
+      <c r="A4" s="72" t="s">
+        <v>9</v>
+      </c>
+      <c r="B4" s="73" t="s">
+        <v>95</v>
+      </c>
+      <c r="C4" s="28">
+        <v>45910</v>
+      </c>
+      <c r="D4" s="74">
+        <v>134304975</v>
+      </c>
+      <c r="E4" s="18">
+        <v>3450073870</v>
+      </c>
+      <c r="F4" s="75" t="s">
+        <v>96</v>
+      </c>
+      <c r="G4" s="76" t="s">
+        <v>24</v>
+      </c>
+      <c r="H4" s="13" t="s">
+        <v>97</v>
+      </c>
+      <c r="I4" s="73">
+        <v>45909</v>
+      </c>
     </row>
     <row r="5" spans="1:9">
-      <c r="A5" s="6" t="s">
-        <v>9</v>
-      </c>
-      <c r="B5" s="6"/>
-      <c r="C5" s="28"/>
-      <c r="D5" s="29"/>
-      <c r="E5" s="18"/>
-      <c r="F5" s="12"/>
-      <c r="G5" s="20"/>
-      <c r="H5" s="15"/>
+      <c r="A5" s="72" t="s">
+        <v>9</v>
+      </c>
+      <c r="B5" s="73">
+        <v>45911</v>
+      </c>
+      <c r="C5" s="28">
+        <v>45910</v>
+      </c>
+      <c r="D5" s="74">
+        <v>134345251</v>
+      </c>
+      <c r="E5" s="18">
+        <v>3450076003</v>
+      </c>
+      <c r="F5" s="75" t="s">
+        <v>98</v>
+      </c>
+      <c r="G5" s="76" t="s">
+        <v>24</v>
+      </c>
+      <c r="H5" s="13" t="s">
+        <v>97</v>
+      </c>
+      <c r="I5" s="73">
+        <v>45909</v>
+      </c>
     </row>
     <row r="6" spans="1:9">
-      <c r="A6" s="6" t="s">
-        <v>9</v>
-      </c>
-      <c r="B6" s="6"/>
-      <c r="C6" s="28"/>
-      <c r="D6" s="29"/>
-      <c r="E6" s="18"/>
-      <c r="F6" s="12"/>
-      <c r="G6" s="20"/>
-      <c r="H6" s="9"/>
+      <c r="A6" s="72" t="s">
+        <v>9</v>
+      </c>
+      <c r="B6" s="73">
+        <v>45909</v>
+      </c>
+      <c r="C6" s="28">
+        <v>45910</v>
+      </c>
+      <c r="D6" s="74">
+        <v>134354096</v>
+      </c>
+      <c r="E6" s="18">
+        <v>3450076290</v>
+      </c>
+      <c r="F6" s="75" t="s">
+        <v>30</v>
+      </c>
+      <c r="G6" s="76" t="s">
+        <v>31</v>
+      </c>
+      <c r="H6" s="13" t="s">
+        <v>32</v>
+      </c>
+      <c r="I6" s="73">
+        <v>45909</v>
+      </c>
     </row>
     <row r="7" spans="1:9">
-      <c r="A7" s="6" t="s">
-        <v>9</v>
-      </c>
-      <c r="B7" s="6"/>
-      <c r="C7" s="28"/>
-      <c r="D7" s="29"/>
-      <c r="E7" s="18"/>
-      <c r="F7" s="12"/>
-      <c r="G7" s="20"/>
-      <c r="H7" s="9"/>
-    </row>
-    <row r="8" spans="1:9">
-      <c r="A8" s="6" t="s">
-        <v>9</v>
-      </c>
-      <c r="B8" s="6"/>
-      <c r="C8" s="28"/>
-      <c r="D8" s="29"/>
-      <c r="E8" s="18"/>
-      <c r="F8" s="12"/>
-      <c r="G8" s="20"/>
-      <c r="H8" s="9"/>
+      <c r="A7" s="72" t="s">
+        <v>9</v>
+      </c>
+      <c r="B7" s="73" t="s">
+        <v>99</v>
+      </c>
+      <c r="C7" s="28">
+        <v>45910</v>
+      </c>
+      <c r="D7" s="74">
+        <v>134170423</v>
+      </c>
+      <c r="E7" s="18">
+        <v>3450066720</v>
+      </c>
+      <c r="F7" s="75" t="s">
+        <v>100</v>
+      </c>
+      <c r="G7" s="76" t="s">
+        <v>12</v>
+      </c>
+      <c r="H7" s="13" t="s">
+        <v>101</v>
+      </c>
+      <c r="I7" s="73">
+        <v>45902</v>
+      </c>
+    </row>
+    <row r="8" spans="1:9" s="87" customFormat="1" ht="43.5">
+      <c r="A8" s="82" t="s">
+        <v>9</v>
+      </c>
+      <c r="B8" s="83" t="s">
+        <v>99</v>
+      </c>
+      <c r="C8" s="28">
+        <v>45910</v>
+      </c>
+      <c r="D8" s="84">
+        <v>134174713</v>
+      </c>
+      <c r="E8" s="81">
+        <v>3450067027</v>
+      </c>
+      <c r="F8" s="85" t="s">
+        <v>72</v>
+      </c>
+      <c r="G8" s="81" t="s">
+        <v>68</v>
+      </c>
+      <c r="H8" s="86" t="s">
+        <v>102</v>
+      </c>
+      <c r="I8" s="83" t="s">
+        <v>103</v>
+      </c>
     </row>
     <row r="9" spans="1:9">
-      <c r="A9" s="6" t="s">
-        <v>9</v>
-      </c>
-      <c r="B9" s="6"/>
-      <c r="C9" s="28"/>
-      <c r="D9" s="29"/>
-      <c r="E9" s="18"/>
-      <c r="F9" s="12"/>
-      <c r="G9" s="20"/>
-      <c r="H9" s="9"/>
+      <c r="A9" s="72" t="s">
+        <v>9</v>
+      </c>
+      <c r="B9" s="73" t="s">
+        <v>99</v>
+      </c>
+      <c r="C9" s="28">
+        <v>45910</v>
+      </c>
+      <c r="D9" s="74">
+        <v>134175439</v>
+      </c>
+      <c r="E9" s="18">
+        <v>3450067082</v>
+      </c>
+      <c r="F9" s="75" t="s">
+        <v>104</v>
+      </c>
+      <c r="G9" s="76" t="s">
+        <v>12</v>
+      </c>
+      <c r="H9" s="13" t="s">
+        <v>105</v>
+      </c>
+      <c r="I9" s="73">
+        <v>45905</v>
+      </c>
     </row>
     <row r="10" spans="1:9">
-      <c r="A10" s="6" t="s">
-        <v>9</v>
-      </c>
-      <c r="B10" s="6"/>
-      <c r="C10" s="28"/>
-      <c r="D10" s="25"/>
-      <c r="E10" s="18"/>
-      <c r="F10" s="12"/>
-      <c r="G10" s="24"/>
-      <c r="H10" s="9"/>
+      <c r="A10" s="72" t="s">
+        <v>9</v>
+      </c>
+      <c r="B10" s="73">
+        <v>45910</v>
+      </c>
+      <c r="C10" s="28">
+        <v>45910</v>
+      </c>
+      <c r="D10" s="74">
+        <v>134374124</v>
+      </c>
+      <c r="E10" s="18">
+        <v>3450077268</v>
+      </c>
+      <c r="F10" s="75" t="s">
+        <v>82</v>
+      </c>
+      <c r="G10" s="76" t="s">
+        <v>31</v>
+      </c>
+      <c r="H10" s="13" t="s">
+        <v>32</v>
+      </c>
+      <c r="I10" s="73">
+        <v>45910</v>
+      </c>
     </row>
     <row r="11" spans="1:9">
-      <c r="A11" s="6" t="s">
-        <v>9</v>
-      </c>
-      <c r="B11" s="6"/>
-      <c r="C11" s="28"/>
-      <c r="D11" s="29"/>
-      <c r="E11" s="18"/>
-      <c r="F11" s="12"/>
-      <c r="G11" s="20"/>
-      <c r="H11" s="9"/>
+      <c r="A11" s="72" t="s">
+        <v>9</v>
+      </c>
+      <c r="B11" s="73">
+        <v>45901</v>
+      </c>
+      <c r="C11" s="28">
+        <v>45910</v>
+      </c>
+      <c r="D11" s="74">
+        <v>134230537</v>
+      </c>
+      <c r="E11" s="18">
+        <v>3450070140</v>
+      </c>
+      <c r="F11" s="75" t="s">
+        <v>106</v>
+      </c>
+      <c r="G11" s="76" t="s">
+        <v>24</v>
+      </c>
+      <c r="H11" s="13" t="s">
+        <v>97</v>
+      </c>
+      <c r="I11" s="73">
+        <v>45909</v>
+      </c>
     </row>
     <row r="12" spans="1:9">
-      <c r="A12" s="6" t="s">
-        <v>9</v>
-      </c>
-      <c r="B12" s="6"/>
-      <c r="C12" s="28"/>
-      <c r="D12" s="25"/>
-      <c r="E12" s="18"/>
-      <c r="F12" s="12"/>
-      <c r="G12" s="24"/>
-      <c r="H12" s="9"/>
+      <c r="A12" s="72" t="s">
+        <v>9</v>
+      </c>
+      <c r="B12" s="73" t="s">
+        <v>107</v>
+      </c>
+      <c r="C12" s="28">
+        <v>45910</v>
+      </c>
+      <c r="D12" s="74">
+        <v>134188240</v>
+      </c>
+      <c r="E12" s="18">
+        <v>3450067710</v>
+      </c>
+      <c r="F12" s="75" t="s">
+        <v>108</v>
+      </c>
+      <c r="G12" s="76" t="s">
+        <v>24</v>
+      </c>
+      <c r="H12" s="13" t="s">
+        <v>97</v>
+      </c>
+      <c r="I12" s="73">
+        <v>45909</v>
+      </c>
     </row>
     <row r="13" spans="1:9">
-      <c r="A13" s="6" t="s">
-        <v>9</v>
-      </c>
-      <c r="B13" s="6"/>
-      <c r="C13" s="28"/>
-      <c r="D13" s="29"/>
-      <c r="E13" s="18"/>
-      <c r="F13" s="12"/>
-      <c r="G13" s="20"/>
-      <c r="H13" s="9"/>
-    </row>
-    <row r="14" spans="1:9">
-      <c r="A14" s="6" t="s">
-        <v>9</v>
-      </c>
-      <c r="B14" s="6"/>
-      <c r="C14" s="28"/>
-      <c r="D14" s="29"/>
-      <c r="E14" s="18"/>
-      <c r="F14" s="12"/>
-      <c r="G14" s="20"/>
-      <c r="H14" s="9"/>
+      <c r="A13" s="72" t="s">
+        <v>9</v>
+      </c>
+      <c r="B13" s="73">
+        <v>45910</v>
+      </c>
+      <c r="C13" s="28">
+        <v>45910</v>
+      </c>
+      <c r="D13" s="74">
+        <v>134383118</v>
+      </c>
+      <c r="E13" s="18">
+        <v>3450077818</v>
+      </c>
+      <c r="F13" s="75" t="s">
+        <v>109</v>
+      </c>
+      <c r="G13" s="76" t="s">
+        <v>24</v>
+      </c>
+      <c r="H13" s="13" t="s">
+        <v>110</v>
+      </c>
+      <c r="I13" s="73">
+        <v>45910</v>
+      </c>
+    </row>
+    <row r="14" spans="1:9" s="87" customFormat="1" ht="29">
+      <c r="A14" s="82" t="s">
+        <v>9</v>
+      </c>
+      <c r="B14" s="83" t="s">
+        <v>111</v>
+      </c>
+      <c r="C14" s="28">
+        <v>45910</v>
+      </c>
+      <c r="D14" s="84">
+        <v>134272786</v>
+      </c>
+      <c r="E14" s="81">
+        <v>3450072461</v>
+      </c>
+      <c r="F14" s="85" t="s">
+        <v>112</v>
+      </c>
+      <c r="G14" s="81" t="s">
+        <v>68</v>
+      </c>
+      <c r="H14" s="86" t="s">
+        <v>113</v>
+      </c>
+      <c r="I14" s="83">
+        <v>45905</v>
+      </c>
     </row>
     <row r="15" spans="1:9">
-      <c r="A15" s="6" t="s">
-        <v>9</v>
-      </c>
+      <c r="A15" s="6"/>
       <c r="B15" s="6"/>
       <c r="C15" s="28"/>
       <c r="D15" s="29"/>
@@ -3643,9 +3998,7 @@
       <c r="H15" s="9"/>
     </row>
     <row r="16" spans="1:9">
-      <c r="A16" s="6" t="s">
-        <v>9</v>
-      </c>
+      <c r="A16" s="6"/>
       <c r="B16" s="6"/>
       <c r="C16" s="28"/>
       <c r="D16" s="29"/>
@@ -3926,9 +4279,12 @@
     </row>
   </sheetData>
   <conditionalFormatting sqref="B1:C1">
-    <cfRule type="notContainsBlanks" priority="2">
+    <cfRule type="notContainsBlanks" priority="4">
       <formula>LEN(TRIM(B1))&gt;0</formula>
     </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="D3:D14">
+    <cfRule type="duplicateValues" dxfId="1" priority="1"/>
   </conditionalFormatting>
   <dataValidations count="3">
     <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="A17:A36" xr:uid="{F535CD1B-7EC8-4CD4-9DE2-4943F25AAD12}">
@@ -3937,7 +4293,7 @@
     <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="G2:G36" xr:uid="{9AF2051F-77D3-4586-8B0A-6A9380E3F6D6}">
       <formula1>"Vistoria Frustrada;,Vistoria Recusada,Bônus;,Desistência;,Inadimplência;,Política de Aceitação;,Duplicidade;,Demais Motivos,Falta de Vistoria;,"</formula1>
     </dataValidation>
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="A2:B16" xr:uid="{E44F5A38-408F-4061-943F-128F4E144D8E}">
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="B15:B16 A2:A16" xr:uid="{E44F5A38-408F-4061-943F-128F4E144D8E}">
       <formula1>$J$2</formula1>
     </dataValidation>
   </dataValidations>
@@ -3947,18 +4303,18 @@
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{9BF216D7-F2B3-4C54-A7B9-7048B06C2C75}">
-  <dimension ref="A1:I55"/>
-  <sheetFormatPr defaultRowHeight="15"/>
+  <dimension ref="A1:I52"/>
+  <sheetFormatPr defaultRowHeight="14.5"/>
   <cols>
-    <col min="1" max="1" width="14.7109375" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="15.5703125" customWidth="1"/>
-    <col min="3" max="3" width="18.140625" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="14.7265625" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="18.453125" customWidth="1"/>
+    <col min="3" max="3" width="18.1796875" bestFit="1" customWidth="1"/>
     <col min="4" max="4" width="26" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="29.5703125" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="36.5703125" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="20.28515625" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="36.5703125" bestFit="1" customWidth="1"/>
-    <col min="9" max="9" width="18.7109375" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="29.54296875" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="36.54296875" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="20.26953125" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="54.26953125" customWidth="1"/>
+    <col min="9" max="9" width="18.7265625" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:9">
@@ -3991,331 +4347,335 @@
       </c>
     </row>
     <row r="2" spans="1:9">
-      <c r="A2" s="6" t="s">
-        <v>9</v>
-      </c>
-      <c r="B2" s="7"/>
-      <c r="C2" s="7"/>
-      <c r="D2" s="29"/>
-      <c r="E2" s="8"/>
-      <c r="F2" s="12"/>
-      <c r="G2" s="30"/>
-      <c r="H2" s="9"/>
-      <c r="I2" s="27"/>
+      <c r="A2" s="72" t="s">
+        <v>9</v>
+      </c>
+      <c r="B2" s="73"/>
+      <c r="C2" s="73"/>
+      <c r="D2" s="74"/>
+      <c r="E2" s="18"/>
+      <c r="F2" s="75"/>
+      <c r="G2" s="76"/>
+      <c r="H2" s="79"/>
+      <c r="I2" s="73"/>
     </row>
     <row r="3" spans="1:9">
-      <c r="A3" s="6" t="s">
-        <v>9</v>
-      </c>
-      <c r="B3" s="7"/>
-      <c r="C3" s="7"/>
-      <c r="D3" s="29"/>
-      <c r="E3" s="8"/>
-      <c r="F3" s="12"/>
-      <c r="G3" s="30"/>
-      <c r="H3" s="9"/>
-      <c r="I3" s="27"/>
+      <c r="A3" s="72" t="s">
+        <v>9</v>
+      </c>
+      <c r="B3" s="73"/>
+      <c r="C3" s="73"/>
+      <c r="D3" s="74"/>
+      <c r="E3" s="18"/>
+      <c r="F3" s="75"/>
+      <c r="G3" s="76"/>
+      <c r="H3" s="13"/>
+      <c r="I3" s="73"/>
     </row>
     <row r="4" spans="1:9">
-      <c r="A4" s="6" t="s">
-        <v>9</v>
-      </c>
-      <c r="B4" s="7"/>
-      <c r="C4" s="7"/>
-      <c r="D4" s="29"/>
-      <c r="E4" s="8"/>
-      <c r="F4" s="12"/>
-      <c r="G4" s="30"/>
-      <c r="H4" s="9"/>
-      <c r="I4" s="27"/>
+      <c r="A4" s="72" t="s">
+        <v>9</v>
+      </c>
+      <c r="B4" s="73"/>
+      <c r="C4" s="73"/>
+      <c r="D4" s="74"/>
+      <c r="E4" s="18"/>
+      <c r="F4" s="75"/>
+      <c r="G4" s="76"/>
+      <c r="H4" s="13"/>
+      <c r="I4" s="73"/>
     </row>
     <row r="5" spans="1:9">
-      <c r="A5" s="6" t="s">
-        <v>9</v>
-      </c>
-      <c r="B5" s="7"/>
-      <c r="C5" s="7"/>
-      <c r="D5" s="29"/>
-      <c r="E5" s="8"/>
-      <c r="F5" s="12"/>
-      <c r="G5" s="30"/>
-      <c r="H5" s="9"/>
-      <c r="I5" s="27"/>
+      <c r="A5" s="72" t="s">
+        <v>9</v>
+      </c>
+      <c r="B5" s="73"/>
+      <c r="C5" s="73"/>
+      <c r="D5" s="74"/>
+      <c r="E5" s="18"/>
+      <c r="F5" s="75"/>
+      <c r="G5" s="76"/>
+      <c r="H5" s="13"/>
+      <c r="I5" s="73"/>
     </row>
     <row r="6" spans="1:9">
-      <c r="A6" s="6" t="s">
-        <v>9</v>
-      </c>
-      <c r="B6" s="7"/>
-      <c r="C6" s="7"/>
-      <c r="D6" s="29"/>
-      <c r="E6" s="8"/>
-      <c r="F6" s="12"/>
-      <c r="G6" s="30"/>
-      <c r="H6" s="9"/>
-      <c r="I6" s="27"/>
+      <c r="A6" s="72" t="s">
+        <v>9</v>
+      </c>
+      <c r="B6" s="73"/>
+      <c r="C6" s="73"/>
+      <c r="D6" s="74"/>
+      <c r="E6" s="18"/>
+      <c r="F6" s="75"/>
+      <c r="G6" s="76"/>
+      <c r="H6" s="13"/>
+      <c r="I6" s="73"/>
     </row>
     <row r="7" spans="1:9">
-      <c r="A7" s="6" t="s">
-        <v>9</v>
-      </c>
-      <c r="B7" s="7"/>
-      <c r="C7" s="7"/>
-      <c r="D7" s="29"/>
-      <c r="E7" s="8"/>
-      <c r="F7" s="12"/>
-      <c r="G7" s="30"/>
-      <c r="H7" s="9"/>
-      <c r="I7" s="27"/>
+      <c r="A7" s="72" t="s">
+        <v>9</v>
+      </c>
+      <c r="B7" s="73"/>
+      <c r="C7" s="73"/>
+      <c r="D7" s="74"/>
+      <c r="E7" s="18"/>
+      <c r="F7" s="75"/>
+      <c r="G7" s="81"/>
+      <c r="H7" s="80"/>
+      <c r="I7" s="73"/>
     </row>
     <row r="8" spans="1:9">
-      <c r="A8" s="6" t="s">
-        <v>9</v>
-      </c>
-      <c r="B8" s="7"/>
-      <c r="C8" s="7"/>
-      <c r="D8" s="29"/>
-      <c r="E8" s="8"/>
-      <c r="F8" s="12"/>
-      <c r="G8" s="30"/>
-      <c r="H8" s="9"/>
-      <c r="I8" s="27"/>
+      <c r="A8" s="72" t="s">
+        <v>9</v>
+      </c>
+      <c r="B8" s="73"/>
+      <c r="C8" s="73"/>
+      <c r="D8" s="74"/>
+      <c r="E8" s="18"/>
+      <c r="F8" s="75"/>
+      <c r="G8" s="76"/>
+      <c r="H8" s="13"/>
+      <c r="I8" s="73"/>
     </row>
     <row r="9" spans="1:9">
-      <c r="A9" s="6" t="s">
-        <v>9</v>
-      </c>
-      <c r="B9" s="7"/>
-      <c r="C9" s="7"/>
-      <c r="D9" s="29"/>
-      <c r="E9" s="8"/>
-      <c r="F9" s="12"/>
-      <c r="G9" s="30"/>
-      <c r="H9" s="9"/>
-      <c r="I9" s="27"/>
+      <c r="A9" s="72" t="s">
+        <v>9</v>
+      </c>
+      <c r="B9" s="73"/>
+      <c r="C9" s="73"/>
+      <c r="D9" s="74"/>
+      <c r="E9" s="18"/>
+      <c r="F9" s="75"/>
+      <c r="G9" s="76"/>
+      <c r="H9" s="13"/>
+      <c r="I9" s="73"/>
     </row>
     <row r="10" spans="1:9">
-      <c r="A10" s="6" t="s">
-        <v>9</v>
-      </c>
-      <c r="B10" s="7"/>
-      <c r="C10" s="7"/>
-      <c r="D10" s="29"/>
-      <c r="E10" s="8"/>
-      <c r="F10" s="12"/>
-      <c r="G10" s="30"/>
-      <c r="H10" s="9"/>
-      <c r="I10" s="27"/>
+      <c r="A10" s="72" t="s">
+        <v>9</v>
+      </c>
+      <c r="B10" s="73"/>
+      <c r="C10" s="73"/>
+      <c r="D10" s="74"/>
+      <c r="E10" s="18"/>
+      <c r="F10" s="75"/>
+      <c r="G10" s="76"/>
+      <c r="H10" s="13"/>
+      <c r="I10" s="73"/>
     </row>
     <row r="11" spans="1:9">
-      <c r="A11" s="6" t="s">
-        <v>9</v>
-      </c>
-      <c r="B11" s="7"/>
-      <c r="C11" s="7"/>
-      <c r="D11" s="29"/>
-      <c r="E11" s="8"/>
-      <c r="F11" s="12"/>
-      <c r="G11" s="30"/>
-      <c r="H11" s="9"/>
-      <c r="I11" s="27"/>
+      <c r="A11" s="72" t="s">
+        <v>9</v>
+      </c>
+      <c r="B11" s="73"/>
+      <c r="C11" s="73"/>
+      <c r="D11" s="74"/>
+      <c r="E11" s="18"/>
+      <c r="F11" s="75"/>
+      <c r="G11" s="76"/>
+      <c r="H11" s="13"/>
+      <c r="I11" s="73"/>
     </row>
     <row r="12" spans="1:9">
-      <c r="A12" s="6" t="s">
-        <v>9</v>
-      </c>
-      <c r="B12" s="7"/>
-      <c r="C12" s="7"/>
-      <c r="D12" s="29"/>
-      <c r="E12" s="8"/>
-      <c r="F12" s="12"/>
-      <c r="G12" s="30"/>
-      <c r="H12" s="9"/>
-      <c r="I12" s="27"/>
+      <c r="A12" s="72" t="s">
+        <v>9</v>
+      </c>
+      <c r="B12" s="73"/>
+      <c r="C12" s="73"/>
+      <c r="D12" s="74"/>
+      <c r="E12" s="18"/>
+      <c r="F12" s="75"/>
+      <c r="G12" s="76"/>
+      <c r="H12" s="13"/>
+      <c r="I12" s="73"/>
     </row>
     <row r="13" spans="1:9">
-      <c r="A13" s="6" t="s">
-        <v>9</v>
-      </c>
-      <c r="B13" s="7"/>
-      <c r="C13" s="7"/>
-      <c r="D13" s="29"/>
-      <c r="E13" s="8"/>
-      <c r="F13" s="12"/>
-      <c r="G13" s="30"/>
-      <c r="H13" s="9"/>
-      <c r="I13" s="27"/>
+      <c r="A13" s="72" t="s">
+        <v>9</v>
+      </c>
+      <c r="B13" s="73"/>
+      <c r="C13" s="73"/>
+      <c r="D13" s="74"/>
+      <c r="E13" s="18"/>
+      <c r="F13" s="75"/>
+      <c r="G13" s="81"/>
+      <c r="H13" s="80"/>
+      <c r="I13" s="73"/>
     </row>
     <row r="14" spans="1:9">
-      <c r="A14" s="6" t="s">
-        <v>9</v>
-      </c>
-      <c r="B14" s="7"/>
-      <c r="C14" s="7"/>
-      <c r="D14" s="29"/>
-      <c r="E14" s="8"/>
+      <c r="A14" s="72"/>
+      <c r="B14" s="73"/>
+      <c r="C14" s="73"/>
+      <c r="D14" s="18"/>
+      <c r="E14" s="18"/>
       <c r="F14" s="12"/>
-      <c r="G14" s="30"/>
-      <c r="H14" s="9"/>
-      <c r="I14" s="27"/>
+      <c r="G14" s="72"/>
+      <c r="H14" s="13"/>
+      <c r="I14" s="73"/>
     </row>
     <row r="15" spans="1:9">
-      <c r="A15" s="6" t="s">
-        <v>9</v>
-      </c>
-      <c r="B15" s="7"/>
-      <c r="C15" s="7"/>
-      <c r="D15" s="29"/>
-      <c r="E15" s="8"/>
+      <c r="A15" s="72"/>
+      <c r="B15" s="73"/>
+      <c r="C15" s="73"/>
+      <c r="D15" s="18"/>
+      <c r="E15" s="18"/>
       <c r="F15" s="12"/>
-      <c r="G15" s="30"/>
-      <c r="H15" s="9"/>
-      <c r="I15" s="27"/>
+      <c r="G15" s="72"/>
+      <c r="H15" s="13"/>
+      <c r="I15" s="73"/>
     </row>
     <row r="16" spans="1:9">
-      <c r="A16" s="6"/>
-      <c r="B16" s="7"/>
-      <c r="C16" s="7"/>
-      <c r="D16" s="29"/>
-      <c r="E16" s="8"/>
-      <c r="F16" s="12"/>
-      <c r="G16" s="30"/>
-      <c r="H16" s="9"/>
-      <c r="I16" s="27"/>
+      <c r="A16" s="72"/>
+      <c r="B16" s="18"/>
+      <c r="C16" s="73"/>
+      <c r="D16" s="18"/>
+      <c r="E16" s="18"/>
+      <c r="F16" s="13"/>
+      <c r="G16" s="72"/>
+      <c r="H16" s="13"/>
+      <c r="I16" s="73"/>
     </row>
     <row r="17" spans="1:9">
-      <c r="A17" s="6"/>
-      <c r="B17" s="7"/>
-      <c r="C17" s="7"/>
-      <c r="D17" s="8"/>
-      <c r="E17" s="14"/>
-      <c r="F17" s="12"/>
-      <c r="G17" s="6"/>
-      <c r="H17" s="9"/>
-      <c r="I17" s="27"/>
+      <c r="A17" s="72"/>
+      <c r="B17" s="18"/>
+      <c r="C17" s="73"/>
+      <c r="D17" s="18"/>
+      <c r="E17" s="18"/>
+      <c r="F17" s="13"/>
+      <c r="G17" s="72"/>
+      <c r="H17" s="13"/>
+      <c r="I17" s="73"/>
     </row>
     <row r="18" spans="1:9">
-      <c r="A18" s="6"/>
-      <c r="B18" s="7"/>
-      <c r="C18" s="7"/>
-      <c r="D18" s="8"/>
-      <c r="E18" s="14"/>
-      <c r="F18" s="12"/>
-      <c r="G18" s="6"/>
-      <c r="H18" s="9"/>
-      <c r="I18" s="27"/>
+      <c r="A18" s="72"/>
+      <c r="B18" s="18"/>
+      <c r="C18" s="73"/>
+      <c r="D18" s="18"/>
+      <c r="E18" s="18"/>
+      <c r="F18" s="13"/>
+      <c r="G18" s="72"/>
+      <c r="H18" s="13"/>
+      <c r="I18" s="13"/>
     </row>
     <row r="19" spans="1:9">
-      <c r="A19" s="6"/>
-      <c r="B19" s="8"/>
-      <c r="C19" s="7"/>
-      <c r="D19" s="8"/>
-      <c r="E19" s="14"/>
+      <c r="A19" s="72"/>
+      <c r="B19" s="18"/>
+      <c r="C19" s="73"/>
+      <c r="D19" s="18"/>
+      <c r="E19" s="18"/>
       <c r="F19" s="13"/>
-      <c r="G19" s="6"/>
-      <c r="H19" s="9"/>
-      <c r="I19" s="27"/>
+      <c r="G19" s="72"/>
+      <c r="H19" s="13"/>
+      <c r="I19" s="13"/>
     </row>
     <row r="20" spans="1:9">
-      <c r="A20" s="6"/>
-      <c r="B20" s="8"/>
-      <c r="C20" s="7"/>
-      <c r="D20" s="8"/>
-      <c r="E20" s="8"/>
-      <c r="F20" s="15"/>
-      <c r="G20" s="6"/>
-      <c r="H20" s="9"/>
-      <c r="I20" s="27"/>
+      <c r="A20" s="72"/>
+      <c r="B20" s="18"/>
+      <c r="C20" s="73"/>
+      <c r="D20" s="18"/>
+      <c r="E20" s="18"/>
+      <c r="F20" s="13"/>
+      <c r="G20" s="72"/>
+      <c r="H20" s="13"/>
+      <c r="I20" s="13"/>
     </row>
     <row r="21" spans="1:9">
-      <c r="A21" s="6"/>
-      <c r="B21" s="8"/>
-      <c r="C21" s="7"/>
-      <c r="D21" s="8"/>
-      <c r="E21" s="8"/>
-      <c r="F21" s="9"/>
-      <c r="G21" s="6"/>
-      <c r="H21" s="9"/>
+      <c r="A21" s="72"/>
+      <c r="B21" s="18"/>
+      <c r="C21" s="73"/>
+      <c r="D21" s="18"/>
+      <c r="E21" s="18"/>
+      <c r="F21" s="13"/>
+      <c r="G21" s="72"/>
+      <c r="H21" s="13"/>
+      <c r="I21" s="13"/>
     </row>
     <row r="22" spans="1:9">
-      <c r="A22" s="6"/>
-      <c r="B22" s="8"/>
-      <c r="C22" s="7"/>
-      <c r="D22" s="8"/>
-      <c r="E22" s="8"/>
-      <c r="F22" s="9"/>
-      <c r="G22" s="6"/>
-      <c r="H22" s="9"/>
+      <c r="A22" s="72"/>
+      <c r="B22" s="18"/>
+      <c r="C22" s="73"/>
+      <c r="D22" s="18"/>
+      <c r="E22" s="18"/>
+      <c r="F22" s="13"/>
+      <c r="G22" s="72"/>
+      <c r="H22" s="13"/>
+      <c r="I22" s="13"/>
     </row>
     <row r="23" spans="1:9">
-      <c r="A23" s="6"/>
-      <c r="B23" s="8"/>
-      <c r="C23" s="7"/>
-      <c r="D23" s="8"/>
-      <c r="E23" s="8"/>
-      <c r="F23" s="9"/>
-      <c r="G23" s="6"/>
-      <c r="H23" s="9"/>
+      <c r="A23" s="72"/>
+      <c r="B23" s="18"/>
+      <c r="C23" s="73"/>
+      <c r="D23" s="18"/>
+      <c r="E23" s="18"/>
+      <c r="F23" s="13"/>
+      <c r="G23" s="72"/>
+      <c r="H23" s="13"/>
+      <c r="I23" s="13"/>
     </row>
     <row r="24" spans="1:9">
-      <c r="A24" s="6"/>
-      <c r="B24" s="8"/>
-      <c r="C24" s="7"/>
-      <c r="D24" s="8"/>
-      <c r="E24" s="8"/>
-      <c r="F24" s="9"/>
-      <c r="G24" s="6"/>
-      <c r="H24" s="9"/>
+      <c r="A24" s="72"/>
+      <c r="B24" s="18"/>
+      <c r="C24" s="73"/>
+      <c r="D24" s="18"/>
+      <c r="E24" s="18"/>
+      <c r="F24" s="13"/>
+      <c r="G24" s="72"/>
+      <c r="H24" s="13"/>
+      <c r="I24" s="13"/>
     </row>
     <row r="25" spans="1:9">
-      <c r="A25" s="6"/>
-      <c r="B25" s="8"/>
-      <c r="C25" s="7"/>
-      <c r="D25" s="8"/>
-      <c r="E25" s="8"/>
-      <c r="F25" s="9"/>
-      <c r="G25" s="6"/>
-      <c r="H25" s="9"/>
+      <c r="A25" s="72"/>
+      <c r="B25" s="18"/>
+      <c r="C25" s="73"/>
+      <c r="D25" s="18"/>
+      <c r="E25" s="18"/>
+      <c r="F25" s="13"/>
+      <c r="G25" s="72"/>
+      <c r="H25" s="13"/>
+      <c r="I25" s="13"/>
     </row>
     <row r="26" spans="1:9">
-      <c r="A26" s="6"/>
-      <c r="B26" s="8"/>
-      <c r="C26" s="7"/>
-      <c r="D26" s="8"/>
-      <c r="E26" s="8"/>
-      <c r="F26" s="9"/>
-      <c r="G26" s="6"/>
-      <c r="H26" s="9"/>
+      <c r="A26" s="72"/>
+      <c r="B26" s="18"/>
+      <c r="C26" s="73"/>
+      <c r="D26" s="18"/>
+      <c r="E26" s="18"/>
+      <c r="F26" s="13"/>
+      <c r="G26" s="72"/>
+      <c r="H26" s="13"/>
+      <c r="I26" s="13"/>
     </row>
     <row r="27" spans="1:9">
-      <c r="A27" s="6"/>
-      <c r="B27" s="8"/>
-      <c r="C27" s="7"/>
-      <c r="D27" s="8"/>
-      <c r="E27" s="8"/>
-      <c r="F27" s="9"/>
-      <c r="G27" s="6"/>
-      <c r="H27" s="9"/>
+      <c r="A27" s="72"/>
+      <c r="B27" s="18"/>
+      <c r="C27" s="73"/>
+      <c r="D27" s="18"/>
+      <c r="E27" s="18"/>
+      <c r="F27" s="13"/>
+      <c r="G27" s="72"/>
+      <c r="H27" s="13"/>
+      <c r="I27" s="13"/>
     </row>
     <row r="28" spans="1:9">
-      <c r="A28" s="6"/>
-      <c r="B28" s="8"/>
-      <c r="C28" s="7"/>
-      <c r="D28" s="8"/>
-      <c r="E28" s="8"/>
-      <c r="F28" s="9"/>
-      <c r="G28" s="6"/>
-      <c r="H28" s="9"/>
+      <c r="A28" s="72"/>
+      <c r="B28" s="18"/>
+      <c r="C28" s="73"/>
+      <c r="D28" s="18"/>
+      <c r="E28" s="18"/>
+      <c r="F28" s="13"/>
+      <c r="G28" s="72"/>
+      <c r="H28" s="13"/>
+      <c r="I28" s="13"/>
     </row>
     <row r="29" spans="1:9">
-      <c r="A29" s="6"/>
-      <c r="B29" s="8"/>
-      <c r="C29" s="7"/>
-      <c r="D29" s="8"/>
-      <c r="E29" s="8"/>
-      <c r="F29" s="9"/>
-      <c r="G29" s="6"/>
-      <c r="H29" s="9"/>
+      <c r="A29" s="77"/>
+      <c r="B29" s="23"/>
+      <c r="C29" s="78"/>
+      <c r="D29" s="23"/>
+      <c r="E29" s="23"/>
+      <c r="F29" s="15"/>
+      <c r="G29" s="77"/>
+      <c r="H29" s="15"/>
     </row>
     <row r="30" spans="1:9">
       <c r="A30" s="6"/>
@@ -4547,47 +4907,20 @@
       <c r="G52" s="6"/>
       <c r="H52" s="9"/>
     </row>
-    <row r="53" spans="1:8">
-      <c r="A53" s="6"/>
-      <c r="B53" s="8"/>
-      <c r="C53" s="7"/>
-      <c r="D53" s="8"/>
-      <c r="E53" s="8"/>
-      <c r="F53" s="9"/>
-      <c r="G53" s="6"/>
-      <c r="H53" s="9"/>
-    </row>
-    <row r="54" spans="1:8">
-      <c r="A54" s="6"/>
-      <c r="B54" s="8"/>
-      <c r="C54" s="7"/>
-      <c r="D54" s="8"/>
-      <c r="E54" s="8"/>
-      <c r="F54" s="9"/>
-      <c r="G54" s="6"/>
-      <c r="H54" s="9"/>
-    </row>
-    <row r="55" spans="1:8">
-      <c r="A55" s="6"/>
-      <c r="B55" s="8"/>
-      <c r="C55" s="7"/>
-      <c r="D55" s="8"/>
-      <c r="E55" s="8"/>
-      <c r="F55" s="9"/>
-      <c r="G55" s="6"/>
-      <c r="H55" s="9"/>
-    </row>
   </sheetData>
   <conditionalFormatting sqref="B1:C1">
-    <cfRule type="notContainsBlanks" priority="2">
+    <cfRule type="notContainsBlanks" priority="3">
       <formula>LEN(TRIM(B1))&gt;0</formula>
     </cfRule>
   </conditionalFormatting>
+  <conditionalFormatting sqref="D1:D1048576">
+    <cfRule type="duplicateValues" dxfId="0" priority="1"/>
+  </conditionalFormatting>
   <dataValidations count="2">
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="A2:A18" xr:uid="{69840FBE-03D6-48CB-B553-2E7186E1B4BD}">
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="A2:A15" xr:uid="{69840FBE-03D6-48CB-B553-2E7186E1B4BD}">
       <formula1>$J$2</formula1>
     </dataValidation>
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="G2:G41" xr:uid="{AF5C7196-9DAE-4339-82D4-9412023E2B2A}">
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="G2:G38" xr:uid="{AF5C7196-9DAE-4339-82D4-9412023E2B2A}">
       <formula1>"Vistoria Frustrada;,Vistoria Recusada,Bônus;,Desistência;,Inadimplência;,Política de Aceitação;,Duplicidade;,Demais Motivos,Falta de Vistoria;,"</formula1>
     </dataValidation>
   </dataValidations>
@@ -4598,17 +4931,17 @@
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{43D38813-FAE5-45C6-9D51-7607EDAA916D}">
   <dimension ref="A1:I55"/>
-  <sheetFormatPr defaultRowHeight="15"/>
+  <sheetFormatPr defaultRowHeight="14.5"/>
   <cols>
-    <col min="1" max="1" width="14.7109375" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="19.5703125" customWidth="1"/>
-    <col min="3" max="3" width="18.140625" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="18.5703125" style="17" customWidth="1"/>
-    <col min="5" max="5" width="21.5703125" customWidth="1"/>
-    <col min="6" max="6" width="36.5703125" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="17.85546875" customWidth="1"/>
-    <col min="8" max="8" width="20.85546875" customWidth="1"/>
-    <col min="9" max="9" width="18.7109375" style="17" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="14.7265625" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="19.54296875" customWidth="1"/>
+    <col min="3" max="3" width="18.1796875" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="18.54296875" style="17" customWidth="1"/>
+    <col min="5" max="5" width="21.54296875" customWidth="1"/>
+    <col min="6" max="6" width="36.54296875" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="17.81640625" customWidth="1"/>
+    <col min="8" max="8" width="20.81640625" customWidth="1"/>
+    <col min="9" max="9" width="18.7265625" style="17" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:9">
@@ -5289,16 +5622,16 @@
 <file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{B760CA2F-2CA8-44F2-8B49-339714F538DA}">
   <dimension ref="A1:I52"/>
-  <sheetFormatPr defaultRowHeight="15"/>
+  <sheetFormatPr defaultRowHeight="14.5"/>
   <cols>
-    <col min="2" max="2" width="14.5703125" customWidth="1"/>
+    <col min="2" max="2" width="14.54296875" customWidth="1"/>
     <col min="3" max="3" width="20" customWidth="1"/>
     <col min="4" max="4" width="19" customWidth="1"/>
-    <col min="5" max="5" width="16.85546875" customWidth="1"/>
+    <col min="5" max="5" width="16.81640625" customWidth="1"/>
     <col min="6" max="6" width="25" customWidth="1"/>
-    <col min="7" max="7" width="19.42578125" customWidth="1"/>
-    <col min="8" max="8" width="24.7109375" customWidth="1"/>
-    <col min="9" max="9" width="21.42578125" customWidth="1"/>
+    <col min="7" max="7" width="19.453125" customWidth="1"/>
+    <col min="8" max="8" width="24.7265625" customWidth="1"/>
+    <col min="9" max="9" width="21.453125" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:9">
@@ -5883,16 +6216,16 @@
 <file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{F6E6B8A0-66E5-406F-8D37-9E8A2778B9CB}">
   <dimension ref="A1:I56"/>
-  <sheetFormatPr defaultRowHeight="15"/>
+  <sheetFormatPr defaultRowHeight="14.5"/>
   <cols>
-    <col min="1" max="1" width="14.7109375" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="25.7109375" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="18.140625" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="14.7265625" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="25.7265625" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="18.1796875" bestFit="1" customWidth="1"/>
     <col min="4" max="4" width="26" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="29.5703125" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="18.7109375" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="20.28515625" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="28.85546875" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="29.54296875" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="18.7265625" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="20.26953125" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="28.81640625" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:9">
@@ -6545,49 +6878,65 @@
 </file>
 
 <file path=customXml/item1.xml><?xml version="1.0" encoding="utf-8"?>
-<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
-  <documentManagement>
-    <_dlc_DocId xmlns="01f4fd7c-51c3-4ad2-ae58-e5034556b4ea">QAFFA7D2F2TC-2102087286-496578</_dlc_DocId>
-    <_dlc_DocIdUrl xmlns="01f4fd7c-51c3-4ad2-ae58-e5034556b4ea">
-      <Url>https://allianzms.sharepoint.com/teams/BR0010-4356589/_layouts/15/DocIdRedir.aspx?ID=QAFFA7D2F2TC-2102087286-496578</Url>
-      <Description>QAFFA7D2F2TC-2102087286-496578</Description>
-    </_dlc_DocIdUrl>
-    <DossierOwner xmlns="01f4fd7c-51c3-4ad2-ae58-e5034556b4ea">
-      <UserInfo>
-        <DisplayName/>
-        <AccountId xsi:nil="true"/>
-        <AccountType/>
-      </UserInfo>
-    </DossierOwner>
-    <_ip_UnifiedCompliancePolicyUIAction xmlns="http://schemas.microsoft.com/sharepoint/v3" xsi:nil="true"/>
-    <ccca9d190a3c43e89f73773ee806c8b5 xmlns="01f4fd7c-51c3-4ad2-ae58-e5034556b4ea">
-      <Terms xmlns="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
-    </ccca9d190a3c43e89f73773ee806c8b5>
-    <lcf76f155ced4ddcb4097134ff3c332f xmlns="ea6c6725-5210-4d6a-93cc-4cf85111ac5e">
-      <Terms xmlns="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
-    </lcf76f155ced4ddcb4097134ff3c332f>
-    <ContractDate xmlns="01f4fd7c-51c3-4ad2-ae58-e5034556b4ea" xsi:nil="true"/>
-    <MailPreviewData xmlns="01f4fd7c-51c3-4ad2-ae58-e5034556b4ea" xsi:nil="true"/>
-    <_Flow_SignoffStatus xmlns="ea6c6725-5210-4d6a-93cc-4cf85111ac5e" xsi:nil="true"/>
-    <_ip_UnifiedCompliancePolicyProperties xmlns="http://schemas.microsoft.com/sharepoint/v3" xsi:nil="true"/>
-    <ContractExpirationDate xmlns="01f4fd7c-51c3-4ad2-ae58-e5034556b4ea" xsi:nil="true"/>
-    <DossierStatus xmlns="01f4fd7c-51c3-4ad2-ae58-e5034556b4ea" xsi:nil="true"/>
-    <ia4b831ccad64069ad2e0cbd870e9b8a xmlns="01f4fd7c-51c3-4ad2-ae58-e5034556b4ea">
-      <Terms xmlns="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
-    </ia4b831ccad64069ad2e0cbd870e9b8a>
-    <TaxCatchAll xmlns="01f4fd7c-51c3-4ad2-ae58-e5034556b4ea" xsi:nil="true"/>
-    <alteradopor xmlns="ea6c6725-5210-4d6a-93cc-4cf85111ac5e">
-      <UserInfo>
-        <DisplayName/>
-        <AccountId xsi:nil="true"/>
-        <AccountType/>
-      </UserInfo>
-    </alteradopor>
-  </documentManagement>
-</p:properties>
+<?mso-contentType ?>
+<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
+  <Display>DocumentLibraryForm</Display>
+  <Edit>DocumentLibraryForm</Edit>
+  <New>DocumentLibraryForm</New>
+</FormTemplates>
 </file>
 
 <file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
+<?mso-contentType ?>
+<spe:Receivers xmlns:spe="http://schemas.microsoft.com/sharepoint/events">
+  <Receiver>
+    <Name>Document ID Generator</Name>
+    <Synchronization>Synchronous</Synchronization>
+    <Type>10001</Type>
+    <SequenceNumber>1000</SequenceNumber>
+    <Url/>
+    <Assembly>Microsoft.Office.DocumentManagement, Version=16.0.0.0, Culture=neutral, PublicKeyToken=71e9bce111e9429c</Assembly>
+    <Class>Microsoft.Office.DocumentManagement.Internal.DocIdHandler</Class>
+    <Data/>
+    <Filter/>
+  </Receiver>
+  <Receiver>
+    <Name>Document ID Generator</Name>
+    <Synchronization>Synchronous</Synchronization>
+    <Type>10002</Type>
+    <SequenceNumber>1001</SequenceNumber>
+    <Url/>
+    <Assembly>Microsoft.Office.DocumentManagement, Version=16.0.0.0, Culture=neutral, PublicKeyToken=71e9bce111e9429c</Assembly>
+    <Class>Microsoft.Office.DocumentManagement.Internal.DocIdHandler</Class>
+    <Data/>
+    <Filter/>
+  </Receiver>
+  <Receiver>
+    <Name>Document ID Generator</Name>
+    <Synchronization>Synchronous</Synchronization>
+    <Type>10004</Type>
+    <SequenceNumber>1002</SequenceNumber>
+    <Url/>
+    <Assembly>Microsoft.Office.DocumentManagement, Version=16.0.0.0, Culture=neutral, PublicKeyToken=71e9bce111e9429c</Assembly>
+    <Class>Microsoft.Office.DocumentManagement.Internal.DocIdHandler</Class>
+    <Data/>
+    <Filter/>
+  </Receiver>
+  <Receiver>
+    <Name>Document ID Generator</Name>
+    <Synchronization>Synchronous</Synchronization>
+    <Type>10006</Type>
+    <SequenceNumber>1003</SequenceNumber>
+    <Url/>
+    <Assembly>Microsoft.Office.DocumentManagement, Version=16.0.0.0, Culture=neutral, PublicKeyToken=71e9bce111e9429c</Assembly>
+    <Class>Microsoft.Office.DocumentManagement.Internal.DocIdHandler</Class>
+    <Data/>
+    <Filter/>
+  </Receiver>
+</spe:Receivers>
+</file>
+
+<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
 <ct:contentTypeSchema xmlns:ct="http://schemas.microsoft.com/office/2006/metadata/contentType" xmlns:ma="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes" ct:_="" ma:_="" ma:contentTypeName="Document" ma:contentTypeID="0x01010006E7B04763359F4AAB0FC84D5027BFC8" ma:contentTypeVersion="44" ma:contentTypeDescription="Create a new document." ma:contentTypeScope="" ma:versionID="ac14f8cb44178d381f4c0afb30680a90">
   <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:ns1="http://schemas.microsoft.com/sharepoint/v3" xmlns:ns2="01f4fd7c-51c3-4ad2-ae58-e5034556b4ea" xmlns:ns3="ea6c6725-5210-4d6a-93cc-4cf85111ac5e" targetNamespace="http://schemas.microsoft.com/office/2006/metadata/properties" ma:root="true" ma:fieldsID="5e58414b065c9b590c40efa77cd84bb6" ns1:_="" ns2:_="" ns3:_="">
     <xsd:import namespace="http://schemas.microsoft.com/sharepoint/v3"/>
@@ -6965,77 +7314,93 @@
 </ct:contentTypeSchema>
 </file>
 
-<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
-<?mso-contentType ?>
-<spe:Receivers xmlns:spe="http://schemas.microsoft.com/sharepoint/events">
-  <Receiver>
-    <Name>Document ID Generator</Name>
-    <Synchronization>Synchronous</Synchronization>
-    <Type>10001</Type>
-    <SequenceNumber>1000</SequenceNumber>
-    <Url/>
-    <Assembly>Microsoft.Office.DocumentManagement, Version=16.0.0.0, Culture=neutral, PublicKeyToken=71e9bce111e9429c</Assembly>
-    <Class>Microsoft.Office.DocumentManagement.Internal.DocIdHandler</Class>
-    <Data/>
-    <Filter/>
-  </Receiver>
-  <Receiver>
-    <Name>Document ID Generator</Name>
-    <Synchronization>Synchronous</Synchronization>
-    <Type>10002</Type>
-    <SequenceNumber>1001</SequenceNumber>
-    <Url/>
-    <Assembly>Microsoft.Office.DocumentManagement, Version=16.0.0.0, Culture=neutral, PublicKeyToken=71e9bce111e9429c</Assembly>
-    <Class>Microsoft.Office.DocumentManagement.Internal.DocIdHandler</Class>
-    <Data/>
-    <Filter/>
-  </Receiver>
-  <Receiver>
-    <Name>Document ID Generator</Name>
-    <Synchronization>Synchronous</Synchronization>
-    <Type>10004</Type>
-    <SequenceNumber>1002</SequenceNumber>
-    <Url/>
-    <Assembly>Microsoft.Office.DocumentManagement, Version=16.0.0.0, Culture=neutral, PublicKeyToken=71e9bce111e9429c</Assembly>
-    <Class>Microsoft.Office.DocumentManagement.Internal.DocIdHandler</Class>
-    <Data/>
-    <Filter/>
-  </Receiver>
-  <Receiver>
-    <Name>Document ID Generator</Name>
-    <Synchronization>Synchronous</Synchronization>
-    <Type>10006</Type>
-    <SequenceNumber>1003</SequenceNumber>
-    <Url/>
-    <Assembly>Microsoft.Office.DocumentManagement, Version=16.0.0.0, Culture=neutral, PublicKeyToken=71e9bce111e9429c</Assembly>
-    <Class>Microsoft.Office.DocumentManagement.Internal.DocIdHandler</Class>
-    <Data/>
-    <Filter/>
-  </Receiver>
-</spe:Receivers>
-</file>
-
 <file path=customXml/item4.xml><?xml version="1.0" encoding="utf-8"?>
-<?mso-contentType ?>
-<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
-  <Display>DocumentLibraryForm</Display>
-  <Edit>DocumentLibraryForm</Edit>
-  <New>DocumentLibraryForm</New>
-</FormTemplates>
+<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
+  <documentManagement>
+    <_dlc_DocId xmlns="01f4fd7c-51c3-4ad2-ae58-e5034556b4ea">QAFFA7D2F2TC-2102087286-496578</_dlc_DocId>
+    <_dlc_DocIdUrl xmlns="01f4fd7c-51c3-4ad2-ae58-e5034556b4ea">
+      <Url>https://allianzms.sharepoint.com/teams/BR0010-4356589/_layouts/15/DocIdRedir.aspx?ID=QAFFA7D2F2TC-2102087286-496578</Url>
+      <Description>QAFFA7D2F2TC-2102087286-496578</Description>
+    </_dlc_DocIdUrl>
+    <DossierOwner xmlns="01f4fd7c-51c3-4ad2-ae58-e5034556b4ea">
+      <UserInfo>
+        <DisplayName/>
+        <AccountId xsi:nil="true"/>
+        <AccountType/>
+      </UserInfo>
+    </DossierOwner>
+    <_ip_UnifiedCompliancePolicyUIAction xmlns="http://schemas.microsoft.com/sharepoint/v3" xsi:nil="true"/>
+    <ccca9d190a3c43e89f73773ee806c8b5 xmlns="01f4fd7c-51c3-4ad2-ae58-e5034556b4ea">
+      <Terms xmlns="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    </ccca9d190a3c43e89f73773ee806c8b5>
+    <lcf76f155ced4ddcb4097134ff3c332f xmlns="ea6c6725-5210-4d6a-93cc-4cf85111ac5e">
+      <Terms xmlns="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    </lcf76f155ced4ddcb4097134ff3c332f>
+    <ContractDate xmlns="01f4fd7c-51c3-4ad2-ae58-e5034556b4ea" xsi:nil="true"/>
+    <MailPreviewData xmlns="01f4fd7c-51c3-4ad2-ae58-e5034556b4ea" xsi:nil="true"/>
+    <_Flow_SignoffStatus xmlns="ea6c6725-5210-4d6a-93cc-4cf85111ac5e" xsi:nil="true"/>
+    <_ip_UnifiedCompliancePolicyProperties xmlns="http://schemas.microsoft.com/sharepoint/v3" xsi:nil="true"/>
+    <ContractExpirationDate xmlns="01f4fd7c-51c3-4ad2-ae58-e5034556b4ea" xsi:nil="true"/>
+    <DossierStatus xmlns="01f4fd7c-51c3-4ad2-ae58-e5034556b4ea" xsi:nil="true"/>
+    <ia4b831ccad64069ad2e0cbd870e9b8a xmlns="01f4fd7c-51c3-4ad2-ae58-e5034556b4ea">
+      <Terms xmlns="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    </ia4b831ccad64069ad2e0cbd870e9b8a>
+    <TaxCatchAll xmlns="01f4fd7c-51c3-4ad2-ae58-e5034556b4ea" xsi:nil="true"/>
+    <alteradopor xmlns="ea6c6725-5210-4d6a-93cc-4cf85111ac5e">
+      <UserInfo>
+        <DisplayName/>
+        <AccountId xsi:nil="true"/>
+        <AccountType/>
+      </UserInfo>
+    </alteradopor>
+  </documentManagement>
+</p:properties>
 </file>
 
 <file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{C48653D8-7562-408C-9B57-D83FFA71DB43}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{BC9CB02D-0F63-4CE2-B316-61A87327416C}">
+  <ds:schemaRefs>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
+  </ds:schemaRefs>
+</ds:datastoreItem>
 </file>
 
 <file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{E4D3A833-2B0B-418C-BE4E-5DFB58A9B857}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{13279B2D-D76C-4CA7-B517-83259B9C0FB4}">
+  <ds:schemaRefs>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/events"/>
+  </ds:schemaRefs>
+</ds:datastoreItem>
 </file>
 
 <file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{13279B2D-D76C-4CA7-B517-83259B9C0FB4}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{5FB975A2-03C7-42F3-8F63-CE01D0A84F3D}">
+  <ds:schemaRefs>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/contentType"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes"/>
+    <ds:schemaRef ds:uri="http://www.w3.org/2001/XMLSchema"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3"/>
+    <ds:schemaRef ds:uri="01f4fd7c-51c3-4ad2-ae58-e5034556b4ea"/>
+    <ds:schemaRef ds:uri="ea6c6725-5210-4d6a-93cc-4cf85111ac5e"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/documentManagement/types"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    <ds:schemaRef ds:uri="http://schemas.openxmlformats.org/package/2006/metadata/core-properties"/>
+    <ds:schemaRef ds:uri="http://purl.org/dc/elements/1.1/"/>
+    <ds:schemaRef ds:uri="http://purl.org/dc/terms/"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/internal/obd"/>
+  </ds:schemaRefs>
+</ds:datastoreItem>
 </file>
 
 <file path=customXml/itemProps4.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{BC9CB02D-0F63-4CE2-B316-61A87327416C}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{C48653D8-7562-408C-9B57-D83FFA71DB43}">
+  <ds:schemaRefs>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    <ds:schemaRef ds:uri="01f4fd7c-51c3-4ad2-ae58-e5034556b4ea"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3"/>
+    <ds:schemaRef ds:uri="ea6c6725-5210-4d6a-93cc-4cf85111ac5e"/>
+  </ds:schemaRefs>
+</ds:datastoreItem>
 </file>
--- a/Data Files/Backoffce/IndexacaoFG/Arquivos/Relatório de Recusas  08.09.2025 a 14.09.2025.xlsx
+++ b/Data Files/Backoffce/IndexacaoFG/Arquivos/Relatório de Recusas  08.09.2025 a 14.09.2025.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="4" rupBuild="28526"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="4" rupBuild="29303"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\APZelizi\Desktop\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://allianzms.sharepoint.com/teams/BR0010-4356589/Shared Documents/BACK-OFFICE SME/Santander/2025/Relatório de Recusas/05. Maio/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{5BABB57C-32F2-4206-813C-D4637768572A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{391140AD-34EE-45D5-9567-F4777C1DB7D4}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10420" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="19530" windowHeight="9780" firstSheet="3" activeTab="3" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="08.09" sheetId="2" r:id="rId1"/>
@@ -42,7 +42,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="403" uniqueCount="114">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="526" uniqueCount="162">
   <si>
     <t>SEGURADORA</t>
   </si>
@@ -390,6 +390,157 @@
   </si>
   <si>
     <t xml:space="preserve">Favor enviar cópia completa da apólice anterior 2024/2025 (atual) através desse e-mail. </t>
+  </si>
+  <si>
+    <t>BRUNO JORGE RENJIFFO -CPF 39074149855</t>
+  </si>
+  <si>
+    <t>NUP Cancelamento 10/09/2025</t>
+  </si>
+  <si>
+    <t>MAURO CONCON FILHO  CPF 25324248851</t>
+  </si>
+  <si>
+    <t xml:space="preserve">O ano modelo informado não corresponde ao chassi do veículo </t>
+  </si>
+  <si>
+    <t xml:space="preserve">RAFAEL RUBIATI SCALVENZI                     </t>
+  </si>
+  <si>
+    <t xml:space="preserve">DANIEL SANTOS ARANTES SOARES                 </t>
+  </si>
+  <si>
+    <t xml:space="preserve">	Santander - Bônus correto deve ser {}, favor corrigir.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">DANIELA BARBISAN                             </t>
+  </si>
+  <si>
+    <t xml:space="preserve">RODRIGO NEVES PEREIRA                        </t>
+  </si>
+  <si>
+    <t xml:space="preserve">DARIO DOS SANTOS MILLER                      </t>
+  </si>
+  <si>
+    <t xml:space="preserve">IVETE TRAGUETA DE DEUS                       </t>
+  </si>
+  <si>
+    <t xml:space="preserve">JOAO PEDRO MORALES LOPES FERRAZ PENTEADO     </t>
+  </si>
+  <si>
+    <t xml:space="preserve">ANDERSON LUIS WOHLGEMUTH MOLENDA             </t>
+  </si>
+  <si>
+    <t>NUP Cancelamento 10.09.2025</t>
+  </si>
+  <si>
+    <t xml:space="preserve">ECLIS RODRIGUES DE CASTILHO                  </t>
+  </si>
+  <si>
+    <t xml:space="preserve">CRISTIANO LOPES                              </t>
+  </si>
+  <si>
+    <t>Conforme consulta na central de bônus, identificamos que não há po
+ssibilidade de efetuar a transferência de bônus para o(a) senhor(a
+) CRISTIANO LOPES, pois este não consta como condutor na apólice a
+nterior.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">CARLOS EDUARDO MIRANDA DA SILVA              </t>
+  </si>
+  <si>
+    <t xml:space="preserve">	Santander - Veículo em duplicidade com proposta</t>
+  </si>
+  <si>
+    <t xml:space="preserve">ALEXANDRE KELLER TURRA                       </t>
+  </si>
+  <si>
+    <t xml:space="preserve">	Aceitação condicionada à confirmação de bônus na CBE</t>
+  </si>
+  <si>
+    <t xml:space="preserve">W FERREIRA DE FREITAS FILHO LTDA ME          </t>
+  </si>
+  <si>
+    <t xml:space="preserve">CHARLES CARDOSO DA SILVA                     </t>
+  </si>
+  <si>
+    <t xml:space="preserve">GEORGE DA SILVA MARQUES                      </t>
+  </si>
+  <si>
+    <t>Aceitação condicionada à confirmação de bônus na CBE</t>
+  </si>
+  <si>
+    <t xml:space="preserve">JOSE ROBERTO NIERI                           </t>
+  </si>
+  <si>
+    <t xml:space="preserve">ALEX GARCIA DE CASTRO LEMOS                  </t>
+  </si>
+  <si>
+    <t xml:space="preserve">JAZIDA PARAISO LTDA ME                       </t>
+  </si>
+  <si>
+    <t>Santander - Veículo informado é diferente do calculado.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">CASSIA VILAS BOAS RODRIGUES ALVES            </t>
+  </si>
+  <si>
+    <t>Aceitação condicionada à confirmação de bônus na CBE.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">JEFERSON CARLOS ALVES                        </t>
+  </si>
+  <si>
+    <t xml:space="preserve">	Divergências na Central de Bônus</t>
+  </si>
+  <si>
+    <t xml:space="preserve">JOAO ANTONIO TORRES GONCALVES                </t>
+  </si>
+  <si>
+    <t>Conforme consulta na central de bônus, identificamos que não há po
+ssibilidade de efetuar a transferência de bônus para o(a) senhor(a
+) JOAO ANTONIO TORRES GONCALVES, pois este não consta como conduto
+rna apólice anterior.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">JULIA FLORES HASS                            </t>
+  </si>
+  <si>
+    <t xml:space="preserve"> NUP Cancelamento 10.09.2025</t>
+  </si>
+  <si>
+    <t xml:space="preserve">REGINA CELIA DE MELLO SILVA                  </t>
+  </si>
+  <si>
+    <t xml:space="preserve">ALCEU JOSE DOS SANTOS                        </t>
+  </si>
+  <si>
+    <t>CLIENTE NÃO CORRIGIU AS FOTOS INCORRETAS - PRAZO EXPIRADO FOTO INCORRETA: CHASSI.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">COOPER MAQUINAS EQUIPAMENTOS E SERVICOS LTDA </t>
+  </si>
+  <si>
+    <t xml:space="preserve">JOSE AUGUSTO SOUSA VELOSO FILHO              </t>
+  </si>
+  <si>
+    <t>Por gentileza nos retornar com o anexo DECLARAÇÃO PEP/SUSEP preenc
+hido</t>
+  </si>
+  <si>
+    <t xml:space="preserve">SIMONE GOULART CARPIO                        </t>
+  </si>
+  <si>
+    <t xml:space="preserve">AMAZONAS SISTEMAS E SERVICOS LTDA            </t>
+  </si>
+  <si>
+    <t xml:space="preserve">RISOLANIA BEZERRA DOS SANTOS ME              </t>
+  </si>
+  <si>
+    <t xml:space="preserve">LF TINTAS LTDA ME                            </t>
+  </si>
+  <si>
+    <t xml:space="preserve">EDIVANIA PEREIRA DA SILVA ME                 </t>
   </si>
 </sst>
 </file>
@@ -473,7 +624,7 @@
       </patternFill>
     </fill>
   </fills>
-  <borders count="15">
+  <borders count="17">
     <border>
       <left/>
       <right/>
@@ -661,12 +812,36 @@
       </bottom>
       <diagonal/>
     </border>
+    <border>
+      <left/>
+      <right style="thin">
+        <color rgb="FF000000"/>
+      </right>
+      <top style="thin">
+        <color rgb="FF000000"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="FF000000"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right style="thin">
+        <color indexed="64"/>
+      </right>
+      <top/>
+      <bottom style="thin">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
   </borders>
   <cellStyleXfs count="2">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="88">
+  <cellXfs count="100">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="2" borderId="1" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
@@ -860,16 +1035,10 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="4" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="6" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top" wrapText="1"/>
-    </xf>
     <xf numFmtId="14" fontId="0" fillId="0" borderId="6" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="4" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment wrapText="1"/>
-    </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="4" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
@@ -877,6 +1046,9 @@
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="14" fontId="0" fillId="0" borderId="4" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="14" fontId="0" fillId="0" borderId="5" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="7" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
@@ -891,22 +1063,43 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
+    <xf numFmtId="14" fontId="0" fillId="0" borderId="4" xfId="0" quotePrefix="1" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="10" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="4" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="5" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="15" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="15" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="16" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="7" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="11" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="5" xfId="0" applyBorder="1" applyAlignment="1"/>
   </cellXfs>
   <cellStyles count="2">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
     <cellStyle name="Normal_Plan2_1" xfId="1" xr:uid="{69F13A52-20D9-46CA-8619-BC7A1BA09FD8}"/>
   </cellStyles>
-  <dxfs count="5">
-    <dxf>
-      <font>
-        <color rgb="FF9C0006"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFC7CE"/>
-        </patternFill>
-      </fill>
-    </dxf>
+  <dxfs count="4">
     <dxf>
       <font>
         <color rgb="FF9C0006"/>
@@ -1278,16 +1471,16 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{A2FDCF22-758E-4370-8390-755171A8B113}">
   <dimension ref="A1:I56"/>
-  <sheetFormatPr defaultRowHeight="14.5"/>
+  <sheetFormatPr defaultRowHeight="15"/>
   <cols>
-    <col min="2" max="2" width="14.1796875" customWidth="1"/>
-    <col min="3" max="3" width="18.1796875" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="16.1796875" customWidth="1"/>
-    <col min="5" max="5" width="18.81640625" customWidth="1"/>
+    <col min="2" max="2" width="14.140625" customWidth="1"/>
+    <col min="3" max="3" width="18.140625" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="16.140625" customWidth="1"/>
+    <col min="5" max="5" width="18.85546875" customWidth="1"/>
     <col min="6" max="6" width="40" customWidth="1"/>
-    <col min="7" max="7" width="20.26953125" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="23.7265625" customWidth="1"/>
-    <col min="9" max="9" width="17.54296875" customWidth="1"/>
+    <col min="7" max="7" width="20.28515625" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="23.7109375" customWidth="1"/>
+    <col min="9" max="9" width="17.5703125" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:9">
@@ -2574,17 +2767,17 @@
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{FFA17127-7620-4DD9-9061-6C654E2EC5C2}">
   <dimension ref="A1:I53"/>
-  <sheetFormatPr defaultRowHeight="14.5"/>
+  <sheetFormatPr defaultRowHeight="15"/>
   <cols>
-    <col min="1" max="1" width="9.54296875" customWidth="1"/>
-    <col min="2" max="2" width="16.54296875" customWidth="1"/>
-    <col min="3" max="3" width="21.54296875" customWidth="1"/>
-    <col min="4" max="4" width="13.26953125" style="17" customWidth="1"/>
-    <col min="5" max="5" width="18.54296875" customWidth="1"/>
-    <col min="6" max="6" width="31.54296875" customWidth="1"/>
-    <col min="7" max="7" width="19.7265625" customWidth="1"/>
+    <col min="1" max="1" width="9.5703125" customWidth="1"/>
+    <col min="2" max="2" width="16.5703125" customWidth="1"/>
+    <col min="3" max="3" width="21.5703125" customWidth="1"/>
+    <col min="4" max="4" width="13.28515625" style="17" customWidth="1"/>
+    <col min="5" max="5" width="18.5703125" customWidth="1"/>
+    <col min="6" max="6" width="31.5703125" customWidth="1"/>
+    <col min="7" max="7" width="19.7109375" customWidth="1"/>
     <col min="8" max="8" width="24" customWidth="1"/>
-    <col min="9" max="9" width="22.7265625" style="16" customWidth="1"/>
+    <col min="9" max="9" width="22.7109375" style="16" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:9">
@@ -3549,13 +3742,13 @@
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="E2">
-    <cfRule type="duplicateValues" dxfId="4" priority="4"/>
+    <cfRule type="duplicateValues" dxfId="3" priority="4"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="E3">
-    <cfRule type="duplicateValues" dxfId="3" priority="3"/>
+    <cfRule type="duplicateValues" dxfId="2" priority="3"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="E4">
-    <cfRule type="duplicateValues" dxfId="2" priority="2"/>
+    <cfRule type="duplicateValues" dxfId="1" priority="2"/>
   </conditionalFormatting>
   <dataValidations count="2">
     <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="A2:A31" xr:uid="{4D257AA8-3FDB-42B7-A450-B3788B0ABB12}">
@@ -3572,15 +3765,15 @@
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{5BD26F43-5C8A-4C67-93F6-3B4E17ED8491}">
   <dimension ref="A1:I43"/>
-  <sheetFormatPr defaultRowHeight="14.5"/>
+  <sheetFormatPr defaultRowHeight="15"/>
   <cols>
-    <col min="2" max="2" width="15.81640625" style="17" customWidth="1"/>
-    <col min="3" max="3" width="18.1796875" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="17.54296875" style="17" customWidth="1"/>
-    <col min="5" max="5" width="17.81640625" style="17" customWidth="1"/>
+    <col min="2" max="2" width="15.85546875" style="17" customWidth="1"/>
+    <col min="3" max="3" width="18.140625" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="17.5703125" style="17" customWidth="1"/>
+    <col min="5" max="5" width="17.85546875" style="17" customWidth="1"/>
     <col min="6" max="6" width="27" customWidth="1"/>
-    <col min="7" max="7" width="20.26953125" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="47.26953125" customWidth="1"/>
+    <col min="7" max="7" width="20.28515625" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="47.28515625" customWidth="1"/>
     <col min="9" max="9" width="21" style="27" customWidth="1"/>
   </cols>
   <sheetData>
@@ -3621,7 +3814,7 @@
         <v>45909</v>
       </c>
       <c r="C2" s="28">
-        <v>45910</v>
+        <v>45939</v>
       </c>
       <c r="D2" s="29" t="s">
         <v>10</v>
@@ -3644,10 +3837,10 @@
         <v>9</v>
       </c>
       <c r="B3" s="73">
-        <v>45905</v>
+        <v>45786</v>
       </c>
       <c r="C3" s="28">
-        <v>45910</v>
+        <v>45939</v>
       </c>
       <c r="D3" s="74">
         <v>134313690</v>
@@ -3661,11 +3854,11 @@
       <c r="G3" s="76" t="s">
         <v>21</v>
       </c>
-      <c r="H3" s="79" t="s">
+      <c r="H3" s="78" t="s">
         <v>94</v>
       </c>
-      <c r="I3" s="83">
-        <v>45905</v>
+      <c r="I3" s="73">
+        <v>45786</v>
       </c>
     </row>
     <row r="4" spans="1:9">
@@ -3676,7 +3869,7 @@
         <v>95</v>
       </c>
       <c r="C4" s="28">
-        <v>45910</v>
+        <v>45939</v>
       </c>
       <c r="D4" s="74">
         <v>134304975</v>
@@ -3702,10 +3895,10 @@
         <v>9</v>
       </c>
       <c r="B5" s="73">
-        <v>45911</v>
+        <v>45970</v>
       </c>
       <c r="C5" s="28">
-        <v>45910</v>
+        <v>45939</v>
       </c>
       <c r="D5" s="74">
         <v>134345251</v>
@@ -3734,7 +3927,7 @@
         <v>45909</v>
       </c>
       <c r="C6" s="28">
-        <v>45910</v>
+        <v>45939</v>
       </c>
       <c r="D6" s="74">
         <v>134354096</v>
@@ -3763,7 +3956,7 @@
         <v>99</v>
       </c>
       <c r="C7" s="28">
-        <v>45910</v>
+        <v>45939</v>
       </c>
       <c r="D7" s="74">
         <v>134170423</v>
@@ -3781,35 +3974,35 @@
         <v>101</v>
       </c>
       <c r="I7" s="73">
-        <v>45902</v>
-      </c>
-    </row>
-    <row r="8" spans="1:9" s="87" customFormat="1" ht="43.5">
-      <c r="A8" s="82" t="s">
-        <v>9</v>
-      </c>
-      <c r="B8" s="83" t="s">
+        <v>45697</v>
+      </c>
+    </row>
+    <row r="8" spans="1:9" s="86" customFormat="1" ht="43.5">
+      <c r="A8" s="80" t="s">
+        <v>9</v>
+      </c>
+      <c r="B8" s="81" t="s">
         <v>99</v>
       </c>
-      <c r="C8" s="28">
-        <v>45910</v>
-      </c>
-      <c r="D8" s="84">
+      <c r="C8" s="82">
+        <v>45939</v>
+      </c>
+      <c r="D8" s="83">
         <v>134174713</v>
       </c>
-      <c r="E8" s="81">
+      <c r="E8" s="79">
         <v>3450067027</v>
       </c>
-      <c r="F8" s="85" t="s">
+      <c r="F8" s="84" t="s">
         <v>72</v>
       </c>
-      <c r="G8" s="81" t="s">
+      <c r="G8" s="79" t="s">
         <v>68</v>
       </c>
-      <c r="H8" s="86" t="s">
+      <c r="H8" s="85" t="s">
         <v>102</v>
       </c>
-      <c r="I8" s="83" t="s">
+      <c r="I8" s="81" t="s">
         <v>103</v>
       </c>
     </row>
@@ -3821,7 +4014,7 @@
         <v>99</v>
       </c>
       <c r="C9" s="28">
-        <v>45910</v>
+        <v>45939</v>
       </c>
       <c r="D9" s="74">
         <v>134175439</v>
@@ -3838,8 +4031,8 @@
       <c r="H9" s="13" t="s">
         <v>105</v>
       </c>
-      <c r="I9" s="73">
-        <v>45905</v>
+      <c r="I9" s="73" t="s">
+        <v>99</v>
       </c>
     </row>
     <row r="10" spans="1:9">
@@ -3847,10 +4040,10 @@
         <v>9</v>
       </c>
       <c r="B10" s="73">
-        <v>45910</v>
+        <v>45939</v>
       </c>
       <c r="C10" s="28">
-        <v>45910</v>
+        <v>45939</v>
       </c>
       <c r="D10" s="74">
         <v>134374124</v>
@@ -3868,7 +4061,7 @@
         <v>32</v>
       </c>
       <c r="I10" s="73">
-        <v>45910</v>
+        <v>45939</v>
       </c>
     </row>
     <row r="11" spans="1:9">
@@ -3876,10 +4069,10 @@
         <v>9</v>
       </c>
       <c r="B11" s="73">
-        <v>45901</v>
+        <v>45666</v>
       </c>
       <c r="C11" s="28">
-        <v>45910</v>
+        <v>45939</v>
       </c>
       <c r="D11" s="74">
         <v>134230537</v>
@@ -3908,7 +4101,7 @@
         <v>107</v>
       </c>
       <c r="C12" s="28">
-        <v>45910</v>
+        <v>45939</v>
       </c>
       <c r="D12" s="74">
         <v>134188240</v>
@@ -3934,10 +4127,10 @@
         <v>9</v>
       </c>
       <c r="B13" s="73">
-        <v>45910</v>
+        <v>45939</v>
       </c>
       <c r="C13" s="28">
-        <v>45910</v>
+        <v>45939</v>
       </c>
       <c r="D13" s="74">
         <v>134383118</v>
@@ -3955,36 +4148,36 @@
         <v>110</v>
       </c>
       <c r="I13" s="73">
-        <v>45910</v>
-      </c>
-    </row>
-    <row r="14" spans="1:9" s="87" customFormat="1" ht="29">
-      <c r="A14" s="82" t="s">
-        <v>9</v>
-      </c>
-      <c r="B14" s="83" t="s">
+        <v>45939</v>
+      </c>
+    </row>
+    <row r="14" spans="1:9" s="86" customFormat="1" ht="29.25">
+      <c r="A14" s="80" t="s">
+        <v>9</v>
+      </c>
+      <c r="B14" s="81" t="s">
         <v>111</v>
       </c>
-      <c r="C14" s="28">
-        <v>45910</v>
-      </c>
-      <c r="D14" s="84">
+      <c r="C14" s="82">
+        <v>45939</v>
+      </c>
+      <c r="D14" s="83">
         <v>134272786</v>
       </c>
-      <c r="E14" s="81">
+      <c r="E14" s="79">
         <v>3450072461</v>
       </c>
-      <c r="F14" s="85" t="s">
+      <c r="F14" s="84" t="s">
         <v>112</v>
       </c>
-      <c r="G14" s="81" t="s">
+      <c r="G14" s="79" t="s">
         <v>68</v>
       </c>
-      <c r="H14" s="86" t="s">
+      <c r="H14" s="85" t="s">
         <v>113</v>
       </c>
-      <c r="I14" s="83">
-        <v>45905</v>
+      <c r="I14" s="81">
+        <v>45786</v>
       </c>
     </row>
     <row r="15" spans="1:9">
@@ -4284,7 +4477,7 @@
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="D3:D14">
-    <cfRule type="duplicateValues" dxfId="1" priority="1"/>
+    <cfRule type="duplicateValues" dxfId="0" priority="1"/>
   </conditionalFormatting>
   <dataValidations count="3">
     <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="A17:A36" xr:uid="{F535CD1B-7EC8-4CD4-9DE2-4943F25AAD12}">
@@ -4303,18 +4496,18 @@
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{9BF216D7-F2B3-4C54-A7B9-7048B06C2C75}">
-  <dimension ref="A1:I52"/>
-  <sheetFormatPr defaultRowHeight="14.5"/>
+  <dimension ref="A1:I40"/>
+  <sheetFormatPr defaultRowHeight="15"/>
   <cols>
-    <col min="1" max="1" width="14.7265625" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="18.453125" customWidth="1"/>
-    <col min="3" max="3" width="18.1796875" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="26" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="29.54296875" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="36.54296875" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="20.26953125" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="54.26953125" customWidth="1"/>
-    <col min="9" max="9" width="18.7265625" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="14.7109375" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="14.28515625" customWidth="1"/>
+    <col min="3" max="3" width="14.140625" customWidth="1"/>
+    <col min="4" max="4" width="11.5703125" customWidth="1"/>
+    <col min="5" max="5" width="18.42578125" customWidth="1"/>
+    <col min="6" max="6" width="41.5703125" customWidth="1"/>
+    <col min="7" max="7" width="16.7109375" customWidth="1"/>
+    <col min="8" max="8" width="23.140625" customWidth="1"/>
+    <col min="9" max="9" width="22.85546875" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:9">
@@ -4336,7 +4529,7 @@
       <c r="F1" s="1" t="s">
         <v>5</v>
       </c>
-      <c r="G1" s="1" t="s">
+      <c r="G1" s="68" t="s">
         <v>6</v>
       </c>
       <c r="H1" s="4" t="s">
@@ -4350,577 +4543,1034 @@
       <c r="A2" s="72" t="s">
         <v>9</v>
       </c>
-      <c r="B2" s="73"/>
-      <c r="C2" s="73"/>
-      <c r="D2" s="74"/>
-      <c r="E2" s="18"/>
-      <c r="F2" s="75"/>
-      <c r="G2" s="76"/>
-      <c r="H2" s="79"/>
-      <c r="I2" s="73"/>
+      <c r="B2" s="73">
+        <v>45909</v>
+      </c>
+      <c r="C2" s="73">
+        <v>45911</v>
+      </c>
+      <c r="D2" s="74" t="s">
+        <v>10</v>
+      </c>
+      <c r="E2" s="18">
+        <v>3450076410</v>
+      </c>
+      <c r="F2" s="75" t="s">
+        <v>114</v>
+      </c>
+      <c r="G2" s="18" t="s">
+        <v>24</v>
+      </c>
+      <c r="H2" s="91" t="s">
+        <v>115</v>
+      </c>
+      <c r="I2" s="73">
+        <v>45910</v>
+      </c>
     </row>
     <row r="3" spans="1:9">
       <c r="A3" s="72" t="s">
         <v>9</v>
       </c>
-      <c r="B3" s="73"/>
-      <c r="C3" s="73"/>
-      <c r="D3" s="74"/>
-      <c r="E3" s="18"/>
-      <c r="F3" s="75"/>
-      <c r="G3" s="76"/>
-      <c r="H3" s="13"/>
+      <c r="B3" s="73">
+        <v>45903</v>
+      </c>
+      <c r="C3" s="87">
+        <v>45911</v>
+      </c>
+      <c r="D3" s="90" t="s">
+        <v>10</v>
+      </c>
+      <c r="E3" s="88">
+        <v>3450072131</v>
+      </c>
+      <c r="F3" s="89" t="s">
+        <v>116</v>
+      </c>
+      <c r="G3" s="18" t="s">
+        <v>12</v>
+      </c>
+      <c r="H3" s="92" t="s">
+        <v>117</v>
+      </c>
       <c r="I3" s="73"/>
     </row>
     <row r="4" spans="1:9">
       <c r="A4" s="72" t="s">
         <v>9</v>
       </c>
-      <c r="B4" s="73"/>
-      <c r="C4" s="73"/>
-      <c r="D4" s="74"/>
-      <c r="E4" s="18"/>
-      <c r="F4" s="75"/>
-      <c r="G4" s="76"/>
-      <c r="H4" s="13"/>
-      <c r="I4" s="73"/>
+      <c r="B4" s="73">
+        <v>45912</v>
+      </c>
+      <c r="C4" s="87">
+        <v>45911</v>
+      </c>
+      <c r="D4" s="25">
+        <v>134202395</v>
+      </c>
+      <c r="E4" s="18">
+        <v>3450068578</v>
+      </c>
+      <c r="F4" s="12" t="s">
+        <v>118</v>
+      </c>
+      <c r="G4" s="94" t="s">
+        <v>68</v>
+      </c>
+      <c r="H4" s="13" t="s">
+        <v>75</v>
+      </c>
+      <c r="I4" s="27">
+        <v>45912</v>
+      </c>
     </row>
     <row r="5" spans="1:9">
       <c r="A5" s="72" t="s">
         <v>9</v>
       </c>
-      <c r="B5" s="73"/>
-      <c r="C5" s="73"/>
-      <c r="D5" s="74"/>
-      <c r="E5" s="18"/>
-      <c r="F5" s="75"/>
-      <c r="G5" s="76"/>
-      <c r="H5" s="13"/>
-      <c r="I5" s="73"/>
+      <c r="B5" s="73">
+        <v>45905</v>
+      </c>
+      <c r="C5" s="87">
+        <v>45911</v>
+      </c>
+      <c r="D5" s="25">
+        <v>134196293</v>
+      </c>
+      <c r="E5" s="18">
+        <v>3450068215</v>
+      </c>
+      <c r="F5" s="12" t="s">
+        <v>119</v>
+      </c>
+      <c r="G5" s="94" t="s">
+        <v>68</v>
+      </c>
+      <c r="H5" s="13" t="s">
+        <v>120</v>
+      </c>
+      <c r="I5" s="27">
+        <v>45905</v>
+      </c>
     </row>
     <row r="6" spans="1:9">
       <c r="A6" s="72" t="s">
         <v>9</v>
       </c>
-      <c r="B6" s="73"/>
-      <c r="C6" s="73"/>
-      <c r="D6" s="74"/>
-      <c r="E6" s="18"/>
-      <c r="F6" s="75"/>
-      <c r="G6" s="76"/>
-      <c r="H6" s="13"/>
-      <c r="I6" s="73"/>
+      <c r="B6" s="73">
+        <v>45898</v>
+      </c>
+      <c r="C6" s="87">
+        <v>45911</v>
+      </c>
+      <c r="D6" s="25">
+        <v>134207349</v>
+      </c>
+      <c r="E6" s="18">
+        <v>3450068875</v>
+      </c>
+      <c r="F6" s="12" t="s">
+        <v>121</v>
+      </c>
+      <c r="G6" s="94" t="s">
+        <v>68</v>
+      </c>
+      <c r="H6" s="13" t="s">
+        <v>120</v>
+      </c>
+      <c r="I6" s="27">
+        <v>45898</v>
+      </c>
     </row>
     <row r="7" spans="1:9">
       <c r="A7" s="72" t="s">
         <v>9</v>
       </c>
-      <c r="B7" s="73"/>
-      <c r="C7" s="73"/>
-      <c r="D7" s="74"/>
-      <c r="E7" s="18"/>
-      <c r="F7" s="75"/>
-      <c r="G7" s="81"/>
-      <c r="H7" s="80"/>
-      <c r="I7" s="73"/>
+      <c r="B7" s="73">
+        <v>45903</v>
+      </c>
+      <c r="C7" s="87">
+        <v>45911</v>
+      </c>
+      <c r="D7" s="25">
+        <v>134272705</v>
+      </c>
+      <c r="E7" s="18">
+        <v>3450072450</v>
+      </c>
+      <c r="F7" s="12" t="s">
+        <v>122</v>
+      </c>
+      <c r="G7" s="94" t="s">
+        <v>16</v>
+      </c>
+      <c r="H7" s="13" t="s">
+        <v>64</v>
+      </c>
+      <c r="I7" s="27">
+        <v>45903</v>
+      </c>
     </row>
     <row r="8" spans="1:9">
       <c r="A8" s="72" t="s">
         <v>9</v>
       </c>
-      <c r="B8" s="73"/>
-      <c r="C8" s="73"/>
-      <c r="D8" s="74"/>
-      <c r="E8" s="18"/>
-      <c r="F8" s="75"/>
-      <c r="G8" s="76"/>
-      <c r="H8" s="13"/>
-      <c r="I8" s="73"/>
+      <c r="B8" s="73">
+        <v>45903</v>
+      </c>
+      <c r="C8" s="87">
+        <v>45911</v>
+      </c>
+      <c r="D8" s="25">
+        <v>134272529</v>
+      </c>
+      <c r="E8" s="18">
+        <v>3450072439</v>
+      </c>
+      <c r="F8" s="12" t="s">
+        <v>123</v>
+      </c>
+      <c r="G8" s="94" t="s">
+        <v>16</v>
+      </c>
+      <c r="H8" s="13" t="s">
+        <v>64</v>
+      </c>
+      <c r="I8" s="27">
+        <v>45903</v>
+      </c>
     </row>
     <row r="9" spans="1:9">
       <c r="A9" s="72" t="s">
         <v>9</v>
       </c>
-      <c r="B9" s="73"/>
-      <c r="C9" s="73"/>
-      <c r="D9" s="74"/>
-      <c r="E9" s="18"/>
-      <c r="F9" s="75"/>
-      <c r="G9" s="76"/>
-      <c r="H9" s="13"/>
-      <c r="I9" s="73"/>
+      <c r="B9" s="73">
+        <v>45926</v>
+      </c>
+      <c r="C9" s="87">
+        <v>45911</v>
+      </c>
+      <c r="D9" s="25">
+        <v>134286685</v>
+      </c>
+      <c r="E9" s="18">
+        <v>3450072846</v>
+      </c>
+      <c r="F9" s="12" t="s">
+        <v>124</v>
+      </c>
+      <c r="G9" s="94" t="s">
+        <v>24</v>
+      </c>
+      <c r="H9" s="13" t="s">
+        <v>25</v>
+      </c>
+      <c r="I9" s="27">
+        <v>45909</v>
+      </c>
     </row>
     <row r="10" spans="1:9">
       <c r="A10" s="72" t="s">
         <v>9</v>
       </c>
-      <c r="B10" s="73"/>
-      <c r="C10" s="73"/>
-      <c r="D10" s="74"/>
-      <c r="E10" s="18"/>
-      <c r="F10" s="75"/>
-      <c r="G10" s="76"/>
-      <c r="H10" s="13"/>
-      <c r="I10" s="73"/>
+      <c r="B10" s="73">
+        <v>45903</v>
+      </c>
+      <c r="C10" s="87">
+        <v>45911</v>
+      </c>
+      <c r="D10" s="25">
+        <v>134276082</v>
+      </c>
+      <c r="E10" s="18">
+        <v>3450072660</v>
+      </c>
+      <c r="F10" s="12" t="s">
+        <v>125</v>
+      </c>
+      <c r="G10" s="94" t="s">
+        <v>16</v>
+      </c>
+      <c r="H10" s="13" t="s">
+        <v>64</v>
+      </c>
+      <c r="I10" s="27">
+        <v>45903</v>
+      </c>
     </row>
     <row r="11" spans="1:9">
       <c r="A11" s="72" t="s">
         <v>9</v>
       </c>
-      <c r="B11" s="73"/>
-      <c r="C11" s="73"/>
-      <c r="D11" s="74"/>
-      <c r="E11" s="18"/>
-      <c r="F11" s="75"/>
-      <c r="G11" s="76"/>
-      <c r="H11" s="13"/>
-      <c r="I11" s="73"/>
+      <c r="B11" s="73">
+        <v>45919</v>
+      </c>
+      <c r="C11" s="87">
+        <v>45911</v>
+      </c>
+      <c r="D11" s="25">
+        <v>134355910</v>
+      </c>
+      <c r="E11" s="18">
+        <v>3450076344</v>
+      </c>
+      <c r="F11" s="12" t="s">
+        <v>126</v>
+      </c>
+      <c r="G11" s="94" t="s">
+        <v>24</v>
+      </c>
+      <c r="H11" s="13" t="s">
+        <v>127</v>
+      </c>
+      <c r="I11" s="27">
+        <v>45910</v>
+      </c>
     </row>
     <row r="12" spans="1:9">
       <c r="A12" s="72" t="s">
         <v>9</v>
       </c>
-      <c r="B12" s="73"/>
-      <c r="C12" s="73"/>
-      <c r="D12" s="74"/>
-      <c r="E12" s="18"/>
-      <c r="F12" s="75"/>
-      <c r="G12" s="76"/>
-      <c r="H12" s="13"/>
-      <c r="I12" s="73"/>
+      <c r="B12" s="73">
+        <v>45925</v>
+      </c>
+      <c r="C12" s="87">
+        <v>45911</v>
+      </c>
+      <c r="D12" s="25">
+        <v>134288666</v>
+      </c>
+      <c r="E12" s="18">
+        <v>3450073110</v>
+      </c>
+      <c r="F12" s="12" t="s">
+        <v>128</v>
+      </c>
+      <c r="G12" s="95" t="s">
+        <v>24</v>
+      </c>
+      <c r="H12" s="13" t="s">
+        <v>25</v>
+      </c>
+      <c r="I12" s="27">
+        <v>45909</v>
+      </c>
     </row>
     <row r="13" spans="1:9">
       <c r="A13" s="72" t="s">
         <v>9</v>
       </c>
-      <c r="B13" s="73"/>
-      <c r="C13" s="73"/>
-      <c r="D13" s="74"/>
-      <c r="E13" s="18"/>
-      <c r="F13" s="75"/>
-      <c r="G13" s="81"/>
-      <c r="H13" s="80"/>
-      <c r="I13" s="73"/>
+      <c r="B13" s="73">
+        <v>45897</v>
+      </c>
+      <c r="C13" s="87">
+        <v>45911</v>
+      </c>
+      <c r="D13" s="25">
+        <v>134185969</v>
+      </c>
+      <c r="E13" s="18">
+        <v>3450067456</v>
+      </c>
+      <c r="F13" s="12" t="s">
+        <v>129</v>
+      </c>
+      <c r="G13" s="95" t="s">
+        <v>68</v>
+      </c>
+      <c r="H13" s="13" t="s">
+        <v>130</v>
+      </c>
+      <c r="I13" s="27">
+        <v>45911</v>
+      </c>
     </row>
     <row r="14" spans="1:9">
-      <c r="A14" s="72"/>
-      <c r="B14" s="73"/>
-      <c r="C14" s="73"/>
-      <c r="D14" s="18"/>
-      <c r="E14" s="18"/>
-      <c r="F14" s="12"/>
-      <c r="G14" s="72"/>
-      <c r="H14" s="13"/>
-      <c r="I14" s="73"/>
+      <c r="A14" s="72" t="s">
+        <v>9</v>
+      </c>
+      <c r="B14" s="73">
+        <v>45910</v>
+      </c>
+      <c r="C14" s="87">
+        <v>45911</v>
+      </c>
+      <c r="D14" s="25">
+        <v>134191506</v>
+      </c>
+      <c r="E14" s="18">
+        <v>3450067863</v>
+      </c>
+      <c r="F14" s="12" t="s">
+        <v>131</v>
+      </c>
+      <c r="G14" s="95" t="s">
+        <v>68</v>
+      </c>
+      <c r="H14" s="13" t="s">
+        <v>132</v>
+      </c>
+      <c r="I14" s="27">
+        <v>45910</v>
+      </c>
     </row>
     <row r="15" spans="1:9">
-      <c r="A15" s="72"/>
-      <c r="B15" s="73"/>
-      <c r="C15" s="73"/>
-      <c r="D15" s="18"/>
-      <c r="E15" s="18"/>
-      <c r="F15" s="12"/>
-      <c r="G15" s="72"/>
-      <c r="H15" s="13"/>
-      <c r="I15" s="73"/>
+      <c r="A15" s="72" t="s">
+        <v>9</v>
+      </c>
+      <c r="B15" s="73">
+        <v>45898</v>
+      </c>
+      <c r="C15" s="87">
+        <v>45911</v>
+      </c>
+      <c r="D15" s="25">
+        <v>134193208</v>
+      </c>
+      <c r="E15" s="18">
+        <v>3450067930</v>
+      </c>
+      <c r="F15" s="12" t="s">
+        <v>133</v>
+      </c>
+      <c r="G15" s="95" t="s">
+        <v>68</v>
+      </c>
+      <c r="H15" s="13" t="s">
+        <v>134</v>
+      </c>
+      <c r="I15" s="27">
+        <v>45898</v>
+      </c>
     </row>
     <row r="16" spans="1:9">
-      <c r="A16" s="72"/>
-      <c r="B16" s="18"/>
-      <c r="C16" s="73"/>
-      <c r="D16" s="18"/>
-      <c r="E16" s="18"/>
-      <c r="F16" s="13"/>
-      <c r="G16" s="72"/>
-      <c r="H16" s="13"/>
-      <c r="I16" s="73"/>
+      <c r="A16" s="72" t="s">
+        <v>9</v>
+      </c>
+      <c r="B16" s="73">
+        <v>45902</v>
+      </c>
+      <c r="C16" s="87">
+        <v>45911</v>
+      </c>
+      <c r="D16" s="25">
+        <v>134196102</v>
+      </c>
+      <c r="E16" s="18">
+        <v>3450068171</v>
+      </c>
+      <c r="F16" s="12" t="s">
+        <v>135</v>
+      </c>
+      <c r="G16" s="95" t="s">
+        <v>68</v>
+      </c>
+      <c r="H16" s="13" t="s">
+        <v>134</v>
+      </c>
+      <c r="I16" s="27">
+        <v>45902</v>
+      </c>
     </row>
     <row r="17" spans="1:9">
-      <c r="A17" s="72"/>
-      <c r="B17" s="18"/>
-      <c r="C17" s="73"/>
-      <c r="D17" s="18"/>
-      <c r="E17" s="18"/>
-      <c r="F17" s="13"/>
-      <c r="G17" s="72"/>
-      <c r="H17" s="13"/>
-      <c r="I17" s="73"/>
+      <c r="A17" s="72" t="s">
+        <v>9</v>
+      </c>
+      <c r="B17" s="73">
+        <v>45895</v>
+      </c>
+      <c r="C17" s="87">
+        <v>45911</v>
+      </c>
+      <c r="D17" s="25">
+        <v>134196146</v>
+      </c>
+      <c r="E17" s="18">
+        <v>3450068182</v>
+      </c>
+      <c r="F17" s="12" t="s">
+        <v>136</v>
+      </c>
+      <c r="G17" s="95" t="s">
+        <v>24</v>
+      </c>
+      <c r="H17" s="13" t="s">
+        <v>25</v>
+      </c>
+      <c r="I17" s="27">
+        <v>45895</v>
+      </c>
     </row>
     <row r="18" spans="1:9">
-      <c r="A18" s="72"/>
-      <c r="B18" s="18"/>
-      <c r="C18" s="73"/>
-      <c r="D18" s="18"/>
-      <c r="E18" s="18"/>
-      <c r="F18" s="13"/>
-      <c r="G18" s="72"/>
-      <c r="H18" s="13"/>
-      <c r="I18" s="13"/>
+      <c r="A18" s="72" t="s">
+        <v>9</v>
+      </c>
+      <c r="B18" s="73">
+        <v>45928</v>
+      </c>
+      <c r="C18" s="87">
+        <v>45911</v>
+      </c>
+      <c r="D18" s="25">
+        <v>134196348</v>
+      </c>
+      <c r="E18" s="18">
+        <v>3450068237</v>
+      </c>
+      <c r="F18" s="12" t="s">
+        <v>137</v>
+      </c>
+      <c r="G18" s="95" t="s">
+        <v>68</v>
+      </c>
+      <c r="H18" s="13" t="s">
+        <v>138</v>
+      </c>
+      <c r="I18" s="27">
+        <v>45928</v>
+      </c>
     </row>
     <row r="19" spans="1:9">
-      <c r="A19" s="72"/>
-      <c r="B19" s="18"/>
-      <c r="C19" s="73"/>
-      <c r="D19" s="18"/>
-      <c r="E19" s="18"/>
-      <c r="F19" s="13"/>
-      <c r="G19" s="72"/>
-      <c r="H19" s="13"/>
-      <c r="I19" s="13"/>
+      <c r="A19" s="72" t="s">
+        <v>9</v>
+      </c>
+      <c r="B19" s="77">
+        <v>45904</v>
+      </c>
+      <c r="C19" s="87">
+        <v>45911</v>
+      </c>
+      <c r="D19" s="25">
+        <v>134196592</v>
+      </c>
+      <c r="E19" s="18">
+        <v>3450068259</v>
+      </c>
+      <c r="F19" s="12" t="s">
+        <v>139</v>
+      </c>
+      <c r="G19" s="96" t="s">
+        <v>68</v>
+      </c>
+      <c r="H19" s="98" t="s">
+        <v>75</v>
+      </c>
+      <c r="I19" s="27">
+        <v>45904</v>
+      </c>
     </row>
     <row r="20" spans="1:9">
-      <c r="A20" s="72"/>
-      <c r="B20" s="18"/>
-      <c r="C20" s="73"/>
-      <c r="D20" s="18"/>
-      <c r="E20" s="18"/>
-      <c r="F20" s="13"/>
-      <c r="G20" s="72"/>
-      <c r="H20" s="13"/>
-      <c r="I20" s="13"/>
+      <c r="A20" s="72" t="s">
+        <v>9</v>
+      </c>
+      <c r="B20" s="7">
+        <v>45905</v>
+      </c>
+      <c r="C20" s="87">
+        <v>45911</v>
+      </c>
+      <c r="D20" s="25">
+        <v>134198312</v>
+      </c>
+      <c r="E20" s="18">
+        <v>3450068336</v>
+      </c>
+      <c r="F20" s="12" t="s">
+        <v>140</v>
+      </c>
+      <c r="G20" s="97" t="s">
+        <v>68</v>
+      </c>
+      <c r="H20" s="98" t="s">
+        <v>75</v>
+      </c>
+      <c r="I20" s="37">
+        <v>45905</v>
+      </c>
     </row>
     <row r="21" spans="1:9">
-      <c r="A21" s="72"/>
-      <c r="B21" s="18"/>
-      <c r="C21" s="73"/>
-      <c r="D21" s="18"/>
-      <c r="E21" s="18"/>
-      <c r="F21" s="13"/>
-      <c r="G21" s="72"/>
-      <c r="H21" s="13"/>
-      <c r="I21" s="13"/>
+      <c r="A21" s="72" t="s">
+        <v>9</v>
+      </c>
+      <c r="B21" s="7">
+        <v>45898</v>
+      </c>
+      <c r="C21" s="87">
+        <v>45911</v>
+      </c>
+      <c r="D21" s="25">
+        <v>134201215</v>
+      </c>
+      <c r="E21" s="18">
+        <v>3450068479</v>
+      </c>
+      <c r="F21" s="12" t="s">
+        <v>141</v>
+      </c>
+      <c r="G21" s="97" t="s">
+        <v>12</v>
+      </c>
+      <c r="H21" s="93" t="s">
+        <v>142</v>
+      </c>
+      <c r="I21" s="27">
+        <v>45898</v>
+      </c>
     </row>
     <row r="22" spans="1:9">
-      <c r="A22" s="72"/>
-      <c r="B22" s="18"/>
-      <c r="C22" s="73"/>
-      <c r="D22" s="18"/>
-      <c r="E22" s="18"/>
-      <c r="F22" s="13"/>
-      <c r="G22" s="72"/>
-      <c r="H22" s="13"/>
-      <c r="I22" s="13"/>
+      <c r="A22" s="72" t="s">
+        <v>9</v>
+      </c>
+      <c r="B22" s="7">
+        <v>45898</v>
+      </c>
+      <c r="C22" s="87">
+        <v>45911</v>
+      </c>
+      <c r="D22" s="25">
+        <v>134207354</v>
+      </c>
+      <c r="E22" s="18">
+        <v>3450068886</v>
+      </c>
+      <c r="F22" s="12" t="s">
+        <v>143</v>
+      </c>
+      <c r="G22" s="97" t="s">
+        <v>68</v>
+      </c>
+      <c r="H22" s="93" t="s">
+        <v>144</v>
+      </c>
+      <c r="I22" s="27">
+        <v>45898</v>
+      </c>
     </row>
     <row r="23" spans="1:9">
-      <c r="A23" s="72"/>
-      <c r="B23" s="18"/>
-      <c r="C23" s="73"/>
-      <c r="D23" s="18"/>
-      <c r="E23" s="18"/>
-      <c r="F23" s="13"/>
-      <c r="G23" s="72"/>
-      <c r="H23" s="13"/>
-      <c r="I23" s="13"/>
+      <c r="A23" s="72" t="s">
+        <v>9</v>
+      </c>
+      <c r="B23" s="7">
+        <v>45908</v>
+      </c>
+      <c r="C23" s="87">
+        <v>45911</v>
+      </c>
+      <c r="D23" s="25">
+        <v>134196164</v>
+      </c>
+      <c r="E23" s="18">
+        <v>3450068193</v>
+      </c>
+      <c r="F23" s="12" t="s">
+        <v>145</v>
+      </c>
+      <c r="G23" s="97" t="s">
+        <v>68</v>
+      </c>
+      <c r="H23" s="93" t="s">
+        <v>146</v>
+      </c>
+      <c r="I23" s="27">
+        <v>45908</v>
+      </c>
     </row>
     <row r="24" spans="1:9">
-      <c r="A24" s="72"/>
-      <c r="B24" s="18"/>
-      <c r="C24" s="73"/>
-      <c r="D24" s="18"/>
-      <c r="E24" s="18"/>
-      <c r="F24" s="13"/>
-      <c r="G24" s="72"/>
-      <c r="H24" s="13"/>
-      <c r="I24" s="13"/>
+      <c r="A24" s="72" t="s">
+        <v>9</v>
+      </c>
+      <c r="B24" s="7">
+        <v>45910</v>
+      </c>
+      <c r="C24" s="87">
+        <v>45911</v>
+      </c>
+      <c r="D24" s="25">
+        <v>134194278</v>
+      </c>
+      <c r="E24" s="18">
+        <v>3450067973</v>
+      </c>
+      <c r="F24" s="12" t="s">
+        <v>147</v>
+      </c>
+      <c r="G24" s="97" t="s">
+        <v>68</v>
+      </c>
+      <c r="H24" s="93" t="s">
+        <v>148</v>
+      </c>
+      <c r="I24" s="27">
+        <v>45911</v>
+      </c>
     </row>
     <row r="25" spans="1:9">
-      <c r="A25" s="72"/>
-      <c r="B25" s="18"/>
-      <c r="C25" s="73"/>
-      <c r="D25" s="18"/>
-      <c r="E25" s="18"/>
-      <c r="F25" s="13"/>
-      <c r="G25" s="72"/>
-      <c r="H25" s="13"/>
-      <c r="I25" s="13"/>
+      <c r="A25" s="72" t="s">
+        <v>9</v>
+      </c>
+      <c r="B25" s="7">
+        <v>45908</v>
+      </c>
+      <c r="C25" s="87">
+        <v>45911</v>
+      </c>
+      <c r="D25" s="25">
+        <v>134202624</v>
+      </c>
+      <c r="E25" s="18">
+        <v>3450068611</v>
+      </c>
+      <c r="F25" s="12" t="s">
+        <v>149</v>
+      </c>
+      <c r="G25" s="97" t="s">
+        <v>24</v>
+      </c>
+      <c r="H25" s="93" t="s">
+        <v>150</v>
+      </c>
+      <c r="I25" s="27">
+        <v>45910</v>
+      </c>
     </row>
     <row r="26" spans="1:9">
-      <c r="A26" s="72"/>
-      <c r="B26" s="18"/>
-      <c r="C26" s="73"/>
-      <c r="D26" s="18"/>
-      <c r="E26" s="18"/>
-      <c r="F26" s="13"/>
-      <c r="G26" s="72"/>
-      <c r="H26" s="13"/>
-      <c r="I26" s="13"/>
+      <c r="A26" s="72" t="s">
+        <v>9</v>
+      </c>
+      <c r="B26" s="7">
+        <v>45910</v>
+      </c>
+      <c r="C26" s="87">
+        <v>45911</v>
+      </c>
+      <c r="D26" s="25">
+        <v>134269504</v>
+      </c>
+      <c r="E26" s="18">
+        <v>3450072153</v>
+      </c>
+      <c r="F26" s="12" t="s">
+        <v>151</v>
+      </c>
+      <c r="G26" s="97" t="s">
+        <v>24</v>
+      </c>
+      <c r="H26" s="93" t="s">
+        <v>127</v>
+      </c>
+      <c r="I26" s="27">
+        <v>45910</v>
+      </c>
     </row>
     <row r="27" spans="1:9">
-      <c r="A27" s="72"/>
-      <c r="B27" s="18"/>
-      <c r="C27" s="73"/>
-      <c r="D27" s="18"/>
-      <c r="E27" s="18"/>
-      <c r="F27" s="13"/>
-      <c r="G27" s="72"/>
-      <c r="H27" s="13"/>
-      <c r="I27" s="13"/>
+      <c r="A27" s="72" t="s">
+        <v>9</v>
+      </c>
+      <c r="B27" s="7">
+        <v>45903</v>
+      </c>
+      <c r="C27" s="87">
+        <v>45911</v>
+      </c>
+      <c r="D27" s="25">
+        <v>134267441</v>
+      </c>
+      <c r="E27" s="18">
+        <v>3450072043</v>
+      </c>
+      <c r="F27" s="12" t="s">
+        <v>152</v>
+      </c>
+      <c r="G27" s="97" t="s">
+        <v>21</v>
+      </c>
+      <c r="H27" s="99" t="s">
+        <v>153</v>
+      </c>
+      <c r="I27" s="27">
+        <v>45903</v>
+      </c>
     </row>
     <row r="28" spans="1:9">
-      <c r="A28" s="72"/>
-      <c r="B28" s="18"/>
-      <c r="C28" s="73"/>
-      <c r="D28" s="18"/>
-      <c r="E28" s="18"/>
-      <c r="F28" s="13"/>
-      <c r="G28" s="72"/>
-      <c r="H28" s="13"/>
-      <c r="I28" s="13"/>
+      <c r="A28" s="72" t="s">
+        <v>9</v>
+      </c>
+      <c r="B28" s="7">
+        <v>45905</v>
+      </c>
+      <c r="C28" s="87">
+        <v>45911</v>
+      </c>
+      <c r="D28" s="25">
+        <v>134309150</v>
+      </c>
+      <c r="E28" s="18">
+        <v>3450074276</v>
+      </c>
+      <c r="F28" s="12" t="s">
+        <v>154</v>
+      </c>
+      <c r="G28" s="97" t="s">
+        <v>31</v>
+      </c>
+      <c r="H28" s="99" t="s">
+        <v>32</v>
+      </c>
+      <c r="I28" s="27">
+        <v>45905</v>
+      </c>
     </row>
     <row r="29" spans="1:9">
-      <c r="A29" s="77"/>
-      <c r="B29" s="23"/>
-      <c r="C29" s="78"/>
-      <c r="D29" s="23"/>
-      <c r="E29" s="23"/>
-      <c r="F29" s="15"/>
-      <c r="G29" s="77"/>
-      <c r="H29" s="15"/>
+      <c r="A29" s="72" t="s">
+        <v>9</v>
+      </c>
+      <c r="B29" s="7">
+        <v>45897</v>
+      </c>
+      <c r="C29" s="87">
+        <v>45911</v>
+      </c>
+      <c r="D29" s="25">
+        <v>134181065</v>
+      </c>
+      <c r="E29" s="18">
+        <v>3450067490</v>
+      </c>
+      <c r="F29" s="12" t="s">
+        <v>155</v>
+      </c>
+      <c r="G29" s="97" t="s">
+        <v>12</v>
+      </c>
+      <c r="H29" s="99" t="s">
+        <v>156</v>
+      </c>
+      <c r="I29" s="27">
+        <v>45902</v>
+      </c>
     </row>
     <row r="30" spans="1:9">
-      <c r="A30" s="6"/>
-      <c r="B30" s="8"/>
-      <c r="C30" s="7"/>
-      <c r="D30" s="8"/>
-      <c r="E30" s="8"/>
-      <c r="F30" s="9"/>
-      <c r="G30" s="6"/>
-      <c r="H30" s="9"/>
+      <c r="A30" s="72" t="s">
+        <v>9</v>
+      </c>
+      <c r="B30" s="7">
+        <v>45903</v>
+      </c>
+      <c r="C30" s="87">
+        <v>45911</v>
+      </c>
+      <c r="D30" s="25">
+        <v>134260322</v>
+      </c>
+      <c r="E30" s="18">
+        <v>3450071493</v>
+      </c>
+      <c r="F30" s="12" t="s">
+        <v>157</v>
+      </c>
+      <c r="G30" s="97" t="s">
+        <v>16</v>
+      </c>
+      <c r="H30" s="93" t="s">
+        <v>64</v>
+      </c>
+      <c r="I30" s="27">
+        <v>45903</v>
+      </c>
     </row>
     <row r="31" spans="1:9">
-      <c r="A31" s="6"/>
-      <c r="B31" s="8"/>
-      <c r="C31" s="7"/>
-      <c r="D31" s="8"/>
-      <c r="E31" s="8"/>
-      <c r="F31" s="9"/>
-      <c r="G31" s="6"/>
-      <c r="H31" s="9"/>
+      <c r="A31" s="72" t="s">
+        <v>9</v>
+      </c>
+      <c r="B31" s="7">
+        <v>45903</v>
+      </c>
+      <c r="C31" s="87">
+        <v>45911</v>
+      </c>
+      <c r="D31" s="25">
+        <v>134262306</v>
+      </c>
+      <c r="E31" s="18">
+        <v>3450071603</v>
+      </c>
+      <c r="F31" s="12" t="s">
+        <v>158</v>
+      </c>
+      <c r="G31" s="97" t="s">
+        <v>16</v>
+      </c>
+      <c r="H31" s="93" t="s">
+        <v>64</v>
+      </c>
+      <c r="I31" s="27">
+        <v>45903</v>
+      </c>
     </row>
     <row r="32" spans="1:9">
-      <c r="A32" s="6"/>
-      <c r="B32" s="8"/>
-      <c r="C32" s="7"/>
-      <c r="D32" s="8"/>
-      <c r="E32" s="8"/>
-      <c r="F32" s="9"/>
-      <c r="G32" s="6"/>
-      <c r="H32" s="9"/>
-    </row>
-    <row r="33" spans="1:8">
-      <c r="A33" s="6"/>
-      <c r="B33" s="8"/>
-      <c r="C33" s="7"/>
-      <c r="D33" s="8"/>
-      <c r="E33" s="8"/>
-      <c r="F33" s="9"/>
-      <c r="G33" s="6"/>
-      <c r="H33" s="9"/>
-    </row>
-    <row r="34" spans="1:8">
-      <c r="A34" s="6"/>
-      <c r="B34" s="8"/>
-      <c r="C34" s="7"/>
-      <c r="D34" s="8"/>
-      <c r="E34" s="8"/>
-      <c r="F34" s="9"/>
-      <c r="G34" s="6"/>
-      <c r="H34" s="9"/>
-    </row>
-    <row r="35" spans="1:8">
+      <c r="A32" s="72" t="s">
+        <v>9</v>
+      </c>
+      <c r="B32" s="7">
+        <v>45903</v>
+      </c>
+      <c r="C32" s="87">
+        <v>45911</v>
+      </c>
+      <c r="D32" s="25">
+        <v>134263367</v>
+      </c>
+      <c r="E32" s="18">
+        <v>3450071702</v>
+      </c>
+      <c r="F32" s="12" t="s">
+        <v>159</v>
+      </c>
+      <c r="G32" s="97" t="s">
+        <v>16</v>
+      </c>
+      <c r="H32" s="93" t="s">
+        <v>64</v>
+      </c>
+      <c r="I32" s="27">
+        <v>45903</v>
+      </c>
+    </row>
+    <row r="33" spans="1:9">
+      <c r="A33" s="72" t="s">
+        <v>9</v>
+      </c>
+      <c r="B33" s="7">
+        <v>45903</v>
+      </c>
+      <c r="C33" s="87">
+        <v>45911</v>
+      </c>
+      <c r="D33" s="25">
+        <v>134267833</v>
+      </c>
+      <c r="E33" s="18">
+        <v>3450072087</v>
+      </c>
+      <c r="F33" s="12" t="s">
+        <v>160</v>
+      </c>
+      <c r="G33" s="97" t="s">
+        <v>16</v>
+      </c>
+      <c r="H33" s="93" t="s">
+        <v>64</v>
+      </c>
+      <c r="I33" s="27">
+        <v>45903</v>
+      </c>
+    </row>
+    <row r="34" spans="1:9">
+      <c r="A34" s="72" t="s">
+        <v>9</v>
+      </c>
+      <c r="B34" s="7">
+        <v>45903</v>
+      </c>
+      <c r="C34" s="87">
+        <v>45911</v>
+      </c>
+      <c r="D34" s="25">
+        <v>134274558</v>
+      </c>
+      <c r="E34" s="18">
+        <v>3450072571</v>
+      </c>
+      <c r="F34" s="12" t="s">
+        <v>161</v>
+      </c>
+      <c r="G34" s="97" t="s">
+        <v>16</v>
+      </c>
+      <c r="H34" s="93" t="s">
+        <v>64</v>
+      </c>
+      <c r="I34" s="27">
+        <v>45903</v>
+      </c>
+    </row>
+    <row r="35" spans="1:9">
       <c r="A35" s="6"/>
       <c r="B35" s="8"/>
       <c r="C35" s="7"/>
-      <c r="D35" s="8"/>
-      <c r="E35" s="8"/>
-      <c r="F35" s="9"/>
-      <c r="G35" s="6"/>
-      <c r="H35" s="9"/>
-    </row>
-    <row r="36" spans="1:8">
+      <c r="D35" s="23"/>
+      <c r="E35" s="23"/>
+      <c r="F35" s="15"/>
+      <c r="G35" s="97"/>
+      <c r="H35" s="93"/>
+      <c r="I35" s="13"/>
+    </row>
+    <row r="36" spans="1:9">
       <c r="A36" s="6"/>
       <c r="B36" s="8"/>
       <c r="C36" s="7"/>
       <c r="D36" s="8"/>
       <c r="E36" s="8"/>
       <c r="F36" s="9"/>
-      <c r="G36" s="6"/>
-      <c r="H36" s="9"/>
-    </row>
-    <row r="37" spans="1:8">
+      <c r="G36" s="97"/>
+      <c r="H36" s="93"/>
+      <c r="I36" s="13"/>
+    </row>
+    <row r="37" spans="1:9">
       <c r="A37" s="6"/>
       <c r="B37" s="8"/>
       <c r="C37" s="7"/>
       <c r="D37" s="8"/>
       <c r="E37" s="8"/>
       <c r="F37" s="9"/>
-      <c r="G37" s="6"/>
-      <c r="H37" s="9"/>
-    </row>
-    <row r="38" spans="1:8">
+      <c r="G37" s="97"/>
+      <c r="H37" s="93"/>
+      <c r="I37" s="13"/>
+    </row>
+    <row r="38" spans="1:9">
       <c r="A38" s="6"/>
       <c r="B38" s="8"/>
       <c r="C38" s="7"/>
       <c r="D38" s="8"/>
       <c r="E38" s="8"/>
       <c r="F38" s="9"/>
-      <c r="G38" s="6"/>
-      <c r="H38" s="9"/>
-    </row>
-    <row r="39" spans="1:8">
+      <c r="G38" s="97"/>
+      <c r="H38" s="93"/>
+      <c r="I38" s="13"/>
+    </row>
+    <row r="39" spans="1:9">
       <c r="A39" s="6"/>
       <c r="B39" s="8"/>
       <c r="C39" s="7"/>
       <c r="D39" s="8"/>
       <c r="E39" s="8"/>
       <c r="F39" s="9"/>
-      <c r="G39" s="6"/>
-      <c r="H39" s="9"/>
-    </row>
-    <row r="40" spans="1:8">
+      <c r="G39" s="97"/>
+      <c r="H39" s="93"/>
+      <c r="I39" s="13"/>
+    </row>
+    <row r="40" spans="1:9">
       <c r="A40" s="6"/>
       <c r="B40" s="8"/>
       <c r="C40" s="7"/>
       <c r="D40" s="8"/>
       <c r="E40" s="8"/>
       <c r="F40" s="9"/>
-      <c r="G40" s="6"/>
-      <c r="H40" s="9"/>
-    </row>
-    <row r="41" spans="1:8">
-      <c r="A41" s="6"/>
-      <c r="B41" s="8"/>
-      <c r="C41" s="7"/>
-      <c r="D41" s="8"/>
-      <c r="E41" s="8"/>
-      <c r="F41" s="9"/>
-      <c r="G41" s="6"/>
-      <c r="H41" s="9"/>
-    </row>
-    <row r="42" spans="1:8">
-      <c r="A42" s="6"/>
-      <c r="B42" s="8"/>
-      <c r="C42" s="7"/>
-      <c r="D42" s="8"/>
-      <c r="E42" s="8"/>
-      <c r="F42" s="9"/>
-      <c r="G42" s="6"/>
-      <c r="H42" s="9"/>
-    </row>
-    <row r="43" spans="1:8">
-      <c r="A43" s="6"/>
-      <c r="B43" s="8"/>
-      <c r="C43" s="7"/>
-      <c r="D43" s="8"/>
-      <c r="E43" s="8"/>
-      <c r="F43" s="9"/>
-      <c r="G43" s="6"/>
-      <c r="H43" s="9"/>
-    </row>
-    <row r="44" spans="1:8">
-      <c r="A44" s="6"/>
-      <c r="B44" s="8"/>
-      <c r="C44" s="7"/>
-      <c r="D44" s="8"/>
-      <c r="E44" s="8"/>
-      <c r="F44" s="9"/>
-      <c r="G44" s="6"/>
-      <c r="H44" s="9"/>
-    </row>
-    <row r="45" spans="1:8">
-      <c r="A45" s="6"/>
-      <c r="B45" s="8"/>
-      <c r="C45" s="7"/>
-      <c r="D45" s="8"/>
-      <c r="E45" s="8"/>
-      <c r="F45" s="9"/>
-      <c r="G45" s="6"/>
-      <c r="H45" s="9"/>
-    </row>
-    <row r="46" spans="1:8">
-      <c r="A46" s="6"/>
-      <c r="B46" s="8"/>
-      <c r="C46" s="7"/>
-      <c r="D46" s="8"/>
-      <c r="E46" s="8"/>
-      <c r="F46" s="9"/>
-      <c r="G46" s="6"/>
-      <c r="H46" s="9"/>
-    </row>
-    <row r="47" spans="1:8">
-      <c r="A47" s="6"/>
-      <c r="B47" s="8"/>
-      <c r="C47" s="7"/>
-      <c r="D47" s="8"/>
-      <c r="E47" s="8"/>
-      <c r="F47" s="9"/>
-      <c r="G47" s="6"/>
-      <c r="H47" s="9"/>
-    </row>
-    <row r="48" spans="1:8">
-      <c r="A48" s="6"/>
-      <c r="B48" s="8"/>
-      <c r="C48" s="7"/>
-      <c r="D48" s="8"/>
-      <c r="E48" s="8"/>
-      <c r="F48" s="9"/>
-      <c r="G48" s="6"/>
-      <c r="H48" s="9"/>
-    </row>
-    <row r="49" spans="1:8">
-      <c r="A49" s="6"/>
-      <c r="B49" s="8"/>
-      <c r="C49" s="7"/>
-      <c r="D49" s="8"/>
-      <c r="E49" s="8"/>
-      <c r="F49" s="9"/>
-      <c r="G49" s="6"/>
-      <c r="H49" s="9"/>
-    </row>
-    <row r="50" spans="1:8">
-      <c r="A50" s="6"/>
-      <c r="B50" s="8"/>
-      <c r="C50" s="7"/>
-      <c r="D50" s="8"/>
-      <c r="E50" s="8"/>
-      <c r="F50" s="9"/>
-      <c r="G50" s="6"/>
-      <c r="H50" s="9"/>
-    </row>
-    <row r="51" spans="1:8">
-      <c r="A51" s="6"/>
-      <c r="B51" s="8"/>
-      <c r="C51" s="7"/>
-      <c r="D51" s="8"/>
-      <c r="E51" s="8"/>
-      <c r="F51" s="9"/>
-      <c r="G51" s="6"/>
-      <c r="H51" s="9"/>
-    </row>
-    <row r="52" spans="1:8">
-      <c r="A52" s="6"/>
-      <c r="B52" s="8"/>
-      <c r="C52" s="7"/>
-      <c r="D52" s="8"/>
-      <c r="E52" s="8"/>
-      <c r="F52" s="9"/>
-      <c r="G52" s="6"/>
-      <c r="H52" s="9"/>
+      <c r="G40" s="97"/>
+      <c r="H40" s="93"/>
+      <c r="I40" s="13"/>
     </row>
   </sheetData>
   <conditionalFormatting sqref="B1:C1">
-    <cfRule type="notContainsBlanks" priority="3">
+    <cfRule type="notContainsBlanks" priority="5">
       <formula>LEN(TRIM(B1))&gt;0</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="D1:D1048576">
-    <cfRule type="duplicateValues" dxfId="0" priority="1"/>
-  </conditionalFormatting>
   <dataValidations count="2">
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="A2:A15" xr:uid="{69840FBE-03D6-48CB-B553-2E7186E1B4BD}">
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="A2:A34" xr:uid="{69840FBE-03D6-48CB-B553-2E7186E1B4BD}">
       <formula1>$J$2</formula1>
     </dataValidation>
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="G2:G38" xr:uid="{AF5C7196-9DAE-4339-82D4-9412023E2B2A}">
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="G2:G40" xr:uid="{AF5C7196-9DAE-4339-82D4-9412023E2B2A}">
       <formula1>"Vistoria Frustrada;,Vistoria Recusada,Bônus;,Desistência;,Inadimplência;,Política de Aceitação;,Duplicidade;,Demais Motivos,Falta de Vistoria;,"</formula1>
     </dataValidation>
   </dataValidations>
@@ -4931,17 +5581,17 @@
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{43D38813-FAE5-45C6-9D51-7607EDAA916D}">
   <dimension ref="A1:I55"/>
-  <sheetFormatPr defaultRowHeight="14.5"/>
+  <sheetFormatPr defaultRowHeight="15"/>
   <cols>
-    <col min="1" max="1" width="14.7265625" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="19.54296875" customWidth="1"/>
-    <col min="3" max="3" width="18.1796875" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="18.54296875" style="17" customWidth="1"/>
-    <col min="5" max="5" width="21.54296875" customWidth="1"/>
-    <col min="6" max="6" width="36.54296875" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="17.81640625" customWidth="1"/>
-    <col min="8" max="8" width="20.81640625" customWidth="1"/>
-    <col min="9" max="9" width="18.7265625" style="17" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="14.7109375" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="19.5703125" customWidth="1"/>
+    <col min="3" max="3" width="18.140625" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="18.5703125" style="17" customWidth="1"/>
+    <col min="5" max="5" width="21.5703125" customWidth="1"/>
+    <col min="6" max="6" width="36.5703125" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="17.85546875" customWidth="1"/>
+    <col min="8" max="8" width="20.85546875" customWidth="1"/>
+    <col min="9" max="9" width="18.7109375" style="17" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:9">
@@ -5622,16 +6272,16 @@
 <file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{B760CA2F-2CA8-44F2-8B49-339714F538DA}">
   <dimension ref="A1:I52"/>
-  <sheetFormatPr defaultRowHeight="14.5"/>
+  <sheetFormatPr defaultRowHeight="15"/>
   <cols>
-    <col min="2" max="2" width="14.54296875" customWidth="1"/>
+    <col min="2" max="2" width="14.5703125" customWidth="1"/>
     <col min="3" max="3" width="20" customWidth="1"/>
     <col min="4" max="4" width="19" customWidth="1"/>
-    <col min="5" max="5" width="16.81640625" customWidth="1"/>
+    <col min="5" max="5" width="16.85546875" customWidth="1"/>
     <col min="6" max="6" width="25" customWidth="1"/>
-    <col min="7" max="7" width="19.453125" customWidth="1"/>
-    <col min="8" max="8" width="24.7265625" customWidth="1"/>
-    <col min="9" max="9" width="21.453125" customWidth="1"/>
+    <col min="7" max="7" width="19.42578125" customWidth="1"/>
+    <col min="8" max="8" width="24.7109375" customWidth="1"/>
+    <col min="9" max="9" width="21.42578125" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:9">
@@ -6216,16 +6866,16 @@
 <file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{F6E6B8A0-66E5-406F-8D37-9E8A2778B9CB}">
   <dimension ref="A1:I56"/>
-  <sheetFormatPr defaultRowHeight="14.5"/>
+  <sheetFormatPr defaultRowHeight="15"/>
   <cols>
-    <col min="1" max="1" width="14.7265625" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="25.7265625" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="18.1796875" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="14.7109375" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="25.7109375" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="18.140625" bestFit="1" customWidth="1"/>
     <col min="4" max="4" width="26" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="29.54296875" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="18.7265625" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="20.26953125" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="28.81640625" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="29.5703125" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="18.7109375" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="20.28515625" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="28.85546875" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:9">
@@ -6878,15 +7528,6 @@
 </file>
 
 <file path=customXml/item1.xml><?xml version="1.0" encoding="utf-8"?>
-<?mso-contentType ?>
-<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
-  <Display>DocumentLibraryForm</Display>
-  <Edit>DocumentLibraryForm</Edit>
-  <New>DocumentLibraryForm</New>
-</FormTemplates>
-</file>
-
-<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
 <?mso-contentType ?>
 <spe:Receivers xmlns:spe="http://schemas.microsoft.com/sharepoint/events">
   <Receiver>
@@ -6936,7 +7577,7 @@
 </spe:Receivers>
 </file>
 
-<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
 <ct:contentTypeSchema xmlns:ct="http://schemas.microsoft.com/office/2006/metadata/contentType" xmlns:ma="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes" ct:_="" ma:_="" ma:contentTypeName="Document" ma:contentTypeID="0x01010006E7B04763359F4AAB0FC84D5027BFC8" ma:contentTypeVersion="44" ma:contentTypeDescription="Create a new document." ma:contentTypeScope="" ma:versionID="ac14f8cb44178d381f4c0afb30680a90">
   <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:ns1="http://schemas.microsoft.com/sharepoint/v3" xmlns:ns2="01f4fd7c-51c3-4ad2-ae58-e5034556b4ea" xmlns:ns3="ea6c6725-5210-4d6a-93cc-4cf85111ac5e" targetNamespace="http://schemas.microsoft.com/office/2006/metadata/properties" ma:root="true" ma:fieldsID="5e58414b065c9b590c40efa77cd84bb6" ns1:_="" ns2:_="" ns3:_="">
     <xsd:import namespace="http://schemas.microsoft.com/sharepoint/v3"/>
@@ -7314,7 +7955,7 @@
 </ct:contentTypeSchema>
 </file>
 
-<file path=customXml/item4.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
 <p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
   <documentManagement>
     <_dlc_DocId xmlns="01f4fd7c-51c3-4ad2-ae58-e5034556b4ea">QAFFA7D2F2TC-2102087286-496578</_dlc_DocId>
@@ -7357,50 +7998,27 @@
 </p:properties>
 </file>
 
+<file path=customXml/item4.xml><?xml version="1.0" encoding="utf-8"?>
+<?mso-contentType ?>
+<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
+  <Display>DocumentLibraryForm</Display>
+  <Edit>DocumentLibraryForm</Edit>
+  <New>DocumentLibraryForm</New>
+</FormTemplates>
+</file>
+
 <file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{BC9CB02D-0F63-4CE2-B316-61A87327416C}">
-  <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
-  </ds:schemaRefs>
-</ds:datastoreItem>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{13279B2D-D76C-4CA7-B517-83259B9C0FB4}"/>
 </file>
 
 <file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{13279B2D-D76C-4CA7-B517-83259B9C0FB4}">
-  <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/events"/>
-  </ds:schemaRefs>
-</ds:datastoreItem>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{5FB975A2-03C7-42F3-8F63-CE01D0A84F3D}"/>
 </file>
 
 <file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{5FB975A2-03C7-42F3-8F63-CE01D0A84F3D}">
-  <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/contentType"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes"/>
-    <ds:schemaRef ds:uri="http://www.w3.org/2001/XMLSchema"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3"/>
-    <ds:schemaRef ds:uri="01f4fd7c-51c3-4ad2-ae58-e5034556b4ea"/>
-    <ds:schemaRef ds:uri="ea6c6725-5210-4d6a-93cc-4cf85111ac5e"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/documentManagement/types"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
-    <ds:schemaRef ds:uri="http://schemas.openxmlformats.org/package/2006/metadata/core-properties"/>
-    <ds:schemaRef ds:uri="http://purl.org/dc/elements/1.1/"/>
-    <ds:schemaRef ds:uri="http://purl.org/dc/terms/"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/internal/obd"/>
-  </ds:schemaRefs>
-</ds:datastoreItem>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{C48653D8-7562-408C-9B57-D83FFA71DB43}"/>
 </file>
 
 <file path=customXml/itemProps4.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{C48653D8-7562-408C-9B57-D83FFA71DB43}">
-  <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
-    <ds:schemaRef ds:uri="01f4fd7c-51c3-4ad2-ae58-e5034556b4ea"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3"/>
-    <ds:schemaRef ds:uri="ea6c6725-5210-4d6a-93cc-4cf85111ac5e"/>
-  </ds:schemaRefs>
-</ds:datastoreItem>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{BC9CB02D-0F63-4CE2-B316-61A87327416C}"/>
 </file>